--- a/data/Incubation_Outreach_Tracker.xlsx
+++ b/data/Incubation_Outreach_Tracker.xlsx
@@ -12997,8 +12997,16 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
-      <c r="J199" s="14" t="n"/>
-      <c r="K199" s="14" t="n"/>
+      <c r="J199" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K199" s="14" t="inlineStr">
+        <is>
+          <t>External Mentor for Saveetha SIMATS Innovation &amp; Incubation Centre</t>
+        </is>
+      </c>
       <c r="L199" s="14" t="n"/>
       <c r="M199" s="14" t="inlineStr">
         <is>
@@ -34649,6 +34657,16 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>External Mentor for BIHER Incubation Centre</t>
+        </is>
+      </c>
       <c r="M511" s="9" t="inlineStr">
         <is>
           <t>https://www.bharathuniv.ac.in/Academic.php</t>
@@ -34894,6 +34912,16 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>External Advisor for TNAU Agribusiness Development</t>
+        </is>
+      </c>
       <c r="M516" s="9" t="inlineStr">
         <is>
           <t>https://tnau.ac.in/site/abd/directorss-desk/</t>
@@ -34949,6 +34977,16 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>External Mentor for Avinashilingam Innovation and Incubation Centre</t>
+        </is>
+      </c>
       <c r="M517" s="9" t="inlineStr">
         <is>
           <t>https://avinuty.ac.in/aiic/register-incubation</t>
@@ -34999,6 +35037,16 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>External Mentor for CMR University IIC</t>
+        </is>
+      </c>
       <c r="M518" s="9" t="inlineStr">
         <is>
           <t>https://cmr.edu.in/cmru-iic/</t>
@@ -35054,6 +35102,16 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>External Mentor for JNTUH DEIS</t>
+        </is>
+      </c>
       <c r="M519" s="9" t="inlineStr">
         <is>
           <t>https://www.jntuh.ac.in/rti-act</t>
@@ -35154,6 +35212,16 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>External Mentor for AIC MIT ADT</t>
+        </is>
+      </c>
       <c r="M521" s="9" t="inlineStr">
         <is>
           <t>https://mituniversity.ac.in/research/nisp/</t>
@@ -35209,6 +35277,16 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>External Mentor for D.Y. Patil CIIE</t>
+        </is>
+      </c>
       <c r="M522" s="9" t="inlineStr">
         <is>
           <t>https://www.dypiu.ac.in/centre-for-innovation-incubation-and-entrepreneurship</t>
@@ -35259,6 +35337,16 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>External Mentor for FLAME Centre for Entrepreneurship &amp; Innovation</t>
+        </is>
+      </c>
       <c r="M523" s="9" t="inlineStr">
         <is>
           <t>https://www.flame.edu.in/research/centres/centre-for-entrepreneurship-innovation/flame-incubator-program</t>
@@ -35309,6 +35397,16 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>External Mentor for Ahmedabad University VentureStudio</t>
+        </is>
+      </c>
       <c r="M524" s="9" t="inlineStr">
         <is>
           <t>https://ahduni.edu.in/academics/schools-centres/venturestudio/</t>
@@ -35494,6 +35592,16 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>External Mentor for BML Munjal I2E</t>
+        </is>
+      </c>
       <c r="M528" s="9" t="inlineStr">
         <is>
           <t>https://www.bmu.edu.in/institute-of-innovation-and-entrepreneurship-i2e/education/</t>
@@ -35594,6 +35702,16 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>External Mentor for MGU Business Innovation &amp; Incubation Centre</t>
+        </is>
+      </c>
       <c r="M530" s="9" t="inlineStr">
         <is>
           <t>https://biic.mgu.ac.in/team</t>
@@ -35689,6 +35807,16 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>External Mentor for Adamas University Incubation Cell</t>
+        </is>
+      </c>
       <c r="M532" s="9" t="inlineStr">
         <is>
           <t>https://incubation.adamasuniversity.ac.in/</t>
@@ -35787,6 +35915,16 @@
       <c r="I534" s="9" t="inlineStr">
         <is>
           <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>External Mentor for Shoolini eYUVA Innovation Centre</t>
         </is>
       </c>
       <c r="M534" s="9" t="inlineStr">

--- a/data/Incubation_Outreach_Tracker.xlsx
+++ b/data/Incubation_Outreach_Tracker.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q534"/>
+  <dimension ref="A1:Q601"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="9" min="1" max="1"/>
@@ -34657,12 +34657,12 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
-      <c r="J511" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="K511" t="inlineStr">
+      <c r="J511" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K511" s="9" t="inlineStr">
         <is>
           <t>External Mentor for BIHER Incubation Centre</t>
         </is>
@@ -34912,12 +34912,12 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
-      <c r="J516" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="K516" t="inlineStr">
+      <c r="J516" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K516" s="9" t="inlineStr">
         <is>
           <t>External Advisor for TNAU Agribusiness Development</t>
         </is>
@@ -34977,12 +34977,12 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
-      <c r="J517" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="K517" t="inlineStr">
+      <c r="J517" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K517" s="9" t="inlineStr">
         <is>
           <t>External Mentor for Avinashilingam Innovation and Incubation Centre</t>
         </is>
@@ -35037,12 +35037,12 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
-      <c r="J518" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="K518" t="inlineStr">
+      <c r="J518" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K518" s="9" t="inlineStr">
         <is>
           <t>External Mentor for CMR University IIC</t>
         </is>
@@ -35102,12 +35102,12 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
-      <c r="J519" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="K519" t="inlineStr">
+      <c r="J519" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K519" s="9" t="inlineStr">
         <is>
           <t>External Mentor for JNTUH DEIS</t>
         </is>
@@ -35212,12 +35212,12 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
-      <c r="J521" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="K521" t="inlineStr">
+      <c r="J521" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K521" s="9" t="inlineStr">
         <is>
           <t>External Mentor for AIC MIT ADT</t>
         </is>
@@ -35277,12 +35277,12 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
-      <c r="J522" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="K522" t="inlineStr">
+      <c r="J522" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K522" s="9" t="inlineStr">
         <is>
           <t>External Mentor for D.Y. Patil CIIE</t>
         </is>
@@ -35337,12 +35337,12 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
-      <c r="J523" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="K523" t="inlineStr">
+      <c r="J523" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K523" s="9" t="inlineStr">
         <is>
           <t>External Mentor for FLAME Centre for Entrepreneurship &amp; Innovation</t>
         </is>
@@ -35397,12 +35397,12 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
-      <c r="J524" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="K524" t="inlineStr">
+      <c r="J524" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K524" s="9" t="inlineStr">
         <is>
           <t>External Mentor for Ahmedabad University VentureStudio</t>
         </is>
@@ -35592,12 +35592,12 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
-      <c r="J528" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="K528" t="inlineStr">
+      <c r="J528" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K528" s="9" t="inlineStr">
         <is>
           <t>External Mentor for BML Munjal I2E</t>
         </is>
@@ -35702,12 +35702,12 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
-      <c r="J530" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="K530" t="inlineStr">
+      <c r="J530" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K530" s="9" t="inlineStr">
         <is>
           <t>External Mentor for MGU Business Innovation &amp; Incubation Centre</t>
         </is>
@@ -35807,12 +35807,12 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
-      <c r="J532" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="K532" t="inlineStr">
+      <c r="J532" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K532" s="9" t="inlineStr">
         <is>
           <t>External Mentor for Adamas University Incubation Cell</t>
         </is>
@@ -35917,12 +35917,12 @@
           <t>Drafted (not sent)</t>
         </is>
       </c>
-      <c r="J534" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="K534" t="inlineStr">
+      <c r="J534" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K534" s="9" t="inlineStr">
         <is>
           <t>External Mentor for Shoolini eYUVA Innovation Centre</t>
         </is>
@@ -35935,6 +35935,3681 @@
       <c r="N534" s="9" t="inlineStr">
         <is>
           <t>Role confirmed on official core-team page; email is the centre's shared address, not personal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="9" t="n">
+        <v>534</v>
+      </c>
+      <c r="B535" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C535" s="9" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="D535" s="9" t="inlineStr">
+        <is>
+          <t>IIT/IISc</t>
+        </is>
+      </c>
+      <c r="E535" s="9" t="inlineStr">
+        <is>
+          <t>IIT Indore</t>
+        </is>
+      </c>
+      <c r="H535" s="9" t="inlineStr">
+        <is>
+          <t>ardracademic@iiti.ac.in</t>
+        </is>
+      </c>
+      <c r="I535" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J535" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K535" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – IIT Indore</t>
+        </is>
+      </c>
+      <c r="M535" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N535" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="9" t="n">
+        <v>535</v>
+      </c>
+      <c r="B536" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C536" s="9" t="inlineStr">
+        <is>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="D536" s="9" t="inlineStr">
+        <is>
+          <t>IIT/IISc</t>
+        </is>
+      </c>
+      <c r="E536" s="9" t="inlineStr">
+        <is>
+          <t>IIT Gandhinagar</t>
+        </is>
+      </c>
+      <c r="H536" s="9" t="inlineStr">
+        <is>
+          <t>dr.acad@iitgn.ac.in</t>
+        </is>
+      </c>
+      <c r="I536" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J536" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K536" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – IIT Gandhinagar</t>
+        </is>
+      </c>
+      <c r="M536" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N536" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="9" t="n">
+        <v>536</v>
+      </c>
+      <c r="B537" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C537" s="9" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="D537" s="9" t="inlineStr">
+        <is>
+          <t>IIT/IISc</t>
+        </is>
+      </c>
+      <c r="E537" s="9" t="inlineStr">
+        <is>
+          <t>IIT Goa</t>
+        </is>
+      </c>
+      <c r="H537" s="9" t="inlineStr">
+        <is>
+          <t>dean.ap@iitgoa.ac.in</t>
+        </is>
+      </c>
+      <c r="I537" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J537" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K537" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – IIT Goa</t>
+        </is>
+      </c>
+      <c r="M537" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N537" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="9" t="n">
+        <v>537</v>
+      </c>
+      <c r="B538" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C538" s="9" t="inlineStr">
+        <is>
+          <t>Kerala</t>
+        </is>
+      </c>
+      <c r="D538" s="9" t="inlineStr">
+        <is>
+          <t>IIT/IISc</t>
+        </is>
+      </c>
+      <c r="E538" s="9" t="inlineStr">
+        <is>
+          <t>IIT Palakkad</t>
+        </is>
+      </c>
+      <c r="H538" s="9" t="inlineStr">
+        <is>
+          <t>chair.jee@iitpkd.ac.in</t>
+        </is>
+      </c>
+      <c r="I538" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J538" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K538" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – IIT Palakkad</t>
+        </is>
+      </c>
+      <c r="M538" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N538" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="9" t="n">
+        <v>538</v>
+      </c>
+      <c r="B539" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C539" s="9" t="inlineStr">
+        <is>
+          <t>Jammu &amp; Kashmir</t>
+        </is>
+      </c>
+      <c r="D539" s="9" t="inlineStr">
+        <is>
+          <t>IIT/IISc</t>
+        </is>
+      </c>
+      <c r="E539" s="9" t="inlineStr">
+        <is>
+          <t>IIT Jammu</t>
+        </is>
+      </c>
+      <c r="H539" s="9" t="inlineStr">
+        <is>
+          <t>jeechair@iitjammu.ac.in</t>
+        </is>
+      </c>
+      <c r="I539" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J539" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K539" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – IIT Jammu</t>
+        </is>
+      </c>
+      <c r="M539" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N539" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="9" t="n">
+        <v>539</v>
+      </c>
+      <c r="B540" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C540" s="9" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D540" s="9" t="inlineStr">
+        <is>
+          <t>IIT/IISc</t>
+        </is>
+      </c>
+      <c r="E540" s="9" t="inlineStr">
+        <is>
+          <t>IIT Dharwad</t>
+        </is>
+      </c>
+      <c r="H540" s="9" t="inlineStr">
+        <is>
+          <t>b.tech.admissions@iitdh.ac.in</t>
+        </is>
+      </c>
+      <c r="I540" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J540" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K540" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – IIT Dharwad</t>
+        </is>
+      </c>
+      <c r="M540" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N540" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="9" t="n">
+        <v>540</v>
+      </c>
+      <c r="B541" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C541" s="9" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="D541" s="9" t="inlineStr">
+        <is>
+          <t>NIT/IIEST</t>
+        </is>
+      </c>
+      <c r="E541" s="9" t="inlineStr">
+        <is>
+          <t>NIT Jalandhar</t>
+        </is>
+      </c>
+      <c r="H541" s="9" t="inlineStr">
+        <is>
+          <t>as.daug@nitj.ac.in</t>
+        </is>
+      </c>
+      <c r="I541" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J541" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K541" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIT Jalandhar</t>
+        </is>
+      </c>
+      <c r="M541" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N541" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="9" t="n">
+        <v>541</v>
+      </c>
+      <c r="B542" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C542" s="9" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="D542" s="9" t="inlineStr">
+        <is>
+          <t>NIT/IIEST</t>
+        </is>
+      </c>
+      <c r="E542" s="9" t="inlineStr">
+        <is>
+          <t>MANIT Bhopal</t>
+        </is>
+      </c>
+      <c r="H542" s="9" t="inlineStr">
+        <is>
+          <t>fic.admission@manit.ac.in</t>
+        </is>
+      </c>
+      <c r="I542" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J542" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K542" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – MANIT Bhopal</t>
+        </is>
+      </c>
+      <c r="M542" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N542" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="9" t="n">
+        <v>542</v>
+      </c>
+      <c r="B543" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C543" s="9" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="D543" s="9" t="inlineStr">
+        <is>
+          <t>NIT/IIEST</t>
+        </is>
+      </c>
+      <c r="E543" s="9" t="inlineStr">
+        <is>
+          <t>MNNIT Allahabad</t>
+        </is>
+      </c>
+      <c r="H543" s="9" t="inlineStr">
+        <is>
+          <t>admissioncell@mnnit.ac.in</t>
+        </is>
+      </c>
+      <c r="I543" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J543" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K543" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – MNNIT Allahabad</t>
+        </is>
+      </c>
+      <c r="M543" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N543" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="9" t="n">
+        <v>543</v>
+      </c>
+      <c r="B544" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C544" s="9" t="inlineStr">
+        <is>
+          <t>Tripura</t>
+        </is>
+      </c>
+      <c r="D544" s="9" t="inlineStr">
+        <is>
+          <t>NIT/IIEST</t>
+        </is>
+      </c>
+      <c r="E544" s="9" t="inlineStr">
+        <is>
+          <t>NIT Agartala</t>
+        </is>
+      </c>
+      <c r="H544" s="9" t="inlineStr">
+        <is>
+          <t>john.me@faculty.nita.ac.in</t>
+        </is>
+      </c>
+      <c r="I544" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J544" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K544" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIT Agartala</t>
+        </is>
+      </c>
+      <c r="M544" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N544" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="9" t="n">
+        <v>544</v>
+      </c>
+      <c r="B545" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C545" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D545" s="9" t="inlineStr">
+        <is>
+          <t>NIT/IIEST</t>
+        </is>
+      </c>
+      <c r="E545" s="9" t="inlineStr">
+        <is>
+          <t>NIT Durgapur</t>
+        </is>
+      </c>
+      <c r="H545" s="9" t="inlineStr">
+        <is>
+          <t>deanac@nitdgp.ac.in</t>
+        </is>
+      </c>
+      <c r="I545" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J545" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K545" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIT Durgapur</t>
+        </is>
+      </c>
+      <c r="M545" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N545" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="9" t="n">
+        <v>545</v>
+      </c>
+      <c r="B546" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C546" s="9" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="D546" s="9" t="inlineStr">
+        <is>
+          <t>NIT/IIEST</t>
+        </is>
+      </c>
+      <c r="E546" s="9" t="inlineStr">
+        <is>
+          <t>NIT Goa</t>
+        </is>
+      </c>
+      <c r="H546" s="9" t="inlineStr">
+        <is>
+          <t>ugadmissions@nitgoa.ac.in</t>
+        </is>
+      </c>
+      <c r="I546" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J546" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K546" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIT Goa</t>
+        </is>
+      </c>
+      <c r="M546" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N546" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="9" t="n">
+        <v>546</v>
+      </c>
+      <c r="B547" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C547" s="9" t="inlineStr">
+        <is>
+          <t>Himachal Pradesh</t>
+        </is>
+      </c>
+      <c r="D547" s="9" t="inlineStr">
+        <is>
+          <t>NIT/IIEST</t>
+        </is>
+      </c>
+      <c r="E547" s="9" t="inlineStr">
+        <is>
+          <t>NIT Hamirpur</t>
+        </is>
+      </c>
+      <c r="H547" s="9" t="inlineStr">
+        <is>
+          <t>rajeev@nith.ac.in</t>
+        </is>
+      </c>
+      <c r="I547" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J547" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K547" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIT Hamirpur</t>
+        </is>
+      </c>
+      <c r="M547" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N547" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="9" t="n">
+        <v>547</v>
+      </c>
+      <c r="B548" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C548" s="9" t="inlineStr">
+        <is>
+          <t>Meghalaya</t>
+        </is>
+      </c>
+      <c r="D548" s="9" t="inlineStr">
+        <is>
+          <t>NIT/IIEST</t>
+        </is>
+      </c>
+      <c r="E548" s="9" t="inlineStr">
+        <is>
+          <t>NIT Meghalaya</t>
+        </is>
+      </c>
+      <c r="H548" s="9" t="inlineStr">
+        <is>
+          <t>admissions_incharge_ug@nitm.ac.in</t>
+        </is>
+      </c>
+      <c r="I548" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J548" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K548" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIT Meghalaya</t>
+        </is>
+      </c>
+      <c r="M548" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N548" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="9" t="n">
+        <v>548</v>
+      </c>
+      <c r="B549" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C549" s="9" t="inlineStr">
+        <is>
+          <t>Nagaland</t>
+        </is>
+      </c>
+      <c r="D549" s="9" t="inlineStr">
+        <is>
+          <t>NIT/IIEST</t>
+        </is>
+      </c>
+      <c r="E549" s="9" t="inlineStr">
+        <is>
+          <t>NIT Nagaland</t>
+        </is>
+      </c>
+      <c r="H549" s="9" t="inlineStr">
+        <is>
+          <t>valan@nitnagaland.ac.in</t>
+        </is>
+      </c>
+      <c r="I549" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J549" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K549" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIT Nagaland</t>
+        </is>
+      </c>
+      <c r="M549" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N549" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="9" t="n">
+        <v>549</v>
+      </c>
+      <c r="B550" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C550" s="9" t="inlineStr">
+        <is>
+          <t>Puducherry</t>
+        </is>
+      </c>
+      <c r="D550" s="9" t="inlineStr">
+        <is>
+          <t>NIT/IIEST</t>
+        </is>
+      </c>
+      <c r="E550" s="9" t="inlineStr">
+        <is>
+          <t>NIT Puducherry</t>
+        </is>
+      </c>
+      <c r="H550" s="9" t="inlineStr">
+        <is>
+          <t>dean-acad@nitpy.ac.in</t>
+        </is>
+      </c>
+      <c r="I550" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J550" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K550" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIT Puducherry</t>
+        </is>
+      </c>
+      <c r="M550" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N550" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="9" t="n">
+        <v>550</v>
+      </c>
+      <c r="B551" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C551" s="9" t="inlineStr">
+        <is>
+          <t>Sikkim</t>
+        </is>
+      </c>
+      <c r="D551" s="9" t="inlineStr">
+        <is>
+          <t>NIT/IIEST</t>
+        </is>
+      </c>
+      <c r="E551" s="9" t="inlineStr">
+        <is>
+          <t>NIT Sikkim</t>
+        </is>
+      </c>
+      <c r="H551" s="9" t="inlineStr">
+        <is>
+          <t>basakranjan@nitsikkim.ac.in</t>
+        </is>
+      </c>
+      <c r="I551" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J551" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K551" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIT Sikkim</t>
+        </is>
+      </c>
+      <c r="M551" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N551" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="9" t="n">
+        <v>551</v>
+      </c>
+      <c r="B552" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C552" s="9" t="inlineStr">
+        <is>
+          <t>Jharkhand</t>
+        </is>
+      </c>
+      <c r="D552" s="9" t="inlineStr">
+        <is>
+          <t>NIT/IIEST</t>
+        </is>
+      </c>
+      <c r="E552" s="9" t="inlineStr">
+        <is>
+          <t>NIT Jamshedpur</t>
+        </is>
+      </c>
+      <c r="H552" s="9" t="inlineStr">
+        <is>
+          <t>ugadmission@nitjsr.ac.in</t>
+        </is>
+      </c>
+      <c r="I552" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J552" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K552" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIT Jamshedpur</t>
+        </is>
+      </c>
+      <c r="M552" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N552" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="9" t="n">
+        <v>552</v>
+      </c>
+      <c r="B553" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C553" s="9" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="D553" s="9" t="inlineStr">
+        <is>
+          <t>NIT/IIEST</t>
+        </is>
+      </c>
+      <c r="E553" s="9" t="inlineStr">
+        <is>
+          <t>NIT Kurukshetra</t>
+        </is>
+      </c>
+      <c r="H553" s="9" t="inlineStr">
+        <is>
+          <t>dean_academic@nitkkr.ac.in</t>
+        </is>
+      </c>
+      <c r="I553" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J553" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K553" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIT Kurukshetra</t>
+        </is>
+      </c>
+      <c r="M553" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N553" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="9" t="n">
+        <v>553</v>
+      </c>
+      <c r="B554" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C554" s="9" t="inlineStr">
+        <is>
+          <t>Manipur</t>
+        </is>
+      </c>
+      <c r="D554" s="9" t="inlineStr">
+        <is>
+          <t>NIT/IIEST</t>
+        </is>
+      </c>
+      <c r="E554" s="9" t="inlineStr">
+        <is>
+          <t>NIT Manipur</t>
+        </is>
+      </c>
+      <c r="H554" s="9" t="inlineStr">
+        <is>
+          <t>khel@nitmanipur.ac.in</t>
+        </is>
+      </c>
+      <c r="I554" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J554" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K554" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIT Manipur</t>
+        </is>
+      </c>
+      <c r="M554" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N554" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="9" t="n">
+        <v>554</v>
+      </c>
+      <c r="B555" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C555" s="9" t="inlineStr">
+        <is>
+          <t>Mizoram</t>
+        </is>
+      </c>
+      <c r="D555" s="9" t="inlineStr">
+        <is>
+          <t>NIT/IIEST</t>
+        </is>
+      </c>
+      <c r="E555" s="9" t="inlineStr">
+        <is>
+          <t>NIT Mizoram</t>
+        </is>
+      </c>
+      <c r="H555" s="9" t="inlineStr">
+        <is>
+          <t>dean_acad@nitmz.ac.in</t>
+        </is>
+      </c>
+      <c r="I555" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J555" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K555" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIT Mizoram</t>
+        </is>
+      </c>
+      <c r="M555" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N555" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="9" t="n">
+        <v>555</v>
+      </c>
+      <c r="B556" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C556" s="9" t="inlineStr">
+        <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="D556" s="9" t="inlineStr">
+        <is>
+          <t>NIT/IIEST</t>
+        </is>
+      </c>
+      <c r="E556" s="9" t="inlineStr">
+        <is>
+          <t>NIT Silchar</t>
+        </is>
+      </c>
+      <c r="H556" s="9" t="inlineStr">
+        <is>
+          <t>rdmisra@mech.nits.ac.in</t>
+        </is>
+      </c>
+      <c r="I556" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J556" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K556" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIT Silchar</t>
+        </is>
+      </c>
+      <c r="M556" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N556" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="9" t="n">
+        <v>556</v>
+      </c>
+      <c r="B557" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C557" s="9" t="inlineStr">
+        <is>
+          <t>Uttarakhand</t>
+        </is>
+      </c>
+      <c r="D557" s="9" t="inlineStr">
+        <is>
+          <t>NIT/IIEST</t>
+        </is>
+      </c>
+      <c r="E557" s="9" t="inlineStr">
+        <is>
+          <t>NIT Uttarakhand</t>
+        </is>
+      </c>
+      <c r="H557" s="9" t="inlineStr">
+        <is>
+          <t>dtripathi@nituk.ac.in</t>
+        </is>
+      </c>
+      <c r="I557" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J557" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K557" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIT Uttarakhand</t>
+        </is>
+      </c>
+      <c r="M557" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N557" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="9" t="n">
+        <v>557</v>
+      </c>
+      <c r="B558" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C558" s="9" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D558" s="9" t="inlineStr">
+        <is>
+          <t>NIT/IIEST</t>
+        </is>
+      </c>
+      <c r="E558" s="9" t="inlineStr">
+        <is>
+          <t>NIT Warangal</t>
+        </is>
+      </c>
+      <c r="H558" s="9" t="inlineStr">
+        <is>
+          <t>admissions@nitw.ac.in</t>
+        </is>
+      </c>
+      <c r="I558" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J558" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K558" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIT Warangal</t>
+        </is>
+      </c>
+      <c r="M558" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N558" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="9" t="n">
+        <v>558</v>
+      </c>
+      <c r="B559" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C559" s="9" t="inlineStr">
+        <is>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="D559" s="9" t="inlineStr">
+        <is>
+          <t>NIT/IIEST</t>
+        </is>
+      </c>
+      <c r="E559" s="9" t="inlineStr">
+        <is>
+          <t>SVNIT Surat</t>
+        </is>
+      </c>
+      <c r="H559" s="9" t="inlineStr">
+        <is>
+          <t>vk@phy.svnit.ac.in</t>
+        </is>
+      </c>
+      <c r="I559" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J559" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K559" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – SVNIT Surat</t>
+        </is>
+      </c>
+      <c r="M559" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N559" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="9" t="n">
+        <v>559</v>
+      </c>
+      <c r="B560" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C560" s="9" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="D560" s="9" t="inlineStr">
+        <is>
+          <t>NIT/IIEST</t>
+        </is>
+      </c>
+      <c r="E560" s="9" t="inlineStr">
+        <is>
+          <t>VNIT Nagpur</t>
+        </is>
+      </c>
+      <c r="H560" s="9" t="inlineStr">
+        <is>
+          <t>dr_acd@vnit.ac.in</t>
+        </is>
+      </c>
+      <c r="I560" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J560" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K560" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – VNIT Nagpur</t>
+        </is>
+      </c>
+      <c r="M560" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N560" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="9" t="n">
+        <v>560</v>
+      </c>
+      <c r="B561" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C561" s="9" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="D561" s="9" t="inlineStr">
+        <is>
+          <t>IIIT</t>
+        </is>
+      </c>
+      <c r="E561" s="9" t="inlineStr">
+        <is>
+          <t>ABV-IIITM Gwalior</t>
+        </is>
+      </c>
+      <c r="H561" s="9" t="inlineStr">
+        <is>
+          <t>academics@iiitm.ac.in</t>
+        </is>
+      </c>
+      <c r="I561" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J561" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K561" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – ABV-IIITM Gwalior</t>
+        </is>
+      </c>
+      <c r="M561" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N561" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="9" t="n">
+        <v>561</v>
+      </c>
+      <c r="B562" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C562" s="9" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="D562" s="9" t="inlineStr">
+        <is>
+          <t>IIIT</t>
+        </is>
+      </c>
+      <c r="E562" s="9" t="inlineStr">
+        <is>
+          <t>IIIT Kota</t>
+        </is>
+      </c>
+      <c r="H562" s="9" t="inlineStr">
+        <is>
+          <t>admissions@iiitkota.ac.in</t>
+        </is>
+      </c>
+      <c r="I562" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J562" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K562" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – IIIT Kota</t>
+        </is>
+      </c>
+      <c r="M562" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N562" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="9" t="n">
+        <v>562</v>
+      </c>
+      <c r="B563" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C563" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D563" s="9" t="inlineStr">
+        <is>
+          <t>IIIT</t>
+        </is>
+      </c>
+      <c r="E563" s="9" t="inlineStr">
+        <is>
+          <t>IIIT Kalyani</t>
+        </is>
+      </c>
+      <c r="H563" s="9" t="inlineStr">
+        <is>
+          <t>chinmoy@iiitkalyani.ac.in</t>
+        </is>
+      </c>
+      <c r="I563" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J563" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K563" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – IIIT Kalyani</t>
+        </is>
+      </c>
+      <c r="M563" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N563" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="9" t="n">
+        <v>563</v>
+      </c>
+      <c r="B564" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C564" s="9" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="D564" s="9" t="inlineStr">
+        <is>
+          <t>IIIT</t>
+        </is>
+      </c>
+      <c r="E564" s="9" t="inlineStr">
+        <is>
+          <t>IIIT Sonepat</t>
+        </is>
+      </c>
+      <c r="H564" s="9" t="inlineStr">
+        <is>
+          <t>ckumar@iiitsonepat.ac.in</t>
+        </is>
+      </c>
+      <c r="I564" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J564" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K564" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – IIIT Sonepat</t>
+        </is>
+      </c>
+      <c r="M564" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N564" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="9" t="n">
+        <v>564</v>
+      </c>
+      <c r="B565" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C565" s="9" t="inlineStr">
+        <is>
+          <t>Himachal Pradesh</t>
+        </is>
+      </c>
+      <c r="D565" s="9" t="inlineStr">
+        <is>
+          <t>IIIT</t>
+        </is>
+      </c>
+      <c r="E565" s="9" t="inlineStr">
+        <is>
+          <t>IIIT Una</t>
+        </is>
+      </c>
+      <c r="H565" s="9" t="inlineStr">
+        <is>
+          <t>csabcoordinator@iiitu.ac.in</t>
+        </is>
+      </c>
+      <c r="I565" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J565" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K565" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – IIIT Una</t>
+        </is>
+      </c>
+      <c r="M565" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N565" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="9" t="n">
+        <v>565</v>
+      </c>
+      <c r="B566" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C566" s="9" t="inlineStr">
+        <is>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="D566" s="9" t="inlineStr">
+        <is>
+          <t>IIIT</t>
+        </is>
+      </c>
+      <c r="E566" s="9" t="inlineStr">
+        <is>
+          <t>IIIT Vadodara</t>
+        </is>
+      </c>
+      <c r="H566" s="9" t="inlineStr">
+        <is>
+          <t>admissions@iiitvadodara.ac.in</t>
+        </is>
+      </c>
+      <c r="I566" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J566" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K566" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – IIIT Vadodara</t>
+        </is>
+      </c>
+      <c r="M566" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N566" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="9" t="n">
+        <v>566</v>
+      </c>
+      <c r="B567" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C567" s="9" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="D567" s="9" t="inlineStr">
+        <is>
+          <t>IIIT</t>
+        </is>
+      </c>
+      <c r="E567" s="9" t="inlineStr">
+        <is>
+          <t>IIIT Allahabad</t>
+        </is>
+      </c>
+      <c r="H567" s="9" t="inlineStr">
+        <is>
+          <t>dean.acad@iiita.ac.in</t>
+        </is>
+      </c>
+      <c r="I567" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J567" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K567" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – IIIT Allahabad</t>
+        </is>
+      </c>
+      <c r="M567" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N567" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="9" t="n">
+        <v>567</v>
+      </c>
+      <c r="B568" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C568" s="9" t="inlineStr">
+        <is>
+          <t>Manipur</t>
+        </is>
+      </c>
+      <c r="D568" s="9" t="inlineStr">
+        <is>
+          <t>IIIT</t>
+        </is>
+      </c>
+      <c r="E568" s="9" t="inlineStr">
+        <is>
+          <t>IIIT Senapati Manipur</t>
+        </is>
+      </c>
+      <c r="H568" s="9" t="inlineStr">
+        <is>
+          <t>admission@iiitmanipur.ac.in</t>
+        </is>
+      </c>
+      <c r="I568" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J568" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K568" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – IIIT Senapati Manipur</t>
+        </is>
+      </c>
+      <c r="M568" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N568" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="9" t="n">
+        <v>568</v>
+      </c>
+      <c r="B569" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C569" s="9" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="D569" s="9" t="inlineStr">
+        <is>
+          <t>IIIT</t>
+        </is>
+      </c>
+      <c r="E569" s="9" t="inlineStr">
+        <is>
+          <t>IIIT Lucknow</t>
+        </is>
+      </c>
+      <c r="H569" s="9" t="inlineStr">
+        <is>
+          <t>deepshikha@iiitl.ac.in</t>
+        </is>
+      </c>
+      <c r="I569" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J569" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K569" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – IIIT Lucknow</t>
+        </is>
+      </c>
+      <c r="M569" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N569" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="9" t="n">
+        <v>569</v>
+      </c>
+      <c r="B570" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C570" s="9" t="inlineStr">
+        <is>
+          <t>Kerala</t>
+        </is>
+      </c>
+      <c r="D570" s="9" t="inlineStr">
+        <is>
+          <t>IIIT</t>
+        </is>
+      </c>
+      <c r="E570" s="9" t="inlineStr">
+        <is>
+          <t>IIIT Kottayam</t>
+        </is>
+      </c>
+      <c r="H570" s="9" t="inlineStr">
+        <is>
+          <t>ugadmissions@iiitkottayam.ac.in</t>
+        </is>
+      </c>
+      <c r="I570" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J570" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K570" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – IIIT Kottayam</t>
+        </is>
+      </c>
+      <c r="M570" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N570" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="9" t="n">
+        <v>570</v>
+      </c>
+      <c r="B571" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C571" s="9" t="inlineStr">
+        <is>
+          <t>Jharkhand</t>
+        </is>
+      </c>
+      <c r="D571" s="9" t="inlineStr">
+        <is>
+          <t>IIIT</t>
+        </is>
+      </c>
+      <c r="E571" s="9" t="inlineStr">
+        <is>
+          <t>IIIT Ranchi</t>
+        </is>
+      </c>
+      <c r="H571" s="9" t="inlineStr">
+        <is>
+          <t>admission@iiitranchi.ac.in</t>
+        </is>
+      </c>
+      <c r="I571" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J571" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K571" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – IIIT Ranchi</t>
+        </is>
+      </c>
+      <c r="M571" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N571" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="9" t="n">
+        <v>571</v>
+      </c>
+      <c r="B572" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C572" s="9" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="D572" s="9" t="inlineStr">
+        <is>
+          <t>IIIT</t>
+        </is>
+      </c>
+      <c r="E572" s="9" t="inlineStr">
+        <is>
+          <t>IIIT Nagpur</t>
+        </is>
+      </c>
+      <c r="H572" s="9" t="inlineStr">
+        <is>
+          <t>jchakole@iiitn.ac.in</t>
+        </is>
+      </c>
+      <c r="I572" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J572" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K572" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – IIIT Nagpur</t>
+        </is>
+      </c>
+      <c r="M572" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N572" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="9" t="n">
+        <v>572</v>
+      </c>
+      <c r="B573" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C573" s="9" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="D573" s="9" t="inlineStr">
+        <is>
+          <t>IIIT</t>
+        </is>
+      </c>
+      <c r="E573" s="9" t="inlineStr">
+        <is>
+          <t>IIIT Pune</t>
+        </is>
+      </c>
+      <c r="H573" s="9" t="inlineStr">
+        <is>
+          <t>bhupendra@iiitp.ac.in</t>
+        </is>
+      </c>
+      <c r="I573" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J573" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K573" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – IIIT Pune</t>
+        </is>
+      </c>
+      <c r="M573" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N573" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="9" t="n">
+        <v>573</v>
+      </c>
+      <c r="B574" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C574" s="9" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="D574" s="9" t="inlineStr">
+        <is>
+          <t>IIIT</t>
+        </is>
+      </c>
+      <c r="E574" s="9" t="inlineStr">
+        <is>
+          <t>IIIT Bhopal</t>
+        </is>
+      </c>
+      <c r="H574" s="9" t="inlineStr">
+        <is>
+          <t>ugadmissions@iiitbhopal.ac.in</t>
+        </is>
+      </c>
+      <c r="I574" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J574" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K574" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – IIIT Bhopal</t>
+        </is>
+      </c>
+      <c r="M574" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N574" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="9" t="n">
+        <v>574</v>
+      </c>
+      <c r="B575" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C575" s="9" t="inlineStr">
+        <is>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="D575" s="9" t="inlineStr">
+        <is>
+          <t>IIIT</t>
+        </is>
+      </c>
+      <c r="E575" s="9" t="inlineStr">
+        <is>
+          <t>IIIT Surat</t>
+        </is>
+      </c>
+      <c r="H575" s="9" t="inlineStr">
+        <is>
+          <t>admission@iiitsurat.ac.in</t>
+        </is>
+      </c>
+      <c r="I575" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J575" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K575" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – IIIT Surat</t>
+        </is>
+      </c>
+      <c r="M575" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N575" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="9" t="n">
+        <v>575</v>
+      </c>
+      <c r="B576" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C576" s="9" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D576" s="9" t="inlineStr">
+        <is>
+          <t>IIIT</t>
+        </is>
+      </c>
+      <c r="E576" s="9" t="inlineStr">
+        <is>
+          <t>IIIT Raichur</t>
+        </is>
+      </c>
+      <c r="H576" s="9" t="inlineStr">
+        <is>
+          <t>alka03@iiitr.ac.in</t>
+        </is>
+      </c>
+      <c r="I576" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J576" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K576" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – IIIT Raichur</t>
+        </is>
+      </c>
+      <c r="M576" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N576" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="9" t="n">
+        <v>576</v>
+      </c>
+      <c r="B577" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C577" s="9" t="inlineStr">
+        <is>
+          <t>Dadra and Nagar Haveli and Daman and Diu</t>
+        </is>
+      </c>
+      <c r="D577" s="9" t="inlineStr">
+        <is>
+          <t>IIIT</t>
+        </is>
+      </c>
+      <c r="E577" s="9" t="inlineStr">
+        <is>
+          <t>IIIT Vadodara International Campus Diu</t>
+        </is>
+      </c>
+      <c r="H577" s="9" t="inlineStr">
+        <is>
+          <t>nodal_officer@diu.iiitvadodara.ac.in</t>
+        </is>
+      </c>
+      <c r="I577" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J577" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K577" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – IIIT Vadodara International Campus Diu</t>
+        </is>
+      </c>
+      <c r="M577" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N577" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="9" t="n">
+        <v>577</v>
+      </c>
+      <c r="B578" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C578" s="9" t="inlineStr">
+        <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="D578" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E578" s="9" t="inlineStr">
+        <is>
+          <t>Assam University, Silchar – Engineering/Technical Programmes</t>
+        </is>
+      </c>
+      <c r="H578" s="9" t="inlineStr">
+        <is>
+          <t>vc@aus.ac.in</t>
+        </is>
+      </c>
+      <c r="I578" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J578" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K578" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – Assam University, Silchar – Engineering/Technical Programmes</t>
+        </is>
+      </c>
+      <c r="M578" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N578" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="9" t="n">
+        <v>578</v>
+      </c>
+      <c r="B579" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C579" s="9" t="inlineStr">
+        <is>
+          <t>Uttarakhand</t>
+        </is>
+      </c>
+      <c r="D579" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E579" s="9" t="inlineStr">
+        <is>
+          <t>Gurukula Kangri Vishwavidyalaya – Faculty of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="H579" s="9" t="inlineStr">
+        <is>
+          <t>murli.tiwari@gkv.ac.in</t>
+        </is>
+      </c>
+      <c r="I579" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J579" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K579" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – Gurukula Kangri Vishwavidyalaya – Faculty of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="M579" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N579" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="9" t="n">
+        <v>579</v>
+      </c>
+      <c r="B580" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C580" s="9" t="inlineStr">
+        <is>
+          <t>Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="D580" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E580" s="9" t="inlineStr">
+        <is>
+          <t>Guru Ghasidas Vishwavidyalaya – School of Engineering</t>
+        </is>
+      </c>
+      <c r="H580" s="9" t="inlineStr">
+        <is>
+          <t>deanetggv@gmail.com</t>
+        </is>
+      </c>
+      <c r="I580" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J580" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K580" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – Guru Ghasidas Vishwavidyalaya – School of Engineering</t>
+        </is>
+      </c>
+      <c r="M580" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N580" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="9" t="n">
+        <v>580</v>
+      </c>
+      <c r="B581" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C581" s="9" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="D581" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E581" s="9" t="inlineStr">
+        <is>
+          <t>NIELIT Aurangabad</t>
+        </is>
+      </c>
+      <c r="H581" s="9" t="inlineStr">
+        <is>
+          <t>anirban@nielit.gov.in</t>
+        </is>
+      </c>
+      <c r="I581" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J581" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K581" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIELIT Aurangabad</t>
+        </is>
+      </c>
+      <c r="M581" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N581" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="9" t="n">
+        <v>581</v>
+      </c>
+      <c r="B582" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C582" s="9" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="D582" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E582" s="9" t="inlineStr">
+        <is>
+          <t>School of Planning &amp; Architecture Bhopal</t>
+        </is>
+      </c>
+      <c r="H582" s="9" t="inlineStr">
+        <is>
+          <t>amitkhare@spabhopal.ac.in</t>
+        </is>
+      </c>
+      <c r="I582" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J582" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K582" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – School of Planning &amp; Architecture Bhopal</t>
+        </is>
+      </c>
+      <c r="M582" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N582" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="9" t="n">
+        <v>582</v>
+      </c>
+      <c r="B583" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C583" s="9" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D583" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E583" s="9" t="inlineStr">
+        <is>
+          <t>School of Planning &amp; Architecture New Delhi</t>
+        </is>
+      </c>
+      <c r="H583" s="9" t="inlineStr">
+        <is>
+          <t>admission@spa.ac.in</t>
+        </is>
+      </c>
+      <c r="I583" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J583" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K583" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – School of Planning &amp; Architecture New Delhi</t>
+        </is>
+      </c>
+      <c r="M583" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N583" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="9" t="n">
+        <v>583</v>
+      </c>
+      <c r="B584" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C584" s="9" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="D584" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E584" s="9" t="inlineStr">
+        <is>
+          <t>School of Planning &amp; Architecture Vijayawada</t>
+        </is>
+      </c>
+      <c r="H584" s="9" t="inlineStr">
+        <is>
+          <t>admission@spav.ac.in</t>
+        </is>
+      </c>
+      <c r="I584" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J584" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K584" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – School of Planning &amp; Architecture Vijayawada</t>
+        </is>
+      </c>
+      <c r="M584" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N584" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="9" t="n">
+        <v>584</v>
+      </c>
+      <c r="B585" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C585" s="9" t="inlineStr">
+        <is>
+          <t>Jammu &amp; Kashmir</t>
+        </is>
+      </c>
+      <c r="D585" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E585" s="9" t="inlineStr">
+        <is>
+          <t>Shri Mata Vaishno Devi University</t>
+        </is>
+      </c>
+      <c r="H585" s="9" t="inlineStr">
+        <is>
+          <t>amit.pandit@smvdu.ac.in</t>
+        </is>
+      </c>
+      <c r="I585" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J585" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K585" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – Shri Mata Vaishno Devi University</t>
+        </is>
+      </c>
+      <c r="M585" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N585" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="9" t="n">
+        <v>585</v>
+      </c>
+      <c r="B586" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C586" s="9" t="inlineStr">
+        <is>
+          <t>Chandigarh</t>
+        </is>
+      </c>
+      <c r="D586" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E586" s="9" t="inlineStr">
+        <is>
+          <t>Punjab Engineering College (Deemed to be University)</t>
+        </is>
+      </c>
+      <c r="H586" s="9" t="inlineStr">
+        <is>
+          <t>admissions@pec.edu.in</t>
+        </is>
+      </c>
+      <c r="I586" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J586" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K586" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – Punjab Engineering College (Deemed to be University)</t>
+        </is>
+      </c>
+      <c r="M586" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N586" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="9" t="n">
+        <v>586</v>
+      </c>
+      <c r="B587" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C587" s="9" t="inlineStr">
+        <is>
+          <t>Puducherry</t>
+        </is>
+      </c>
+      <c r="D587" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E587" s="9" t="inlineStr">
+        <is>
+          <t>Puducherry Technological University</t>
+        </is>
+      </c>
+      <c r="H587" s="9" t="inlineStr">
+        <is>
+          <t>admissions@ptuniv.edu.in</t>
+        </is>
+      </c>
+      <c r="I587" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J587" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K587" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – Puducherry Technological University</t>
+        </is>
+      </c>
+      <c r="M587" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N587" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="9" t="n">
+        <v>587</v>
+      </c>
+      <c r="B588" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C588" s="9" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="D588" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E588" s="9" t="inlineStr">
+        <is>
+          <t>NIFTEM Kundli</t>
+        </is>
+      </c>
+      <c r="H588" s="9" t="inlineStr">
+        <is>
+          <t>mkprayaga.niftem@gmail.com</t>
+        </is>
+      </c>
+      <c r="I588" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J588" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K588" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIFTEM Kundli</t>
+        </is>
+      </c>
+      <c r="M588" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N588" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="9" t="n">
+        <v>588</v>
+      </c>
+      <c r="B589" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C589" s="9" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="D589" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E589" s="9" t="inlineStr">
+        <is>
+          <t>NIFTEM Thanjavur</t>
+        </is>
+      </c>
+      <c r="H589" s="9" t="inlineStr">
+        <is>
+          <t>admission@iifpt.edu.in</t>
+        </is>
+      </c>
+      <c r="I589" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J589" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K589" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIFTEM Thanjavur</t>
+        </is>
+      </c>
+      <c r="M589" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N589" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="9" t="n">
+        <v>589</v>
+      </c>
+      <c r="B590" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C590" s="9" t="inlineStr">
+        <is>
+          <t>Meghalaya</t>
+        </is>
+      </c>
+      <c r="D590" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E590" s="9" t="inlineStr">
+        <is>
+          <t>North-Eastern Hill University – Engineering/Technology</t>
+        </is>
+      </c>
+      <c r="H590" s="9" t="inlineStr">
+        <is>
+          <t>sufal.das@gmail.com</t>
+        </is>
+      </c>
+      <c r="I590" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J590" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K590" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – North-Eastern Hill University – Engineering/Technology</t>
+        </is>
+      </c>
+      <c r="M590" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N590" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="9" t="n">
+        <v>590</v>
+      </c>
+      <c r="B591" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C591" s="9" t="inlineStr">
+        <is>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="D591" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E591" s="9" t="inlineStr">
+        <is>
+          <t>Gati Shakti Vishwavidyalaya</t>
+        </is>
+      </c>
+      <c r="H591" s="9" t="inlineStr">
+        <is>
+          <t>admission@gsv.ac.in</t>
+        </is>
+      </c>
+      <c r="I591" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J591" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K591" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – Gati Shakti Vishwavidyalaya</t>
+        </is>
+      </c>
+      <c r="M591" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N591" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="9" t="n">
+        <v>591</v>
+      </c>
+      <c r="B592" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C592" s="9" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="D592" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E592" s="9" t="inlineStr">
+        <is>
+          <t>NIELIT Ropar</t>
+        </is>
+      </c>
+      <c r="H592" s="9" t="inlineStr">
+        <is>
+          <t>dir-ropar@nielit.gov.in</t>
+        </is>
+      </c>
+      <c r="I592" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J592" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K592" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIELIT Ropar</t>
+        </is>
+      </c>
+      <c r="M592" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N592" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="9" t="n">
+        <v>592</v>
+      </c>
+      <c r="B593" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C593" s="9" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D593" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E593" s="9" t="inlineStr">
+        <is>
+          <t>NIELIT Patna</t>
+        </is>
+      </c>
+      <c r="H593" s="9" t="inlineStr">
+        <is>
+          <t>dir-patna@nielit.gov.in</t>
+        </is>
+      </c>
+      <c r="I593" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J593" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K593" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIELIT Patna</t>
+        </is>
+      </c>
+      <c r="M593" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N593" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="9" t="n">
+        <v>593</v>
+      </c>
+      <c r="B594" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C594" s="9" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="D594" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E594" s="9" t="inlineStr">
+        <is>
+          <t>NIELIT Ajmer</t>
+        </is>
+      </c>
+      <c r="H594" s="9" t="inlineStr">
+        <is>
+          <t>dir-ajmer@nielit.gov.in</t>
+        </is>
+      </c>
+      <c r="I594" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J594" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K594" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIELIT Ajmer</t>
+        </is>
+      </c>
+      <c r="M594" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N594" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="9" t="n">
+        <v>594</v>
+      </c>
+      <c r="B595" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C595" s="9" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="D595" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E595" s="9" t="inlineStr">
+        <is>
+          <t>NIELIT Gorakhpur</t>
+        </is>
+      </c>
+      <c r="H595" s="9" t="inlineStr">
+        <is>
+          <t>dir-gorakhpur@nielit.gov.in</t>
+        </is>
+      </c>
+      <c r="I595" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J595" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K595" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIELIT Gorakhpur</t>
+        </is>
+      </c>
+      <c r="M595" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N595" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="9" t="n">
+        <v>595</v>
+      </c>
+      <c r="B596" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C596" s="9" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="D596" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E596" s="9" t="inlineStr">
+        <is>
+          <t>Rajiv Gandhi National Aviation University</t>
+        </is>
+      </c>
+      <c r="H596" s="9" t="inlineStr">
+        <is>
+          <t>academic@rgnau.ac.in</t>
+        </is>
+      </c>
+      <c r="I596" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J596" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K596" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – Rajiv Gandhi National Aviation University</t>
+        </is>
+      </c>
+      <c r="M596" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N596" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="9" t="n">
+        <v>596</v>
+      </c>
+      <c r="B597" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C597" s="9" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="D597" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E597" s="9" t="inlineStr">
+        <is>
+          <t>NITTTR Bhopal</t>
+        </is>
+      </c>
+      <c r="H597" s="9" t="inlineStr">
+        <is>
+          <t>mbhargava@nitttrbpl.ac.in</t>
+        </is>
+      </c>
+      <c r="I597" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J597" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K597" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NITTTR Bhopal</t>
+        </is>
+      </c>
+      <c r="M597" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N597" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="9" t="n">
+        <v>597</v>
+      </c>
+      <c r="B598" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C598" s="9" t="inlineStr">
+        <is>
+          <t>Mizoram</t>
+        </is>
+      </c>
+      <c r="D598" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E598" s="9" t="inlineStr">
+        <is>
+          <t>NIELIT Aizawl</t>
+        </is>
+      </c>
+      <c r="H598" s="9" t="inlineStr">
+        <is>
+          <t>dir-aizawl@nielit.gov.in</t>
+        </is>
+      </c>
+      <c r="I598" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J598" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K598" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIELIT Aizawl</t>
+        </is>
+      </c>
+      <c r="M598" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N598" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="9" t="n">
+        <v>598</v>
+      </c>
+      <c r="B599" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C599" s="9" t="inlineStr">
+        <is>
+          <t>Manipur</t>
+        </is>
+      </c>
+      <c r="D599" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E599" s="9" t="inlineStr">
+        <is>
+          <t>NIELIT Imphal</t>
+        </is>
+      </c>
+      <c r="H599" s="9" t="inlineStr">
+        <is>
+          <t>dir-imphal@nielit.gov.in</t>
+        </is>
+      </c>
+      <c r="I599" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J599" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K599" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIELIT Imphal</t>
+        </is>
+      </c>
+      <c r="M599" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N599" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="9" t="n">
+        <v>599</v>
+      </c>
+      <c r="B600" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C600" s="9" t="inlineStr">
+        <is>
+          <t>Nagaland</t>
+        </is>
+      </c>
+      <c r="D600" s="9" t="inlineStr">
+        <is>
+          <t>GFTI / Technical University</t>
+        </is>
+      </c>
+      <c r="E600" s="9" t="inlineStr">
+        <is>
+          <t>NIELIT Kohima</t>
+        </is>
+      </c>
+      <c r="H600" s="9" t="inlineStr">
+        <is>
+          <t>dir-kohima@nielit.gov.in</t>
+        </is>
+      </c>
+      <c r="I600" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J600" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="K600" s="9" t="inlineStr">
+        <is>
+          <t>External Advisor / Mentor Outreach – NIELIT Kohima</t>
+        </is>
+      </c>
+      <c r="M600" s="9" t="inlineStr">
+        <is>
+          <t>https://josaa.admissions.nic.in/applicant/seatmatrix/instituteview.aspx</t>
+        </is>
+      </c>
+      <c r="N600" s="9" t="inlineStr">
+        <is>
+          <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="9" t="n">
+        <v>600</v>
+      </c>
+      <c r="B601" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C601" s="9" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="D601" s="9" t="inlineStr">
+        <is>
+          <t>IIT/IISc</t>
+        </is>
+      </c>
+      <c r="E601" s="9" t="inlineStr">
+        <is>
+          <t>NIT Tiruchirappalli</t>
+        </is>
+      </c>
+      <c r="F601" s="9" t="inlineStr">
+        <is>
+          <t>CEDI</t>
+        </is>
+      </c>
+      <c r="H601" s="9" t="inlineStr">
+        <is>
+          <t>ug@nitt.edu</t>
+        </is>
+      </c>
+      <c r="I601" s="9" t="inlineStr">
+        <is>
+          <t>Skipped: Already emailed via CEDI, NIT Trichy (cedi@nitt.edu)</t>
+        </is>
+      </c>
+      <c r="N601" s="9" t="inlineStr">
+        <is>
+          <t>Candidate from new upload was a generic UG admissions address; institution already contacted via its actual incubation centre.</t>
         </is>
       </c>
     </row>
@@ -35997,7 +39672,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="10">
@@ -36007,7 +39682,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>14</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="10">

--- a/data/Incubation_Outreach_Tracker.xlsx
+++ b/data/Incubation_Outreach_Tracker.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q601"/>
+  <dimension ref="A1:Q683"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="9" min="1" max="1"/>
@@ -39613,6 +39613,3942 @@
         </is>
       </c>
     </row>
+    <row r="602">
+      <c r="A602" s="9" t="n">
+        <v>601</v>
+      </c>
+      <c r="B602" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C602" s="9" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="D602" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E602" s="9" t="inlineStr">
+        <is>
+          <t>University College of Engineering Kakinada</t>
+        </is>
+      </c>
+      <c r="F602" s="9" t="inlineStr"/>
+      <c r="G602" s="9" t="inlineStr"/>
+      <c r="H602" s="9" t="inlineStr">
+        <is>
+          <t>principal.ucek@jntucek.ac.in</t>
+        </is>
+      </c>
+      <c r="I602" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M602" s="9" t="inlineStr">
+        <is>
+          <t>https://www.jntucek.ac.in/administration</t>
+        </is>
+      </c>
+      <c r="N602" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O602" s="9" t="n"/>
+    </row>
+    <row r="603">
+      <c r="A603" s="9" t="n">
+        <v>602</v>
+      </c>
+      <c r="B603" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C603" s="9" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="D603" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E603" s="9" t="inlineStr">
+        <is>
+          <t>RGUKT-RK Valley</t>
+        </is>
+      </c>
+      <c r="F603" s="9" t="inlineStr"/>
+      <c r="G603" s="9" t="inlineStr"/>
+      <c r="H603" s="9" t="inlineStr">
+        <is>
+          <t>director@rguktrkv.ac.in</t>
+        </is>
+      </c>
+      <c r="I603" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M603" s="9" t="inlineStr">
+        <is>
+          <t>https://rgukt.in/contact-directory/</t>
+        </is>
+      </c>
+      <c r="N603" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O603" s="9" t="n"/>
+    </row>
+    <row r="604">
+      <c r="A604" s="9" t="n">
+        <v>603</v>
+      </c>
+      <c r="B604" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C604" s="9" t="inlineStr">
+        <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="D604" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E604" s="9" t="inlineStr">
+        <is>
+          <t>Assam Don Bosco University School of Technology</t>
+        </is>
+      </c>
+      <c r="F604" s="9" t="inlineStr"/>
+      <c r="G604" s="9" t="inlineStr"/>
+      <c r="H604" s="9" t="inlineStr">
+        <is>
+          <t>contact@dbuniversity.ac.in</t>
+        </is>
+      </c>
+      <c r="I604" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M604" s="9" t="inlineStr">
+        <is>
+          <t>https://dbuniversity.ac.in/contactus</t>
+        </is>
+      </c>
+      <c r="N604" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O604" s="9" t="n"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="9" t="n">
+        <v>604</v>
+      </c>
+      <c r="B605" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C605" s="9" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D605" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E605" s="9" t="inlineStr">
+        <is>
+          <t>Bhagwan Parshuram Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F605" s="9" t="inlineStr"/>
+      <c r="G605" s="9" t="inlineStr"/>
+      <c r="H605" s="9" t="inlineStr">
+        <is>
+          <t>bpitindia@yahoo.com</t>
+        </is>
+      </c>
+      <c r="I605" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M605" s="9" t="inlineStr">
+        <is>
+          <t>https://bpitindia.ac.in/contact/</t>
+        </is>
+      </c>
+      <c r="N605" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O605" s="9" t="n"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="9" t="n">
+        <v>605</v>
+      </c>
+      <c r="B606" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C606" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D606" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E606" s="9" t="inlineStr">
+        <is>
+          <t>Bengal Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F606" s="9" t="inlineStr"/>
+      <c r="G606" s="9" t="inlineStr"/>
+      <c r="H606" s="9" t="inlineStr">
+        <is>
+          <t>admin.bit@bitcollege.in</t>
+        </is>
+      </c>
+      <c r="I606" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M606" s="9" t="inlineStr">
+        <is>
+          <t>https://www.bitcollege.in/ContactUs</t>
+        </is>
+      </c>
+      <c r="N606" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O606" s="9" t="n"/>
+    </row>
+    <row r="607">
+      <c r="A607" s="9" t="n">
+        <v>606</v>
+      </c>
+      <c r="B607" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C607" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D607" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E607" s="9" t="inlineStr">
+        <is>
+          <t>Narula Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F607" s="9" t="inlineStr"/>
+      <c r="G607" s="9" t="inlineStr"/>
+      <c r="H607" s="9" t="inlineStr">
+        <is>
+          <t>info@nit.ac.in</t>
+        </is>
+      </c>
+      <c r="I607" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M607" s="9" t="inlineStr">
+        <is>
+          <t>https://www.nit.ac.in/contact.php</t>
+        </is>
+      </c>
+      <c r="N607" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O607" s="9" t="n"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="9" t="n">
+        <v>607</v>
+      </c>
+      <c r="B608" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C608" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D608" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E608" s="9" t="inlineStr">
+        <is>
+          <t>Government College of Engineering and Leather Technology</t>
+        </is>
+      </c>
+      <c r="F608" s="9" t="inlineStr"/>
+      <c r="G608" s="9" t="inlineStr"/>
+      <c r="H608" s="9" t="inlineStr">
+        <is>
+          <t>principal@gcelt.gov.in</t>
+        </is>
+      </c>
+      <c r="I608" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M608" s="9" t="inlineStr">
+        <is>
+          <t>https://gcelt.gov.in/contact-us-5/</t>
+        </is>
+      </c>
+      <c r="N608" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O608" s="9" t="n"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="9" t="n">
+        <v>608</v>
+      </c>
+      <c r="B609" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C609" s="9" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="D609" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E609" s="9" t="inlineStr">
+        <is>
+          <t>Dr. Mahalingam College of Engineering and Technology</t>
+        </is>
+      </c>
+      <c r="F609" s="9" t="inlineStr"/>
+      <c r="G609" s="9" t="inlineStr"/>
+      <c r="H609" s="9" t="inlineStr">
+        <is>
+          <t>principal@drmcet.ac.in</t>
+        </is>
+      </c>
+      <c r="I609" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M609" s="9" t="inlineStr">
+        <is>
+          <t>https://drmcet.ac.in/contact/</t>
+        </is>
+      </c>
+      <c r="N609" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O609" s="9" t="n"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="9" t="n">
+        <v>609</v>
+      </c>
+      <c r="B610" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C610" s="9" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="D610" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E610" s="9" t="inlineStr">
+        <is>
+          <t>Baba Kuma Singh Ji Engg College, Amritsar</t>
+        </is>
+      </c>
+      <c r="F610" s="9" t="inlineStr"/>
+      <c r="G610" s="9" t="inlineStr"/>
+      <c r="H610" s="9" t="inlineStr">
+        <is>
+          <t>bksjec14@gmail.com</t>
+        </is>
+      </c>
+      <c r="I610" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M610" s="9" t="inlineStr">
+        <is>
+          <t>https://bksjec.in/contact/</t>
+        </is>
+      </c>
+      <c r="N610" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O610" s="9" t="n"/>
+    </row>
+    <row r="611">
+      <c r="A611" s="9" t="n">
+        <v>610</v>
+      </c>
+      <c r="B611" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C611" s="9" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="D611" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E611" s="9" t="inlineStr">
+        <is>
+          <t>MCT's Rajiv Gandhi Institute of Technology, Mumbai</t>
+        </is>
+      </c>
+      <c r="F611" s="9" t="inlineStr"/>
+      <c r="G611" s="9" t="inlineStr"/>
+      <c r="H611" s="9" t="inlineStr">
+        <is>
+          <t>adminrgit@mctrgit.ac.in</t>
+        </is>
+      </c>
+      <c r="I611" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M611" s="9" t="inlineStr">
+        <is>
+          <t>https://www.mctrgit.ac.in/contact</t>
+        </is>
+      </c>
+      <c r="N611" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O611" s="9" t="n"/>
+    </row>
+    <row r="612">
+      <c r="A612" s="9" t="n">
+        <v>611</v>
+      </c>
+      <c r="B612" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C612" s="9" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="D612" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E612" s="9" t="inlineStr">
+        <is>
+          <t>Nagaji Institute of Technology &amp; Management, Gwalior</t>
+        </is>
+      </c>
+      <c r="F612" s="9" t="inlineStr"/>
+      <c r="G612" s="9" t="inlineStr"/>
+      <c r="H612" s="9" t="inlineStr">
+        <is>
+          <t>nitmadm0917@gmail.com</t>
+        </is>
+      </c>
+      <c r="I612" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M612" s="9" t="inlineStr">
+        <is>
+          <t>https://nagajiinstitutes.org/contact-us.aspx</t>
+        </is>
+      </c>
+      <c r="N612" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O612" s="9" t="n"/>
+    </row>
+    <row r="613">
+      <c r="A613" s="9" t="n">
+        <v>612</v>
+      </c>
+      <c r="B613" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C613" s="9" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D613" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E613" s="9" t="inlineStr">
+        <is>
+          <t>Mangalore Institute of Technology &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="F613" s="9" t="inlineStr"/>
+      <c r="G613" s="9" t="inlineStr"/>
+      <c r="H613" s="9" t="inlineStr">
+        <is>
+          <t>info@mite.ac.in</t>
+        </is>
+      </c>
+      <c r="I613" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M613" s="9" t="inlineStr">
+        <is>
+          <t>https://mite.ac.in/</t>
+        </is>
+      </c>
+      <c r="N613" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O613" s="9" t="n"/>
+    </row>
+    <row r="614">
+      <c r="A614" s="9" t="n">
+        <v>613</v>
+      </c>
+      <c r="B614" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C614" s="9" t="inlineStr">
+        <is>
+          <t>Jharkhand</t>
+        </is>
+      </c>
+      <c r="D614" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E614" s="9" t="inlineStr">
+        <is>
+          <t>Guru Gobind Singh Educational Society's Technical Campus</t>
+        </is>
+      </c>
+      <c r="F614" s="9" t="inlineStr"/>
+      <c r="G614" s="9" t="inlineStr"/>
+      <c r="H614" s="9" t="inlineStr">
+        <is>
+          <t>info@ggsestc.ac.in</t>
+        </is>
+      </c>
+      <c r="I614" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M614" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ggsestc.ac.in/contact-us</t>
+        </is>
+      </c>
+      <c r="N614" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O614" s="9" t="n"/>
+    </row>
+    <row r="615">
+      <c r="A615" s="9" t="n">
+        <v>614</v>
+      </c>
+      <c r="B615" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C615" s="9" t="inlineStr">
+        <is>
+          <t>Himachal Pradesh</t>
+        </is>
+      </c>
+      <c r="D615" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E615" s="9" t="inlineStr">
+        <is>
+          <t>Mahatma Gandhi Government Engineering College, Kotla Jeori</t>
+        </is>
+      </c>
+      <c r="F615" s="9" t="inlineStr"/>
+      <c r="G615" s="9" t="inlineStr"/>
+      <c r="H615" s="9" t="inlineStr">
+        <is>
+          <t>gecrampur@gmail.com</t>
+        </is>
+      </c>
+      <c r="I615" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M615" s="9" t="inlineStr">
+        <is>
+          <t>https://www.mggec.ac.in/contactus.aspx</t>
+        </is>
+      </c>
+      <c r="N615" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O615" s="9" t="n"/>
+    </row>
+    <row r="616">
+      <c r="A616" s="9" t="n">
+        <v>615</v>
+      </c>
+      <c r="B616" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C616" s="9" t="inlineStr">
+        <is>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="D616" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E616" s="9" t="inlineStr">
+        <is>
+          <t>Government Engineering College, Modasa</t>
+        </is>
+      </c>
+      <c r="F616" s="9" t="inlineStr"/>
+      <c r="G616" s="9" t="inlineStr"/>
+      <c r="H616" s="9" t="inlineStr">
+        <is>
+          <t>gec-modasa-dte@gujarat.gov.in</t>
+        </is>
+      </c>
+      <c r="I616" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M616" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gecmodasa.ac.in/</t>
+        </is>
+      </c>
+      <c r="N616" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O616" s="9" t="n"/>
+    </row>
+    <row r="617">
+      <c r="A617" s="9" t="n">
+        <v>616</v>
+      </c>
+      <c r="B617" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C617" s="9" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="D617" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E617" s="9" t="inlineStr">
+        <is>
+          <t>DVR &amp; Dr. HS MIC College of Technology</t>
+        </is>
+      </c>
+      <c r="F617" s="9" t="inlineStr"/>
+      <c r="G617" s="9" t="inlineStr"/>
+      <c r="H617" s="9" t="inlineStr">
+        <is>
+          <t>office@mictech.ac.in</t>
+        </is>
+      </c>
+      <c r="I617" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M617" s="9" t="inlineStr">
+        <is>
+          <t>https://www.mictech.edu.in/</t>
+        </is>
+      </c>
+      <c r="N617" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O617" s="9" t="n"/>
+    </row>
+    <row r="618">
+      <c r="A618" s="9" t="n">
+        <v>617</v>
+      </c>
+      <c r="B618" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C618" s="9" t="inlineStr">
+        <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="D618" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E618" s="9" t="inlineStr">
+        <is>
+          <t>The Assam Royal Global University</t>
+        </is>
+      </c>
+      <c r="F618" s="9" t="inlineStr"/>
+      <c r="G618" s="9" t="inlineStr"/>
+      <c r="H618" s="9" t="inlineStr">
+        <is>
+          <t>admissions@rgu.ac</t>
+        </is>
+      </c>
+      <c r="I618" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M618" s="9" t="inlineStr">
+        <is>
+          <t>https://www.rgu.ac/contact-us</t>
+        </is>
+      </c>
+      <c r="N618" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O618" s="9" t="n"/>
+    </row>
+    <row r="619">
+      <c r="A619" s="9" t="n">
+        <v>618</v>
+      </c>
+      <c r="B619" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C619" s="9" t="inlineStr">
+        <is>
+          <t>Chandigarh</t>
+        </is>
+      </c>
+      <c r="D619" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E619" s="9" t="inlineStr">
+        <is>
+          <t>SVKM's NMIMS Deemed to be University (Chandigarh)</t>
+        </is>
+      </c>
+      <c r="F619" s="9" t="inlineStr"/>
+      <c r="G619" s="9" t="inlineStr"/>
+      <c r="H619" s="9" t="inlineStr">
+        <is>
+          <t>admission.chandigarh@nmims.edu</t>
+        </is>
+      </c>
+      <c r="I619" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M619" s="9" t="inlineStr">
+        <is>
+          <t>https://chandigarh.nmims.edu/get-in-touch/</t>
+        </is>
+      </c>
+      <c r="N619" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O619" s="9" t="n"/>
+    </row>
+    <row r="620">
+      <c r="A620" s="9" t="n">
+        <v>619</v>
+      </c>
+      <c r="B620" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C620" s="9" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D620" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E620" s="9" t="inlineStr">
+        <is>
+          <t>Delhi Technological University</t>
+        </is>
+      </c>
+      <c r="F620" s="9" t="inlineStr"/>
+      <c r="G620" s="9" t="inlineStr"/>
+      <c r="H620" s="9" t="inlineStr">
+        <is>
+          <t>ga@dtu.ac.in</t>
+        </is>
+      </c>
+      <c r="I620" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M620" s="9" t="inlineStr">
+        <is>
+          <t>https://ga.dtu.ac.in/contact.htm</t>
+        </is>
+      </c>
+      <c r="N620" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O620" s="9" t="n"/>
+    </row>
+    <row r="621">
+      <c r="A621" s="9" t="n">
+        <v>620</v>
+      </c>
+      <c r="B621" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C621" s="9" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="D621" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E621" s="9" t="inlineStr">
+        <is>
+          <t>Padre Conceicao College of Engineering</t>
+        </is>
+      </c>
+      <c r="F621" s="9" t="inlineStr"/>
+      <c r="G621" s="9" t="inlineStr"/>
+      <c r="H621" s="9" t="inlineStr">
+        <is>
+          <t>agnelpcce@gmail.com</t>
+        </is>
+      </c>
+      <c r="I621" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M621" s="9" t="inlineStr">
+        <is>
+          <t>https://pccegoa.edu.in/contact-us/</t>
+        </is>
+      </c>
+      <c r="N621" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O621" s="9" t="n"/>
+    </row>
+    <row r="622">
+      <c r="A622" s="9" t="n">
+        <v>621</v>
+      </c>
+      <c r="B622" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C622" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D622" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E622" s="9" t="inlineStr">
+        <is>
+          <t>Heritage Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F622" s="9" t="inlineStr"/>
+      <c r="G622" s="9" t="inlineStr"/>
+      <c r="H622" s="9" t="inlineStr">
+        <is>
+          <t>info@heritageit.edu</t>
+        </is>
+      </c>
+      <c r="I622" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M622" s="9" t="inlineStr">
+        <is>
+          <t>https://www.heritageit.edu/</t>
+        </is>
+      </c>
+      <c r="N622" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O622" s="9" t="n"/>
+    </row>
+    <row r="623">
+      <c r="A623" s="9" t="n">
+        <v>622</v>
+      </c>
+      <c r="B623" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C623" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D623" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E623" s="9" t="inlineStr">
+        <is>
+          <t>JIS College of Engineering</t>
+        </is>
+      </c>
+      <c r="F623" s="9" t="inlineStr"/>
+      <c r="G623" s="9" t="inlineStr"/>
+      <c r="H623" s="9" t="inlineStr">
+        <is>
+          <t>info.jiscollege@jisgroup.org</t>
+        </is>
+      </c>
+      <c r="I623" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M623" s="9" t="inlineStr">
+        <is>
+          <t>https://www.jiscollege.ac.in/contact-us.php</t>
+        </is>
+      </c>
+      <c r="N623" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O623" s="9" t="n"/>
+    </row>
+    <row r="624">
+      <c r="A624" s="9" t="n">
+        <v>623</v>
+      </c>
+      <c r="B624" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C624" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D624" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E624" s="9" t="inlineStr">
+        <is>
+          <t>Bengal Institute of Technology and Management</t>
+        </is>
+      </c>
+      <c r="F624" s="9" t="inlineStr"/>
+      <c r="G624" s="9" t="inlineStr"/>
+      <c r="H624" s="9" t="inlineStr">
+        <is>
+          <t>info@bitms.ac.in</t>
+        </is>
+      </c>
+      <c r="I624" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M624" s="9" t="inlineStr">
+        <is>
+          <t>https://bitms.ac.in/about-us/contact-us/</t>
+        </is>
+      </c>
+      <c r="N624" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O624" s="9" t="n"/>
+    </row>
+    <row r="625">
+      <c r="A625" s="9" t="n">
+        <v>624</v>
+      </c>
+      <c r="B625" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C625" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D625" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E625" s="9" t="inlineStr">
+        <is>
+          <t>Bankura Unnayani Institute of Engineering</t>
+        </is>
+      </c>
+      <c r="F625" s="9" t="inlineStr"/>
+      <c r="G625" s="9" t="inlineStr"/>
+      <c r="H625" s="9" t="inlineStr">
+        <is>
+          <t>info@buie.ac.in</t>
+        </is>
+      </c>
+      <c r="I625" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M625" s="9" t="inlineStr">
+        <is>
+          <t>https://www.buie.ac.in/admission/contact</t>
+        </is>
+      </c>
+      <c r="N625" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O625" s="9" t="n"/>
+    </row>
+    <row r="626">
+      <c r="A626" s="9" t="n">
+        <v>625</v>
+      </c>
+      <c r="B626" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C626" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D626" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E626" s="9" t="inlineStr">
+        <is>
+          <t>Calcutta Institute of Engineering and Management</t>
+        </is>
+      </c>
+      <c r="F626" s="9" t="inlineStr"/>
+      <c r="G626" s="9" t="inlineStr"/>
+      <c r="H626" s="9" t="inlineStr">
+        <is>
+          <t>director@ciem.ac.in</t>
+        </is>
+      </c>
+      <c r="I626" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M626" s="9" t="inlineStr">
+        <is>
+          <t>https://ciem.ac.in/</t>
+        </is>
+      </c>
+      <c r="N626" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O626" s="9" t="n"/>
+    </row>
+    <row r="627">
+      <c r="A627" s="9" t="n">
+        <v>626</v>
+      </c>
+      <c r="B627" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C627" s="9" t="inlineStr">
+        <is>
+          <t>Uttarakhand</t>
+        </is>
+      </c>
+      <c r="D627" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E627" s="9" t="inlineStr">
+        <is>
+          <t>Shivalik College of Engineering</t>
+        </is>
+      </c>
+      <c r="F627" s="9" t="inlineStr"/>
+      <c r="G627" s="9" t="inlineStr"/>
+      <c r="H627" s="9" t="inlineStr">
+        <is>
+          <t>info@shivalikcollege.edu.in</t>
+        </is>
+      </c>
+      <c r="I627" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M627" s="9" t="inlineStr">
+        <is>
+          <t>https://shivalikcollege.edu.in/contact-us/</t>
+        </is>
+      </c>
+      <c r="N627" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O627" s="9" t="n"/>
+    </row>
+    <row r="628">
+      <c r="A628" s="9" t="n">
+        <v>627</v>
+      </c>
+      <c r="B628" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C628" s="9" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="D628" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E628" s="9" t="inlineStr">
+        <is>
+          <t>Institute of Technology &amp; Management, Lucknow</t>
+        </is>
+      </c>
+      <c r="F628" s="9" t="inlineStr"/>
+      <c r="G628" s="9" t="inlineStr"/>
+      <c r="H628" s="9" t="inlineStr">
+        <is>
+          <t>itmlko@gmail.com</t>
+        </is>
+      </c>
+      <c r="I628" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M628" s="9" t="inlineStr">
+        <is>
+          <t>https://itmlucknow.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="N628" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O628" s="9" t="n"/>
+    </row>
+    <row r="629">
+      <c r="A629" s="9" t="n">
+        <v>628</v>
+      </c>
+      <c r="B629" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C629" s="9" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="D629" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E629" s="9" t="inlineStr">
+        <is>
+          <t>Podhigai College of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="F629" s="9" t="inlineStr"/>
+      <c r="G629" s="9" t="inlineStr"/>
+      <c r="H629" s="9" t="inlineStr">
+        <is>
+          <t>podhigaitech@gmail.com</t>
+        </is>
+      </c>
+      <c r="I629" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M629" s="9" t="inlineStr">
+        <is>
+          <t>https://www.podhigaitech.ac.in/</t>
+        </is>
+      </c>
+      <c r="N629" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O629" s="9" t="n"/>
+    </row>
+    <row r="630">
+      <c r="A630" s="9" t="n">
+        <v>629</v>
+      </c>
+      <c r="B630" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C630" s="9" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="D630" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E630" s="9" t="inlineStr">
+        <is>
+          <t>B.K. Birla Institute of Engineering and Technology</t>
+        </is>
+      </c>
+      <c r="F630" s="9" t="inlineStr"/>
+      <c r="G630" s="9" t="inlineStr"/>
+      <c r="H630" s="9" t="inlineStr">
+        <is>
+          <t>admissions@bkbiet.ac.in</t>
+        </is>
+      </c>
+      <c r="I630" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M630" s="9" t="inlineStr">
+        <is>
+          <t>https://bkbiet.ac.in/contact-us/</t>
+        </is>
+      </c>
+      <c r="N630" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O630" s="9" t="n"/>
+    </row>
+    <row r="631">
+      <c r="A631" s="9" t="n">
+        <v>630</v>
+      </c>
+      <c r="B631" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C631" s="9" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="D631" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E631" s="9" t="inlineStr">
+        <is>
+          <t>Apeejay Institute of Management and Engineering Technical Campus</t>
+        </is>
+      </c>
+      <c r="F631" s="9" t="inlineStr"/>
+      <c r="G631" s="9" t="inlineStr"/>
+      <c r="H631" s="9" t="inlineStr">
+        <is>
+          <t>admissions@aimetc.apeejay.edu</t>
+        </is>
+      </c>
+      <c r="I631" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M631" s="9" t="inlineStr">
+        <is>
+          <t>https://aimetc.apeejay.edu/connect/contact-details/</t>
+        </is>
+      </c>
+      <c r="N631" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O631" s="9" t="n"/>
+    </row>
+    <row r="632">
+      <c r="A632" s="9" t="n">
+        <v>631</v>
+      </c>
+      <c r="B632" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C632" s="9" t="inlineStr">
+        <is>
+          <t>Puducherry</t>
+        </is>
+      </c>
+      <c r="D632" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E632" s="9" t="inlineStr">
+        <is>
+          <t>Christ College of Engineering and Technology</t>
+        </is>
+      </c>
+      <c r="F632" s="9" t="inlineStr"/>
+      <c r="G632" s="9" t="inlineStr"/>
+      <c r="H632" s="9" t="inlineStr">
+        <is>
+          <t>contact@christcet.edu.in</t>
+        </is>
+      </c>
+      <c r="I632" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M632" s="9" t="inlineStr">
+        <is>
+          <t>https://christcet.edu.in/</t>
+        </is>
+      </c>
+      <c r="N632" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O632" s="9" t="n"/>
+    </row>
+    <row r="633">
+      <c r="A633" s="9" t="n">
+        <v>632</v>
+      </c>
+      <c r="B633" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C633" s="9" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="D633" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E633" s="9" t="inlineStr">
+        <is>
+          <t>GITA Autonomous College, Bhubaneswar</t>
+        </is>
+      </c>
+      <c r="F633" s="9" t="inlineStr"/>
+      <c r="G633" s="9" t="inlineStr"/>
+      <c r="H633" s="9" t="inlineStr">
+        <is>
+          <t>admissions@gita.edu.in</t>
+        </is>
+      </c>
+      <c r="I633" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M633" s="9" t="inlineStr">
+        <is>
+          <t>https://gita.edu.in/contact.php</t>
+        </is>
+      </c>
+      <c r="N633" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O633" s="9" t="n"/>
+    </row>
+    <row r="634">
+      <c r="A634" s="9" t="n">
+        <v>633</v>
+      </c>
+      <c r="B634" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C634" s="9" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="D634" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E634" s="9" t="inlineStr">
+        <is>
+          <t>Genba Sopanrao Moze Trust's Parvatibai Genba Moze College of Engineering, Wagholi, Pune</t>
+        </is>
+      </c>
+      <c r="F634" s="9" t="inlineStr"/>
+      <c r="G634" s="9" t="inlineStr"/>
+      <c r="H634" s="9" t="inlineStr">
+        <is>
+          <t>principal@pgmozecoepune.in</t>
+        </is>
+      </c>
+      <c r="I634" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M634" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pgmozecoepune.in/contact/</t>
+        </is>
+      </c>
+      <c r="N634" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O634" s="9" t="n"/>
+    </row>
+    <row r="635">
+      <c r="A635" s="9" t="n">
+        <v>634</v>
+      </c>
+      <c r="B635" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C635" s="9" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="D635" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E635" s="9" t="inlineStr">
+        <is>
+          <t>Swami Vivekanand College of Engineering, Indore</t>
+        </is>
+      </c>
+      <c r="F635" s="9" t="inlineStr"/>
+      <c r="G635" s="9" t="inlineStr"/>
+      <c r="H635" s="9" t="inlineStr">
+        <is>
+          <t>info@svceindore.ac.in</t>
+        </is>
+      </c>
+      <c r="I635" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M635" s="9" t="inlineStr">
+        <is>
+          <t>https://vivekanandgroup.com/contact-us</t>
+        </is>
+      </c>
+      <c r="N635" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O635" s="9" t="n"/>
+    </row>
+    <row r="636">
+      <c r="A636" s="9" t="n">
+        <v>635</v>
+      </c>
+      <c r="B636" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C636" s="9" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D636" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E636" s="9" t="inlineStr">
+        <is>
+          <t>Nitte Meenakshi Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F636" s="9" t="inlineStr"/>
+      <c r="G636" s="9" t="inlineStr"/>
+      <c r="H636" s="9" t="inlineStr">
+        <is>
+          <t>admissions.nmit@nitte.edu.in</t>
+        </is>
+      </c>
+      <c r="I636" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M636" s="9" t="inlineStr">
+        <is>
+          <t>https://nitte.edu.in/nmit/contact-nmit.php</t>
+        </is>
+      </c>
+      <c r="N636" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O636" s="9" t="n"/>
+    </row>
+    <row r="637">
+      <c r="A637" s="9" t="n">
+        <v>636</v>
+      </c>
+      <c r="B637" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C637" s="9" t="inlineStr">
+        <is>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="D637" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E637" s="9" t="inlineStr">
+        <is>
+          <t>Shree Swaminarayan Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F637" s="9" t="inlineStr"/>
+      <c r="G637" s="9" t="inlineStr"/>
+      <c r="H637" s="9" t="inlineStr">
+        <is>
+          <t>admin@ssit.co.in</t>
+        </is>
+      </c>
+      <c r="I637" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M637" s="9" t="inlineStr">
+        <is>
+          <t>https://ssit.co.in/</t>
+        </is>
+      </c>
+      <c r="N637" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O637" s="9" t="n"/>
+    </row>
+    <row r="638">
+      <c r="A638" s="9" t="n">
+        <v>637</v>
+      </c>
+      <c r="B638" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C638" s="9" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="D638" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E638" s="9" t="inlineStr">
+        <is>
+          <t>R.K. College of Engineering</t>
+        </is>
+      </c>
+      <c r="F638" s="9" t="inlineStr"/>
+      <c r="G638" s="9" t="inlineStr"/>
+      <c r="H638" s="9" t="inlineStr">
+        <is>
+          <t>admin@rkce.ac.in</t>
+        </is>
+      </c>
+      <c r="I638" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M638" s="9" t="inlineStr">
+        <is>
+          <t>https://www.rkce.ac.in/</t>
+        </is>
+      </c>
+      <c r="N638" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O638" s="9" t="n"/>
+    </row>
+    <row r="639">
+      <c r="A639" s="9" t="n">
+        <v>638</v>
+      </c>
+      <c r="B639" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C639" s="9" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="D639" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E639" s="9" t="inlineStr">
+        <is>
+          <t>Sir C R Reddy College of Engineering</t>
+        </is>
+      </c>
+      <c r="F639" s="9" t="inlineStr"/>
+      <c r="G639" s="9" t="inlineStr"/>
+      <c r="H639" s="9" t="inlineStr">
+        <is>
+          <t>principal@sircrrcoestd.in</t>
+        </is>
+      </c>
+      <c r="I639" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M639" s="9" t="inlineStr">
+        <is>
+          <t>https://sircrrcoestd.in/</t>
+        </is>
+      </c>
+      <c r="N639" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O639" s="9" t="n"/>
+    </row>
+    <row r="640">
+      <c r="A640" s="9" t="n">
+        <v>639</v>
+      </c>
+      <c r="B640" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C640" s="9" t="inlineStr">
+        <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="D640" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E640" s="9" t="inlineStr">
+        <is>
+          <t>Bineswar Brahma Engineering College</t>
+        </is>
+      </c>
+      <c r="F640" s="9" t="inlineStr"/>
+      <c r="G640" s="9" t="inlineStr"/>
+      <c r="H640" s="9" t="inlineStr">
+        <is>
+          <t>bbeckokrajhar@gmail.com</t>
+        </is>
+      </c>
+      <c r="I640" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M640" s="9" t="inlineStr">
+        <is>
+          <t>https://bbec.ac.in/contact/</t>
+        </is>
+      </c>
+      <c r="N640" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O640" s="9" t="n"/>
+    </row>
+    <row r="641">
+      <c r="A641" s="9" t="n">
+        <v>640</v>
+      </c>
+      <c r="B641" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C641" s="9" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D641" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E641" s="9" t="inlineStr">
+        <is>
+          <t>Government Engineering College Buxar</t>
+        </is>
+      </c>
+      <c r="F641" s="9" t="inlineStr"/>
+      <c r="G641" s="9" t="inlineStr"/>
+      <c r="H641" s="9" t="inlineStr">
+        <is>
+          <t>info@gecbuxar.ac.in</t>
+        </is>
+      </c>
+      <c r="I641" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M641" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gecbuxar.ac.in/</t>
+        </is>
+      </c>
+      <c r="N641" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O641" s="9" t="n"/>
+    </row>
+    <row r="642">
+      <c r="A642" s="9" t="n">
+        <v>641</v>
+      </c>
+      <c r="B642" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C642" s="9" t="inlineStr">
+        <is>
+          <t>Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="D642" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E642" s="9" t="inlineStr">
+        <is>
+          <t>Rungta College of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="F642" s="9" t="inlineStr"/>
+      <c r="G642" s="9" t="inlineStr"/>
+      <c r="H642" s="9" t="inlineStr">
+        <is>
+          <t>info@rungta.ac.in</t>
+        </is>
+      </c>
+      <c r="I642" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M642" s="9" t="inlineStr">
+        <is>
+          <t>https://rcet.rungta.ac.in/rungta-group-contact.php</t>
+        </is>
+      </c>
+      <c r="N642" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O642" s="9" t="n"/>
+    </row>
+    <row r="643">
+      <c r="A643" s="9" t="n">
+        <v>642</v>
+      </c>
+      <c r="B643" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C643" s="9" t="inlineStr">
+        <is>
+          <t>Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="D643" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E643" s="9" t="inlineStr">
+        <is>
+          <t>Shri Shankaracharya Technical Campus</t>
+        </is>
+      </c>
+      <c r="F643" s="9" t="inlineStr"/>
+      <c r="G643" s="9" t="inlineStr"/>
+      <c r="H643" s="9" t="inlineStr">
+        <is>
+          <t>info@sstc.com</t>
+        </is>
+      </c>
+      <c r="I643" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M643" s="9" t="inlineStr">
+        <is>
+          <t>https://sstc.ac.in/contact-us/</t>
+        </is>
+      </c>
+      <c r="N643" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O643" s="9" t="n"/>
+    </row>
+    <row r="644">
+      <c r="A644" s="9" t="n">
+        <v>643</v>
+      </c>
+      <c r="B644" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C644" s="9" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D644" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E644" s="9" t="inlineStr">
+        <is>
+          <t>Jamia Hamdard</t>
+        </is>
+      </c>
+      <c r="F644" s="9" t="inlineStr"/>
+      <c r="G644" s="9" t="inlineStr"/>
+      <c r="H644" s="9" t="inlineStr">
+        <is>
+          <t>registrar@jamiahamdard.ac.in</t>
+        </is>
+      </c>
+      <c r="I644" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M644" s="9" t="inlineStr">
+        <is>
+          <t>https://www.jamiahamdard.ac.in/</t>
+        </is>
+      </c>
+      <c r="N644" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O644" s="9" t="n"/>
+    </row>
+    <row r="645">
+      <c r="A645" s="9" t="n">
+        <v>644</v>
+      </c>
+      <c r="B645" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C645" s="9" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="D645" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E645" s="9" t="inlineStr">
+        <is>
+          <t>Agnel Institute of Technology and Design</t>
+        </is>
+      </c>
+      <c r="F645" s="9" t="inlineStr"/>
+      <c r="G645" s="9" t="inlineStr"/>
+      <c r="H645" s="9" t="inlineStr">
+        <is>
+          <t>admissions@aiemgoa.ac.in</t>
+        </is>
+      </c>
+      <c r="I645" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M645" s="9" t="inlineStr">
+        <is>
+          <t>https://aiemgoa.ac.in/</t>
+        </is>
+      </c>
+      <c r="N645" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O645" s="9" t="n"/>
+    </row>
+    <row r="646">
+      <c r="A646" s="9" t="n">
+        <v>645</v>
+      </c>
+      <c r="B646" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C646" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D646" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E646" s="9" t="inlineStr">
+        <is>
+          <t>Gurunanak Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F646" s="9" t="inlineStr"/>
+      <c r="G646" s="9" t="inlineStr"/>
+      <c r="H646" s="9" t="inlineStr">
+        <is>
+          <t>info.gnit@jisgroup.org</t>
+        </is>
+      </c>
+      <c r="I646" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M646" s="9" t="inlineStr">
+        <is>
+          <t>https://gnit.ac.in/contact</t>
+        </is>
+      </c>
+      <c r="N646" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O646" s="9" t="n"/>
+    </row>
+    <row r="647">
+      <c r="A647" s="9" t="n">
+        <v>646</v>
+      </c>
+      <c r="B647" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C647" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D647" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E647" s="9" t="inlineStr">
+        <is>
+          <t>Netaji Subhash Engineering College</t>
+        </is>
+      </c>
+      <c r="F647" s="9" t="inlineStr"/>
+      <c r="G647" s="9" t="inlineStr"/>
+      <c r="H647" s="9" t="inlineStr">
+        <is>
+          <t>info@nsec.ac.in</t>
+        </is>
+      </c>
+      <c r="I647" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M647" s="9" t="inlineStr">
+        <is>
+          <t>https://www.nsec.ac.in/page.php?id=593</t>
+        </is>
+      </c>
+      <c r="N647" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O647" s="9" t="n"/>
+    </row>
+    <row r="648">
+      <c r="A648" s="9" t="n">
+        <v>647</v>
+      </c>
+      <c r="B648" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C648" s="9" t="inlineStr">
+        <is>
+          <t>Uttarakhand</t>
+        </is>
+      </c>
+      <c r="D648" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E648" s="9" t="inlineStr">
+        <is>
+          <t>Beehive College of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="F648" s="9" t="inlineStr"/>
+      <c r="G648" s="9" t="inlineStr"/>
+      <c r="H648" s="9" t="inlineStr">
+        <is>
+          <t>contact@beehivecollege.com</t>
+        </is>
+      </c>
+      <c r="I648" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M648" s="9" t="inlineStr">
+        <is>
+          <t>https://bcmt.beehivecollege.com/</t>
+        </is>
+      </c>
+      <c r="N648" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O648" s="9" t="n"/>
+    </row>
+    <row r="649">
+      <c r="A649" s="9" t="n">
+        <v>648</v>
+      </c>
+      <c r="B649" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C649" s="9" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D649" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E649" s="9" t="inlineStr">
+        <is>
+          <t>Sree Dattha Institute of Engineering and Science</t>
+        </is>
+      </c>
+      <c r="F649" s="9" t="inlineStr"/>
+      <c r="G649" s="9" t="inlineStr"/>
+      <c r="H649" s="9" t="inlineStr">
+        <is>
+          <t>info@sreedattha.ac.in</t>
+        </is>
+      </c>
+      <c r="I649" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M649" s="9" t="inlineStr">
+        <is>
+          <t>https://www.sreedattha.ac.in/sdes/</t>
+        </is>
+      </c>
+      <c r="N649" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O649" s="9" t="n"/>
+    </row>
+    <row r="650">
+      <c r="A650" s="9" t="n">
+        <v>649</v>
+      </c>
+      <c r="B650" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C650" s="9" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="D650" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E650" s="9" t="inlineStr">
+        <is>
+          <t>MBM University, Jodhpur</t>
+        </is>
+      </c>
+      <c r="F650" s="9" t="inlineStr"/>
+      <c r="G650" s="9" t="inlineStr"/>
+      <c r="H650" s="9" t="inlineStr">
+        <is>
+          <t>webadmin@mbm.ac.in</t>
+        </is>
+      </c>
+      <c r="I650" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M650" s="9" t="inlineStr">
+        <is>
+          <t>https://mbm.ac.in/</t>
+        </is>
+      </c>
+      <c r="N650" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O650" s="9" t="n"/>
+    </row>
+    <row r="651">
+      <c r="A651" s="9" t="n">
+        <v>650</v>
+      </c>
+      <c r="B651" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C651" s="9" t="inlineStr">
+        <is>
+          <t>Puducherry</t>
+        </is>
+      </c>
+      <c r="D651" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E651" s="9" t="inlineStr">
+        <is>
+          <t>Manakula Vinayagar Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F651" s="9" t="inlineStr"/>
+      <c r="G651" s="9" t="inlineStr"/>
+      <c r="H651" s="9" t="inlineStr">
+        <is>
+          <t>admin@mvit.edu.in</t>
+        </is>
+      </c>
+      <c r="I651" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M651" s="9" t="inlineStr">
+        <is>
+          <t>https://www.mvit.edu.in/</t>
+        </is>
+      </c>
+      <c r="N651" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O651" s="9" t="n"/>
+    </row>
+    <row r="652">
+      <c r="A652" s="9" t="n">
+        <v>651</v>
+      </c>
+      <c r="B652" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C652" s="9" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="D652" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E652" s="9" t="inlineStr">
+        <is>
+          <t>St. Vincent Pallotti College of Engg. &amp; Technology, Nagpur</t>
+        </is>
+      </c>
+      <c r="F652" s="9" t="inlineStr"/>
+      <c r="G652" s="9" t="inlineStr"/>
+      <c r="H652" s="9" t="inlineStr">
+        <is>
+          <t>info@stvincentngp.edu.in</t>
+        </is>
+      </c>
+      <c r="I652" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M652" s="9" t="inlineStr">
+        <is>
+          <t>https://stvincentngp.edu.in/</t>
+        </is>
+      </c>
+      <c r="N652" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O652" s="9" t="n"/>
+    </row>
+    <row r="653">
+      <c r="A653" s="9" t="n">
+        <v>652</v>
+      </c>
+      <c r="B653" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C653" s="9" t="inlineStr">
+        <is>
+          <t>Kerala</t>
+        </is>
+      </c>
+      <c r="D653" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E653" s="9" t="inlineStr">
+        <is>
+          <t>Providence College of Engineering</t>
+        </is>
+      </c>
+      <c r="F653" s="9" t="inlineStr"/>
+      <c r="G653" s="9" t="inlineStr"/>
+      <c r="H653" s="9" t="inlineStr">
+        <is>
+          <t>admissions@providence.edu.in</t>
+        </is>
+      </c>
+      <c r="I653" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M653" s="9" t="inlineStr">
+        <is>
+          <t>https://www.providence.edu.in/</t>
+        </is>
+      </c>
+      <c r="N653" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O653" s="9" t="n"/>
+    </row>
+    <row r="654">
+      <c r="A654" s="9" t="n">
+        <v>653</v>
+      </c>
+      <c r="B654" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C654" s="9" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D654" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E654" s="9" t="inlineStr">
+        <is>
+          <t>Rajarajeswari College of Engineering</t>
+        </is>
+      </c>
+      <c r="F654" s="9" t="inlineStr"/>
+      <c r="G654" s="9" t="inlineStr"/>
+      <c r="H654" s="9" t="inlineStr">
+        <is>
+          <t>admission@rrce.org</t>
+        </is>
+      </c>
+      <c r="I654" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M654" s="9" t="inlineStr">
+        <is>
+          <t>https://www.rrce.org/</t>
+        </is>
+      </c>
+      <c r="N654" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O654" s="9" t="n"/>
+    </row>
+    <row r="655">
+      <c r="A655" s="9" t="n">
+        <v>654</v>
+      </c>
+      <c r="B655" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C655" s="9" t="inlineStr">
+        <is>
+          <t>Jharkhand</t>
+        </is>
+      </c>
+      <c r="D655" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E655" s="9" t="inlineStr">
+        <is>
+          <t>B I T Sindri</t>
+        </is>
+      </c>
+      <c r="F655" s="9" t="inlineStr"/>
+      <c r="G655" s="9" t="inlineStr"/>
+      <c r="H655" s="9" t="inlineStr">
+        <is>
+          <t>admin@bitsindri.ac.in</t>
+        </is>
+      </c>
+      <c r="I655" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M655" s="9" t="inlineStr">
+        <is>
+          <t>https://bitsindri.ac.in/</t>
+        </is>
+      </c>
+      <c r="N655" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O655" s="9" t="n"/>
+    </row>
+    <row r="656">
+      <c r="A656" s="9" t="n">
+        <v>655</v>
+      </c>
+      <c r="B656" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C656" s="9" t="inlineStr">
+        <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="D656" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E656" s="9" t="inlineStr">
+        <is>
+          <t>Jorhat Engineering College</t>
+        </is>
+      </c>
+      <c r="F656" s="9" t="inlineStr"/>
+      <c r="G656" s="9" t="inlineStr"/>
+      <c r="H656" s="9" t="inlineStr">
+        <is>
+          <t>studentbranchjec@jecassam.ac.in</t>
+        </is>
+      </c>
+      <c r="I656" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M656" s="9" t="inlineStr">
+        <is>
+          <t>https://jecassam.ac.in/contact-us/</t>
+        </is>
+      </c>
+      <c r="N656" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O656" s="9" t="n"/>
+    </row>
+    <row r="657">
+      <c r="A657" s="9" t="n">
+        <v>656</v>
+      </c>
+      <c r="B657" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C657" s="9" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D657" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E657" s="9" t="inlineStr">
+        <is>
+          <t>Mother's Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F657" s="9" t="inlineStr"/>
+      <c r="G657" s="9" t="inlineStr"/>
+      <c r="H657" s="9" t="inlineStr">
+        <is>
+          <t>mitbihta@gmail.com</t>
+        </is>
+      </c>
+      <c r="I657" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M657" s="9" t="inlineStr">
+        <is>
+          <t>https://www.mitbihta.org/about-us/</t>
+        </is>
+      </c>
+      <c r="N657" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O657" s="9" t="n"/>
+    </row>
+    <row r="658">
+      <c r="A658" s="9" t="n">
+        <v>657</v>
+      </c>
+      <c r="B658" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C658" s="9" t="inlineStr">
+        <is>
+          <t>Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="D658" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E658" s="9" t="inlineStr">
+        <is>
+          <t>Chouksey Engineering College</t>
+        </is>
+      </c>
+      <c r="F658" s="9" t="inlineStr"/>
+      <c r="G658" s="9" t="inlineStr"/>
+      <c r="H658" s="9" t="inlineStr">
+        <is>
+          <t>info@cecbilaspur.ac.in</t>
+        </is>
+      </c>
+      <c r="I658" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M658" s="9" t="inlineStr">
+        <is>
+          <t>https://cecbilaspur.ac.in/</t>
+        </is>
+      </c>
+      <c r="N658" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O658" s="9" t="n"/>
+    </row>
+    <row r="659">
+      <c r="A659" s="9" t="n">
+        <v>658</v>
+      </c>
+      <c r="B659" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C659" s="9" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D659" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E659" s="9" t="inlineStr">
+        <is>
+          <t>DSEU Okhla-II Campus</t>
+        </is>
+      </c>
+      <c r="F659" s="9" t="inlineStr"/>
+      <c r="G659" s="9" t="inlineStr"/>
+      <c r="H659" s="9" t="inlineStr">
+        <is>
+          <t>helpdesk-admission@dseu.ac.in</t>
+        </is>
+      </c>
+      <c r="I659" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M659" s="9" t="inlineStr">
+        <is>
+          <t>https://dseu.ac.in/okhla-ii/</t>
+        </is>
+      </c>
+      <c r="N659" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O659" s="9" t="n"/>
+    </row>
+    <row r="660">
+      <c r="A660" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="B660" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C660" s="9" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="D660" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E660" s="9" t="inlineStr">
+        <is>
+          <t>Goa College of Engineering</t>
+        </is>
+      </c>
+      <c r="F660" s="9" t="inlineStr"/>
+      <c r="G660" s="9" t="inlineStr"/>
+      <c r="H660" s="9" t="inlineStr">
+        <is>
+          <t>ppl@gec.ac.in</t>
+        </is>
+      </c>
+      <c r="I660" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M660" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gec.ac.in/DisplayPage.aspx?page=co</t>
+        </is>
+      </c>
+      <c r="N660" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O660" s="9" t="n"/>
+    </row>
+    <row r="661">
+      <c r="A661" s="9" t="n">
+        <v>660</v>
+      </c>
+      <c r="B661" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C661" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D661" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E661" s="9" t="inlineStr">
+        <is>
+          <t>Govt. College of Engineering and Textile Technology, Berhampore</t>
+        </is>
+      </c>
+      <c r="F661" s="9" t="inlineStr"/>
+      <c r="G661" s="9" t="inlineStr"/>
+      <c r="H661" s="9" t="inlineStr">
+        <is>
+          <t>registrar@gcettb.ac.in</t>
+        </is>
+      </c>
+      <c r="I661" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M661" s="9" t="inlineStr">
+        <is>
+          <t>https://wbjeeb.in/assets/ALPG/GEC/GCETTB.pdf</t>
+        </is>
+      </c>
+      <c r="N661" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O661" s="9" t="n"/>
+    </row>
+    <row r="662">
+      <c r="A662" s="9" t="n">
+        <v>661</v>
+      </c>
+      <c r="B662" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C662" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D662" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E662" s="9" t="inlineStr">
+        <is>
+          <t>Techno Main Salt Lake</t>
+        </is>
+      </c>
+      <c r="F662" s="9" t="inlineStr"/>
+      <c r="G662" s="9" t="inlineStr"/>
+      <c r="H662" s="9" t="inlineStr">
+        <is>
+          <t>info@ticollege.ac.in</t>
+        </is>
+      </c>
+      <c r="I662" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M662" s="9" t="inlineStr">
+        <is>
+          <t>https://www.technomainsaltlake.ticollege.ac.in/index1.php?id=30</t>
+        </is>
+      </c>
+      <c r="N662" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O662" s="9" t="n"/>
+    </row>
+    <row r="663">
+      <c r="A663" s="9" t="n">
+        <v>662</v>
+      </c>
+      <c r="B663" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C663" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D663" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E663" s="9" t="inlineStr">
+        <is>
+          <t>Sister Nivedita University</t>
+        </is>
+      </c>
+      <c r="F663" s="9" t="inlineStr"/>
+      <c r="G663" s="9" t="inlineStr"/>
+      <c r="H663" s="9" t="inlineStr">
+        <is>
+          <t>support@snuniv.ac.in</t>
+        </is>
+      </c>
+      <c r="I663" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M663" s="9" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SisterNiveditaUniversity</t>
+        </is>
+      </c>
+      <c r="N663" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O663" s="9" t="n"/>
+    </row>
+    <row r="664">
+      <c r="A664" s="9" t="n">
+        <v>663</v>
+      </c>
+      <c r="B664" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C664" s="9" t="inlineStr">
+        <is>
+          <t>Tripura</t>
+        </is>
+      </c>
+      <c r="D664" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E664" s="9" t="inlineStr">
+        <is>
+          <t>Techno College of Engineering Agartala</t>
+        </is>
+      </c>
+      <c r="F664" s="9" t="inlineStr"/>
+      <c r="G664" s="9" t="inlineStr"/>
+      <c r="H664" s="9" t="inlineStr">
+        <is>
+          <t>info@tiaedu.org</t>
+        </is>
+      </c>
+      <c r="I664" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M664" s="9" t="inlineStr">
+        <is>
+          <t>https://tiaedu.org/</t>
+        </is>
+      </c>
+      <c r="N664" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O664" s="9" t="n"/>
+    </row>
+    <row r="665">
+      <c r="A665" s="9" t="n">
+        <v>664</v>
+      </c>
+      <c r="B665" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C665" s="9" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D665" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E665" s="9" t="inlineStr">
+        <is>
+          <t>Keshav Memorial Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F665" s="9" t="inlineStr"/>
+      <c r="G665" s="9" t="inlineStr"/>
+      <c r="H665" s="9" t="inlineStr">
+        <is>
+          <t>info@kmit.in</t>
+        </is>
+      </c>
+      <c r="I665" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M665" s="9" t="inlineStr">
+        <is>
+          <t>https://kmit.in/</t>
+        </is>
+      </c>
+      <c r="N665" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O665" s="9" t="n"/>
+    </row>
+    <row r="666">
+      <c r="A666" s="9" t="n">
+        <v>665</v>
+      </c>
+      <c r="B666" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C666" s="9" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="D666" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E666" s="9" t="inlineStr">
+        <is>
+          <t>Guru Nanak Dev Engineering College</t>
+        </is>
+      </c>
+      <c r="F666" s="9" t="inlineStr"/>
+      <c r="G666" s="9" t="inlineStr"/>
+      <c r="H666" s="9" t="inlineStr">
+        <is>
+          <t>principal@gndec.ac.in</t>
+        </is>
+      </c>
+      <c r="I666" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M666" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gndec.ac.in/?q=node%2F53</t>
+        </is>
+      </c>
+      <c r="N666" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O666" s="9" t="n"/>
+    </row>
+    <row r="667">
+      <c r="A667" s="9" t="n">
+        <v>666</v>
+      </c>
+      <c r="B667" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C667" s="9" t="inlineStr">
+        <is>
+          <t>Puducherry</t>
+        </is>
+      </c>
+      <c r="D667" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E667" s="9" t="inlineStr">
+        <is>
+          <t>Perunthanalaivar Kamarajar Institute of Engineering and Technology</t>
+        </is>
+      </c>
+      <c r="F667" s="9" t="inlineStr"/>
+      <c r="G667" s="9" t="inlineStr"/>
+      <c r="H667" s="9" t="inlineStr">
+        <is>
+          <t>principal@pkiet.edu.in</t>
+        </is>
+      </c>
+      <c r="I667" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M667" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pkiet.edu.in/p/contact-us.html</t>
+        </is>
+      </c>
+      <c r="N667" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O667" s="9" t="n"/>
+    </row>
+    <row r="668">
+      <c r="A668" s="9" t="n">
+        <v>667</v>
+      </c>
+      <c r="B668" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C668" s="9" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D668" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E668" s="9" t="inlineStr">
+        <is>
+          <t>Bapuji Institute of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="F668" s="9" t="inlineStr"/>
+      <c r="G668" s="9" t="inlineStr"/>
+      <c r="H668" s="9" t="inlineStr">
+        <is>
+          <t>principal@bietdvg.edu</t>
+        </is>
+      </c>
+      <c r="I668" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M668" s="9" t="inlineStr">
+        <is>
+          <t>https://www.bietdvg.edu/admission/contact</t>
+        </is>
+      </c>
+      <c r="N668" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O668" s="9" t="n"/>
+    </row>
+    <row r="669">
+      <c r="A669" s="9" t="n">
+        <v>668</v>
+      </c>
+      <c r="B669" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C669" s="9" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="D669" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E669" s="9" t="inlineStr">
+        <is>
+          <t>Chalapathi Institute of Engineering and Technology</t>
+        </is>
+      </c>
+      <c r="F669" s="9" t="inlineStr"/>
+      <c r="G669" s="9" t="inlineStr"/>
+      <c r="H669" s="9" t="inlineStr">
+        <is>
+          <t>chalapathiengtech@yahoo.com</t>
+        </is>
+      </c>
+      <c r="I669" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M669" s="9" t="inlineStr">
+        <is>
+          <t>https://chalapathiengg.ac.in/contact/</t>
+        </is>
+      </c>
+      <c r="N669" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O669" s="9" t="n"/>
+    </row>
+    <row r="670">
+      <c r="A670" s="9" t="n">
+        <v>669</v>
+      </c>
+      <c r="B670" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C670" s="9" t="inlineStr">
+        <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="D670" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E670" s="9" t="inlineStr">
+        <is>
+          <t>Dhemaji Engineering College</t>
+        </is>
+      </c>
+      <c r="F670" s="9" t="inlineStr"/>
+      <c r="G670" s="9" t="inlineStr"/>
+      <c r="H670" s="9" t="inlineStr">
+        <is>
+          <t>office@dec.ac.in</t>
+        </is>
+      </c>
+      <c r="I670" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M670" s="9" t="inlineStr">
+        <is>
+          <t>https://dec.ac.in/</t>
+        </is>
+      </c>
+      <c r="N670" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O670" s="9" t="n"/>
+    </row>
+    <row r="671">
+      <c r="A671" s="9" t="n">
+        <v>670</v>
+      </c>
+      <c r="B671" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C671" s="9" t="inlineStr">
+        <is>
+          <t>Dadra and Nagar Haveli and Daman and Diu</t>
+        </is>
+      </c>
+      <c r="D671" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E671" s="9" t="inlineStr">
+        <is>
+          <t>Government Engineering College Daman</t>
+        </is>
+      </c>
+      <c r="F671" s="9" t="inlineStr"/>
+      <c r="G671" s="9" t="inlineStr"/>
+      <c r="H671" s="9" t="inlineStr">
+        <is>
+          <t>gecdaman@gmail.com</t>
+        </is>
+      </c>
+      <c r="I671" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M671" s="9" t="inlineStr">
+        <is>
+          <t>https://www.govtenggcollegedaman.org.in/contactus.html</t>
+        </is>
+      </c>
+      <c r="N671" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O671" s="9" t="n"/>
+    </row>
+    <row r="672">
+      <c r="A672" s="9" t="n">
+        <v>671</v>
+      </c>
+      <c r="B672" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C672" s="9" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D672" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E672" s="9" t="inlineStr">
+        <is>
+          <t>Guru Tegh Bahadur Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F672" s="9" t="inlineStr"/>
+      <c r="G672" s="9" t="inlineStr"/>
+      <c r="H672" s="9" t="inlineStr">
+        <is>
+          <t>contactus@gtbit.ac.in</t>
+        </is>
+      </c>
+      <c r="I672" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M672" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gtbit.ac.in/about-us</t>
+        </is>
+      </c>
+      <c r="N672" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O672" s="9" t="n"/>
+    </row>
+    <row r="673">
+      <c r="A673" s="9" t="n">
+        <v>672</v>
+      </c>
+      <c r="B673" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C673" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D673" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E673" s="9" t="inlineStr">
+        <is>
+          <t>Future Institute of Engineering and Management</t>
+        </is>
+      </c>
+      <c r="F673" s="9" t="inlineStr"/>
+      <c r="G673" s="9" t="inlineStr"/>
+      <c r="H673" s="9" t="inlineStr">
+        <is>
+          <t>fiem@teamfutel.in</t>
+        </is>
+      </c>
+      <c r="I673" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M673" s="9" t="inlineStr">
+        <is>
+          <t>https://www.futureeducation.in/fiem/contact.php</t>
+        </is>
+      </c>
+      <c r="N673" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O673" s="9" t="n"/>
+    </row>
+    <row r="674">
+      <c r="A674" s="9" t="n">
+        <v>673</v>
+      </c>
+      <c r="B674" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C674" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D674" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E674" s="9" t="inlineStr">
+        <is>
+          <t>Institute of Science and Technology (Kolkata)</t>
+        </is>
+      </c>
+      <c r="F674" s="9" t="inlineStr"/>
+      <c r="G674" s="9" t="inlineStr"/>
+      <c r="H674" s="9" t="inlineStr">
+        <is>
+          <t>chairman@istonline.org.in</t>
+        </is>
+      </c>
+      <c r="I674" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M674" s="9" t="inlineStr">
+        <is>
+          <t>https://www.istonline.org.in/contact-us</t>
+        </is>
+      </c>
+      <c r="N674" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O674" s="9" t="n"/>
+    </row>
+    <row r="675">
+      <c r="A675" s="9" t="n">
+        <v>674</v>
+      </c>
+      <c r="B675" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C675" s="9" t="inlineStr">
+        <is>
+          <t>Uttarakhand</t>
+        </is>
+      </c>
+      <c r="D675" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E675" s="9" t="inlineStr">
+        <is>
+          <t>Graphic Era Deemed to be University</t>
+        </is>
+      </c>
+      <c r="F675" s="9" t="inlineStr"/>
+      <c r="G675" s="9" t="inlineStr"/>
+      <c r="H675" s="9" t="inlineStr">
+        <is>
+          <t>admissions@geu.ac.in</t>
+        </is>
+      </c>
+      <c r="I675" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M675" s="9" t="inlineStr">
+        <is>
+          <t>https://geu.ac.in/contact-us</t>
+        </is>
+      </c>
+      <c r="N675" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O675" s="9" t="n"/>
+    </row>
+    <row r="676">
+      <c r="A676" s="9" t="n">
+        <v>675</v>
+      </c>
+      <c r="B676" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C676" s="9" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D676" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E676" s="9" t="inlineStr">
+        <is>
+          <t>Malla Reddy Engineering College for Women</t>
+        </is>
+      </c>
+      <c r="F676" s="9" t="inlineStr"/>
+      <c r="G676" s="9" t="inlineStr"/>
+      <c r="H676" s="9" t="inlineStr">
+        <is>
+          <t>principal@mrcew.ac.in</t>
+        </is>
+      </c>
+      <c r="I676" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M676" s="9" t="inlineStr">
+        <is>
+          <t>https://mrcew.ac.in/Contacts.aspx</t>
+        </is>
+      </c>
+      <c r="N676" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O676" s="9" t="n"/>
+    </row>
+    <row r="677">
+      <c r="A677" s="9" t="n">
+        <v>676</v>
+      </c>
+      <c r="B677" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C677" s="9" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="D677" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E677" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College Bikaner</t>
+        </is>
+      </c>
+      <c r="F677" s="9" t="inlineStr"/>
+      <c r="G677" s="9" t="inlineStr"/>
+      <c r="H677" s="9" t="inlineStr">
+        <is>
+          <t>principal@ecb.ac.in</t>
+        </is>
+      </c>
+      <c r="I677" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M677" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ecb.ac.in/contact.php</t>
+        </is>
+      </c>
+      <c r="N677" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O677" s="9" t="n"/>
+    </row>
+    <row r="678">
+      <c r="A678" s="9" t="n">
+        <v>677</v>
+      </c>
+      <c r="B678" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C678" s="9" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="D678" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E678" s="9" t="inlineStr">
+        <is>
+          <t>Faculty of Dairy Technology, Jodhpur</t>
+        </is>
+      </c>
+      <c r="F678" s="9" t="inlineStr"/>
+      <c r="G678" s="9" t="inlineStr"/>
+      <c r="H678" s="9" t="inlineStr">
+        <is>
+          <t>facultydairy.auj@gmail.com</t>
+        </is>
+      </c>
+      <c r="I678" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M678" s="9" t="inlineStr">
+        <is>
+          <t>https://www.aujodhpur.ac.in/college.php?office=24</t>
+        </is>
+      </c>
+      <c r="N678" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O678" s="9" t="n"/>
+    </row>
+    <row r="679">
+      <c r="A679" s="9" t="n">
+        <v>678</v>
+      </c>
+      <c r="B679" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C679" s="9" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="D679" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E679" s="9" t="inlineStr">
+        <is>
+          <t>Baba Farid College of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="F679" s="9" t="inlineStr"/>
+      <c r="G679" s="9" t="inlineStr"/>
+      <c r="H679" s="9" t="inlineStr">
+        <is>
+          <t>principalbfcet@babafaridgroup.com</t>
+        </is>
+      </c>
+      <c r="I679" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M679" s="9" t="inlineStr">
+        <is>
+          <t>https://www.bfcet.com/contact/</t>
+        </is>
+      </c>
+      <c r="N679" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O679" s="9" t="n"/>
+    </row>
+    <row r="680">
+      <c r="A680" s="9" t="n">
+        <v>679</v>
+      </c>
+      <c r="B680" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C680" s="9" t="inlineStr">
+        <is>
+          <t>Puducherry</t>
+        </is>
+      </c>
+      <c r="D680" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E680" s="9" t="inlineStr">
+        <is>
+          <t>Rajiv Gandhi College of Engineering and Technology, Puducherry</t>
+        </is>
+      </c>
+      <c r="F680" s="9" t="inlineStr"/>
+      <c r="G680" s="9" t="inlineStr"/>
+      <c r="H680" s="9" t="inlineStr">
+        <is>
+          <t>info@rgcetpdy.ac.in</t>
+        </is>
+      </c>
+      <c r="I680" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M680" s="9" t="inlineStr">
+        <is>
+          <t>https://www.rgcet.edu.in/contact.php</t>
+        </is>
+      </c>
+      <c r="N680" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O680" s="9" t="n"/>
+    </row>
+    <row r="681">
+      <c r="A681" s="9" t="n">
+        <v>680</v>
+      </c>
+      <c r="B681" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C681" s="9" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="D681" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E681" s="9" t="inlineStr">
+        <is>
+          <t>Odisha University of Technology and Research</t>
+        </is>
+      </c>
+      <c r="F681" s="9" t="inlineStr"/>
+      <c r="G681" s="9" t="inlineStr"/>
+      <c r="H681" s="9" t="inlineStr">
+        <is>
+          <t>info@outr.ac.in</t>
+        </is>
+      </c>
+      <c r="I681" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M681" s="9" t="inlineStr">
+        <is>
+          <t>https://www.outr.ac.in/contact-us</t>
+        </is>
+      </c>
+      <c r="N681" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O681" s="9" t="n"/>
+    </row>
+    <row r="682">
+      <c r="A682" s="9" t="n">
+        <v>681</v>
+      </c>
+      <c r="B682" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C682" s="9" t="inlineStr">
+        <is>
+          <t>Kerala</t>
+        </is>
+      </c>
+      <c r="D682" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E682" s="9" t="inlineStr">
+        <is>
+          <t>University College of Engineering, Kariavattom</t>
+        </is>
+      </c>
+      <c r="F682" s="9" t="inlineStr"/>
+      <c r="G682" s="9" t="inlineStr"/>
+      <c r="H682" s="9" t="inlineStr">
+        <is>
+          <t>ucekprincipal@gmail.com</t>
+        </is>
+      </c>
+      <c r="I682" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M682" s="9" t="inlineStr">
+        <is>
+          <t>https://uck.ac.in/about/contact</t>
+        </is>
+      </c>
+      <c r="N682" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O682" s="9" t="n"/>
+    </row>
+    <row r="683">
+      <c r="A683" s="9" t="n">
+        <v>682</v>
+      </c>
+      <c r="B683" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C683" s="9" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D683" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E683" s="9" t="inlineStr">
+        <is>
+          <t>Dayananda Sagar Academy of Technology &amp; Management Technical Campus</t>
+        </is>
+      </c>
+      <c r="F683" s="9" t="inlineStr"/>
+      <c r="G683" s="9" t="inlineStr"/>
+      <c r="H683" s="9" t="inlineStr">
+        <is>
+          <t>admissions@dsatm.edu.in</t>
+        </is>
+      </c>
+      <c r="I683" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M683" s="9" t="inlineStr">
+        <is>
+          <t>https://dsatm.edu.in/contact-us</t>
+        </is>
+      </c>
+      <c r="N683" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O683" s="9" t="n"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O207"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -39682,7 +43618,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>80</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="10">

--- a/data/Incubation_Outreach_Tracker.xlsx
+++ b/data/Incubation_Outreach_Tracker.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q683"/>
+  <dimension ref="A1:Q743"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="9" min="1" max="1"/>
@@ -43549,6 +43549,2826 @@
       </c>
       <c r="O683" s="9" t="n"/>
     </row>
+    <row r="684">
+      <c r="A684" s="9" t="n">
+        <v>683</v>
+      </c>
+      <c r="B684" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C684" s="9" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="D684" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E684" s="9" t="inlineStr">
+        <is>
+          <t>Geethanjali Institute of Science and Technology</t>
+        </is>
+      </c>
+      <c r="F684" s="9" t="inlineStr"/>
+      <c r="G684" s="9" t="inlineStr"/>
+      <c r="H684" s="9" t="inlineStr">
+        <is>
+          <t>principal@gist.edu.in</t>
+        </is>
+      </c>
+      <c r="I684" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M684" s="9" t="inlineStr">
+        <is>
+          <t>https://gist.edu.in/gist/contact-us/</t>
+        </is>
+      </c>
+      <c r="N684" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="9" t="n">
+        <v>684</v>
+      </c>
+      <c r="B685" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C685" s="9" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="D685" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E685" s="9" t="inlineStr">
+        <is>
+          <t>Aditya Institute of Technology and Management</t>
+        </is>
+      </c>
+      <c r="F685" s="9" t="inlineStr"/>
+      <c r="G685" s="9" t="inlineStr"/>
+      <c r="H685" s="9" t="inlineStr">
+        <is>
+          <t>info@adityatekkali.edu.in</t>
+        </is>
+      </c>
+      <c r="I685" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M685" s="9" t="inlineStr">
+        <is>
+          <t>https://adityatekkali.edu.in/</t>
+        </is>
+      </c>
+      <c r="N685" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="9" t="n">
+        <v>685</v>
+      </c>
+      <c r="B686" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C686" s="9" t="inlineStr">
+        <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="D686" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E686" s="9" t="inlineStr">
+        <is>
+          <t>Golaghat Engineering College</t>
+        </is>
+      </c>
+      <c r="F686" s="9" t="inlineStr"/>
+      <c r="G686" s="9" t="inlineStr"/>
+      <c r="H686" s="9" t="inlineStr">
+        <is>
+          <t>info@gecassam.ac.in</t>
+        </is>
+      </c>
+      <c r="I686" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M686" s="9" t="inlineStr">
+        <is>
+          <t>https://gecassam.ac.in/</t>
+        </is>
+      </c>
+      <c r="N686" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="9" t="n">
+        <v>686</v>
+      </c>
+      <c r="B687" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C687" s="9" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D687" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E687" s="9" t="inlineStr">
+        <is>
+          <t>Jamia Millia Islamia</t>
+        </is>
+      </c>
+      <c r="F687" s="9" t="inlineStr"/>
+      <c r="G687" s="9" t="inlineStr"/>
+      <c r="H687" s="9" t="inlineStr">
+        <is>
+          <t>cit@jmi.ac.in</t>
+        </is>
+      </c>
+      <c r="I687" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M687" s="9" t="inlineStr">
+        <is>
+          <t>https://jmi.ac.in/Contactus/Contact-Us</t>
+        </is>
+      </c>
+      <c r="N687" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="9" t="n">
+        <v>687</v>
+      </c>
+      <c r="B688" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C688" s="9" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D688" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E688" s="9" t="inlineStr">
+        <is>
+          <t>Maharaja Surajmal Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F688" s="9" t="inlineStr"/>
+      <c r="G688" s="9" t="inlineStr"/>
+      <c r="H688" s="9" t="inlineStr">
+        <is>
+          <t>msitadmin@msit.in</t>
+        </is>
+      </c>
+      <c r="I688" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M688" s="9" t="inlineStr">
+        <is>
+          <t>https://www.msit.in/contact</t>
+        </is>
+      </c>
+      <c r="N688" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="9" t="n">
+        <v>688</v>
+      </c>
+      <c r="B689" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C689" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D689" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E689" s="9" t="inlineStr">
+        <is>
+          <t>University College of Science &amp; Technology, Calcutta University</t>
+        </is>
+      </c>
+      <c r="F689" s="9" t="inlineStr"/>
+      <c r="G689" s="9" t="inlineStr"/>
+      <c r="H689" s="9" t="inlineStr">
+        <is>
+          <t>cuadmissionbtech@gmail.com</t>
+        </is>
+      </c>
+      <c r="I689" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M689" s="9" t="inlineStr">
+        <is>
+          <t>https://www.caluniv-ucsta.net/contact</t>
+        </is>
+      </c>
+      <c r="N689" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="9" t="n">
+        <v>689</v>
+      </c>
+      <c r="B690" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C690" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D690" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E690" s="9" t="inlineStr">
+        <is>
+          <t>B. P. Poddar Institute of Management &amp; Technology</t>
+        </is>
+      </c>
+      <c r="F690" s="9" t="inlineStr"/>
+      <c r="G690" s="9" t="inlineStr"/>
+      <c r="H690" s="9" t="inlineStr">
+        <is>
+          <t>info@bppimt.ac.in</t>
+        </is>
+      </c>
+      <c r="I690" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M690" s="9" t="inlineStr">
+        <is>
+          <t>https://bppimt.ac.in/contact-us/</t>
+        </is>
+      </c>
+      <c r="N690" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="9" t="n">
+        <v>690</v>
+      </c>
+      <c r="B691" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C691" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D691" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E691" s="9" t="inlineStr">
+        <is>
+          <t>St. Thomas' College of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="F691" s="9" t="inlineStr"/>
+      <c r="G691" s="9" t="inlineStr"/>
+      <c r="H691" s="9" t="inlineStr">
+        <is>
+          <t>info@stcet.ac.in</t>
+        </is>
+      </c>
+      <c r="I691" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M691" s="9" t="inlineStr">
+        <is>
+          <t>https://stcet.ac.in/contact-us/</t>
+        </is>
+      </c>
+      <c r="N691" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="9" t="n">
+        <v>691</v>
+      </c>
+      <c r="B692" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C692" s="9" t="inlineStr">
+        <is>
+          <t>Uttarakhand</t>
+        </is>
+      </c>
+      <c r="D692" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E692" s="9" t="inlineStr">
+        <is>
+          <t>G.B. Pant Institute of Engineering and Technology</t>
+        </is>
+      </c>
+      <c r="F692" s="9" t="inlineStr"/>
+      <c r="G692" s="9" t="inlineStr"/>
+      <c r="H692" s="9" t="inlineStr">
+        <is>
+          <t>director@gbpiet.ac.in</t>
+        </is>
+      </c>
+      <c r="I692" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M692" s="9" t="inlineStr">
+        <is>
+          <t>https://gbpiet.ac.in/administration/office-of-the-director/</t>
+        </is>
+      </c>
+      <c r="N692" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="9" t="n">
+        <v>692</v>
+      </c>
+      <c r="B693" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C693" s="9" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D693" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E693" s="9" t="inlineStr">
+        <is>
+          <t>Mina Institute of Engineering Technology for Women</t>
+        </is>
+      </c>
+      <c r="F693" s="9" t="inlineStr"/>
+      <c r="G693" s="9" t="inlineStr"/>
+      <c r="H693" s="9" t="inlineStr">
+        <is>
+          <t>mietw2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="I693" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M693" s="9" t="inlineStr">
+        <is>
+          <t>https://minaenggcollege.ac.in/</t>
+        </is>
+      </c>
+      <c r="N693" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="9" t="n">
+        <v>693</v>
+      </c>
+      <c r="B694" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C694" s="9" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="D694" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E694" s="9" t="inlineStr">
+        <is>
+          <t>Annamalaiar College of Engineering</t>
+        </is>
+      </c>
+      <c r="F694" s="9" t="inlineStr"/>
+      <c r="G694" s="9" t="inlineStr"/>
+      <c r="H694" s="9" t="inlineStr">
+        <is>
+          <t>annamalaiarcoe@gmail.com</t>
+        </is>
+      </c>
+      <c r="I694" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M694" s="9" t="inlineStr">
+        <is>
+          <t>https://www.annamalaiarengg.com/contact-number/</t>
+        </is>
+      </c>
+      <c r="N694" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="9" t="n">
+        <v>694</v>
+      </c>
+      <c r="B695" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C695" s="9" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="D695" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E695" s="9" t="inlineStr">
+        <is>
+          <t>CIPET Jaipur (Central Institute of Petrochemicals Engineering and Technology)</t>
+        </is>
+      </c>
+      <c r="F695" s="9" t="inlineStr"/>
+      <c r="G695" s="9" t="inlineStr"/>
+      <c r="H695" s="9" t="inlineStr">
+        <is>
+          <t>cipetiptjaipur@cipet.gov.in</t>
+        </is>
+      </c>
+      <c r="I695" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M695" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cipet.gov.in/centres/cipet-jaipur2/contact-us.php</t>
+        </is>
+      </c>
+      <c r="N695" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="9" t="n">
+        <v>695</v>
+      </c>
+      <c r="B696" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C696" s="9" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="D696" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E696" s="9" t="inlineStr">
+        <is>
+          <t>Rajasthan Institute of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="F696" s="9" t="inlineStr"/>
+      <c r="G696" s="9" t="inlineStr"/>
+      <c r="H696" s="9" t="inlineStr">
+        <is>
+          <t>admissions@poornima.edu.in</t>
+        </is>
+      </c>
+      <c r="I696" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M696" s="9" t="inlineStr">
+        <is>
+          <t>https://poornima.edu.in/rajasthan-institute-of-engineering-technology/</t>
+        </is>
+      </c>
+      <c r="N696" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="9" t="n">
+        <v>696</v>
+      </c>
+      <c r="B697" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C697" s="9" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="D697" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E697" s="9" t="inlineStr">
+        <is>
+          <t>Global Group of Institutes</t>
+        </is>
+      </c>
+      <c r="F697" s="9" t="inlineStr"/>
+      <c r="G697" s="9" t="inlineStr"/>
+      <c r="H697" s="9" t="inlineStr">
+        <is>
+          <t>info@globalinstitutes.edu.in</t>
+        </is>
+      </c>
+      <c r="I697" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M697" s="9" t="inlineStr">
+        <is>
+          <t>https://www.globalinstitutes.edu.in/about/iqac/official-contact-details/</t>
+        </is>
+      </c>
+      <c r="N697" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="9" t="n">
+        <v>697</v>
+      </c>
+      <c r="B698" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C698" s="9" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="D698" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E698" s="9" t="inlineStr">
+        <is>
+          <t>Bhadrak Institute of Engineering &amp; Technology, Barapada, Bhadrak</t>
+        </is>
+      </c>
+      <c r="F698" s="9" t="inlineStr"/>
+      <c r="G698" s="9" t="inlineStr"/>
+      <c r="H698" s="9" t="inlineStr">
+        <is>
+          <t>info@bietbhadrak.ac.in</t>
+        </is>
+      </c>
+      <c r="I698" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M698" s="9" t="inlineStr">
+        <is>
+          <t>https://bietbhadrak.ac.in/ContactUs.php</t>
+        </is>
+      </c>
+      <c r="N698" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="9" t="n">
+        <v>698</v>
+      </c>
+      <c r="B699" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C699" s="9" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="D699" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E699" s="9" t="inlineStr">
+        <is>
+          <t>Trident Academy of Technology</t>
+        </is>
+      </c>
+      <c r="F699" s="9" t="inlineStr"/>
+      <c r="G699" s="9" t="inlineStr"/>
+      <c r="H699" s="9" t="inlineStr">
+        <is>
+          <t>info@tat.ac.in</t>
+        </is>
+      </c>
+      <c r="I699" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M699" s="9" t="inlineStr">
+        <is>
+          <t>https://tat.trident.ac.in/contact/</t>
+        </is>
+      </c>
+      <c r="N699" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="9" t="n">
+        <v>699</v>
+      </c>
+      <c r="B700" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C700" s="9" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="D700" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E700" s="9" t="inlineStr">
+        <is>
+          <t>Pillai HOC College of Engineering and Technology</t>
+        </is>
+      </c>
+      <c r="F700" s="9" t="inlineStr"/>
+      <c r="G700" s="9" t="inlineStr"/>
+      <c r="H700" s="9" t="inlineStr">
+        <is>
+          <t>principal.phcet@mes.ac.in</t>
+        </is>
+      </c>
+      <c r="I700" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M700" s="9" t="inlineStr">
+        <is>
+          <t>https://phcet.ac.in/about/contact-us/</t>
+        </is>
+      </c>
+      <c r="N700" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="9" t="n">
+        <v>700</v>
+      </c>
+      <c r="B701" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C701" s="9" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D701" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E701" s="9" t="inlineStr">
+        <is>
+          <t>Akshaya Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F701" s="9" t="inlineStr"/>
+      <c r="G701" s="9" t="inlineStr"/>
+      <c r="H701" s="9" t="inlineStr">
+        <is>
+          <t>principalakshayait@gmail.com</t>
+        </is>
+      </c>
+      <c r="I701" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M701" s="9" t="inlineStr">
+        <is>
+          <t>https://ait-tumkur.ac.in/contact-us/</t>
+        </is>
+      </c>
+      <c r="N701" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="9" t="n">
+        <v>701</v>
+      </c>
+      <c r="B702" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C702" s="9" t="inlineStr">
+        <is>
+          <t>Himachal Pradesh</t>
+        </is>
+      </c>
+      <c r="D702" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E702" s="9" t="inlineStr">
+        <is>
+          <t>University Institute of Technology, Himachal Pradesh University, Shimla</t>
+        </is>
+      </c>
+      <c r="F702" s="9" t="inlineStr"/>
+      <c r="G702" s="9" t="inlineStr"/>
+      <c r="H702" s="9" t="inlineStr">
+        <is>
+          <t>uiitofficehpu@gmail.com</t>
+        </is>
+      </c>
+      <c r="I702" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M702" s="9" t="inlineStr">
+        <is>
+          <t>http://www.hpuniv.ac.in/university-detail/uiit/contact-us</t>
+        </is>
+      </c>
+      <c r="N702" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="9" t="n">
+        <v>702</v>
+      </c>
+      <c r="B703" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C703" s="9" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="D703" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E703" s="9" t="inlineStr">
+        <is>
+          <t>Dronacharya College of Engineering</t>
+        </is>
+      </c>
+      <c r="F703" s="9" t="inlineStr"/>
+      <c r="G703" s="9" t="inlineStr"/>
+      <c r="H703" s="9" t="inlineStr">
+        <is>
+          <t>info@dronacharya.info</t>
+        </is>
+      </c>
+      <c r="I703" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M703" s="9" t="inlineStr">
+        <is>
+          <t>https://ggnindia.dronacharya.info/contact.aspx</t>
+        </is>
+      </c>
+      <c r="N703" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="9" t="n">
+        <v>703</v>
+      </c>
+      <c r="B704" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C704" s="9" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="D704" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E704" s="9" t="inlineStr">
+        <is>
+          <t>V.K.R., V.N.B. A.G.K. College of Engineering</t>
+        </is>
+      </c>
+      <c r="F704" s="9" t="inlineStr"/>
+      <c r="G704" s="9" t="inlineStr"/>
+      <c r="H704" s="9" t="inlineStr">
+        <is>
+          <t>vkrvnbengineering@gmail.com</t>
+        </is>
+      </c>
+      <c r="I704" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M704" s="9" t="inlineStr">
+        <is>
+          <t>https://vkrvnbcoe.org/contact/</t>
+        </is>
+      </c>
+      <c r="N704" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="9" t="n">
+        <v>704</v>
+      </c>
+      <c r="B705" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C705" s="9" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="D705" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E705" s="9" t="inlineStr">
+        <is>
+          <t>Rayalaseema University College of Engineering</t>
+        </is>
+      </c>
+      <c r="F705" s="9" t="inlineStr"/>
+      <c r="G705" s="9" t="inlineStr"/>
+      <c r="H705" s="9" t="inlineStr">
+        <is>
+          <t>rectt2023@ruce.ac.in</t>
+        </is>
+      </c>
+      <c r="I705" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M705" s="9" t="inlineStr">
+        <is>
+          <t>http://ruce.ac.in/official/contact-us.php</t>
+        </is>
+      </c>
+      <c r="N705" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="9" t="n">
+        <v>705</v>
+      </c>
+      <c r="B706" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C706" s="9" t="inlineStr">
+        <is>
+          <t>Chandigarh</t>
+        </is>
+      </c>
+      <c r="D706" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E706" s="9" t="inlineStr">
+        <is>
+          <t>Chandigarh College of Engineering and Technology</t>
+        </is>
+      </c>
+      <c r="F706" s="9" t="inlineStr"/>
+      <c r="G706" s="9" t="inlineStr"/>
+      <c r="H706" s="9" t="inlineStr">
+        <is>
+          <t>tpo@ccet.ac.in</t>
+        </is>
+      </c>
+      <c r="I706" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M706" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ccet.ac.in/tnp/contact-us.html</t>
+        </is>
+      </c>
+      <c r="N706" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="9" t="n">
+        <v>706</v>
+      </c>
+      <c r="B707" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C707" s="9" t="inlineStr">
+        <is>
+          <t>Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="D707" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E707" s="9" t="inlineStr">
+        <is>
+          <t>Kalinga University - Faculty of Technology</t>
+        </is>
+      </c>
+      <c r="F707" s="9" t="inlineStr"/>
+      <c r="G707" s="9" t="inlineStr"/>
+      <c r="H707" s="9" t="inlineStr">
+        <is>
+          <t>registrar@kalingauniversity.ac.in</t>
+        </is>
+      </c>
+      <c r="I707" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M707" s="9" t="inlineStr">
+        <is>
+          <t>https://kalingauniversity.ac.in/contact-us.php</t>
+        </is>
+      </c>
+      <c r="N707" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="9" t="n">
+        <v>707</v>
+      </c>
+      <c r="B708" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C708" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D708" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E708" s="9" t="inlineStr">
+        <is>
+          <t>University Institute of Technology, Burdwan</t>
+        </is>
+      </c>
+      <c r="F708" s="9" t="inlineStr"/>
+      <c r="G708" s="9" t="inlineStr"/>
+      <c r="H708" s="9" t="inlineStr">
+        <is>
+          <t>principal@uit.buruniv.ac.in</t>
+        </is>
+      </c>
+      <c r="I708" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M708" s="9" t="inlineStr">
+        <is>
+          <t>https://www.buruniv.ac.in/uit/contact.php</t>
+        </is>
+      </c>
+      <c r="N708" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="9" t="n">
+        <v>708</v>
+      </c>
+      <c r="B709" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C709" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D709" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E709" s="9" t="inlineStr">
+        <is>
+          <t>Camellia Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F709" s="9" t="inlineStr"/>
+      <c r="G709" s="9" t="inlineStr"/>
+      <c r="H709" s="9" t="inlineStr">
+        <is>
+          <t>director@camelliait.ac.in</t>
+        </is>
+      </c>
+      <c r="I709" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M709" s="9" t="inlineStr">
+        <is>
+          <t>https://camelliait.ac.in/contact.html</t>
+        </is>
+      </c>
+      <c r="N709" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="9" t="n">
+        <v>709</v>
+      </c>
+      <c r="B710" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C710" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D710" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E710" s="9" t="inlineStr">
+        <is>
+          <t>Techno College Hooghly</t>
+        </is>
+      </c>
+      <c r="F710" s="9" t="inlineStr"/>
+      <c r="G710" s="9" t="inlineStr"/>
+      <c r="H710" s="9" t="inlineStr">
+        <is>
+          <t>info@technocollegehooghly.org</t>
+        </is>
+      </c>
+      <c r="I710" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M710" s="9" t="inlineStr">
+        <is>
+          <t>https://technocollegehooghly.org/contactus.php</t>
+        </is>
+      </c>
+      <c r="N710" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="9" t="n">
+        <v>710</v>
+      </c>
+      <c r="B711" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C711" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D711" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E711" s="9" t="inlineStr">
+        <is>
+          <t>Future Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F711" s="9" t="inlineStr"/>
+      <c r="G711" s="9" t="inlineStr"/>
+      <c r="H711" s="9" t="inlineStr">
+        <is>
+          <t>fit@teamfuture.in</t>
+        </is>
+      </c>
+      <c r="I711" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M711" s="9" t="inlineStr">
+        <is>
+          <t>https://futureeducation.in/fit/</t>
+        </is>
+      </c>
+      <c r="N711" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="9" t="n">
+        <v>711</v>
+      </c>
+      <c r="B712" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C712" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D712" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E712" s="9" t="inlineStr">
+        <is>
+          <t>MCKV Institute of Engineering</t>
+        </is>
+      </c>
+      <c r="F712" s="9" t="inlineStr"/>
+      <c r="G712" s="9" t="inlineStr"/>
+      <c r="H712" s="9" t="inlineStr">
+        <is>
+          <t>info@mckvie.edu.in</t>
+        </is>
+      </c>
+      <c r="I712" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M712" s="9" t="inlineStr">
+        <is>
+          <t>https://www.mckvie.edu.in/contact-us</t>
+        </is>
+      </c>
+      <c r="N712" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="9" t="n">
+        <v>712</v>
+      </c>
+      <c r="B713" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C713" s="9" t="inlineStr">
+        <is>
+          <t>Uttarakhand</t>
+        </is>
+      </c>
+      <c r="D713" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E713" s="9" t="inlineStr">
+        <is>
+          <t>College of Technology, Pantnagar</t>
+        </is>
+      </c>
+      <c r="F713" s="9" t="inlineStr"/>
+      <c r="G713" s="9" t="inlineStr"/>
+      <c r="H713" s="9" t="inlineStr">
+        <is>
+          <t>deanctoffice@gmail.com</t>
+        </is>
+      </c>
+      <c r="I713" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M713" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gbpuat.ac.in/colleges/COT/index.html</t>
+        </is>
+      </c>
+      <c r="N713" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="9" t="n">
+        <v>713</v>
+      </c>
+      <c r="B714" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C714" s="9" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D714" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E714" s="9" t="inlineStr">
+        <is>
+          <t>Vasavi College of Engineering</t>
+        </is>
+      </c>
+      <c r="F714" s="9" t="inlineStr"/>
+      <c r="G714" s="9" t="inlineStr"/>
+      <c r="H714" s="9" t="inlineStr">
+        <is>
+          <t>principal@staff.vce.ac.in</t>
+        </is>
+      </c>
+      <c r="I714" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M714" s="9" t="inlineStr">
+        <is>
+          <t>https://vce.ac.in/contact.php</t>
+        </is>
+      </c>
+      <c r="N714" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="9" t="n">
+        <v>714</v>
+      </c>
+      <c r="B715" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C715" s="9" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D715" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E715" s="9" t="inlineStr">
+        <is>
+          <t>Marri Laxman Reddy Institute of Technology and Management</t>
+        </is>
+      </c>
+      <c r="F715" s="9" t="inlineStr"/>
+      <c r="G715" s="9" t="inlineStr"/>
+      <c r="H715" s="9" t="inlineStr">
+        <is>
+          <t>info@mlritm.ac.in</t>
+        </is>
+      </c>
+      <c r="I715" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M715" s="9" t="inlineStr">
+        <is>
+          <t>https://www.mlritm.ac.in/</t>
+        </is>
+      </c>
+      <c r="N715" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="9" t="n">
+        <v>715</v>
+      </c>
+      <c r="B716" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C716" s="9" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="D716" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E716" s="9" t="inlineStr">
+        <is>
+          <t>PERI Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F716" s="9" t="inlineStr"/>
+      <c r="G716" s="9" t="inlineStr"/>
+      <c r="H716" s="9" t="inlineStr">
+        <is>
+          <t>admin@peri.education</t>
+        </is>
+      </c>
+      <c r="I716" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M716" s="9" t="inlineStr">
+        <is>
+          <t>https://www.peri.education/periit/index.php</t>
+        </is>
+      </c>
+      <c r="N716" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="9" t="n">
+        <v>716</v>
+      </c>
+      <c r="B717" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C717" s="9" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="D717" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E717" s="9" t="inlineStr">
+        <is>
+          <t>Global Institute of Technology, Jaipur</t>
+        </is>
+      </c>
+      <c r="F717" s="9" t="inlineStr"/>
+      <c r="G717" s="9" t="inlineStr"/>
+      <c r="H717" s="9" t="inlineStr">
+        <is>
+          <t>support@gitjaipur.com</t>
+        </is>
+      </c>
+      <c r="I717" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M717" s="9" t="inlineStr">
+        <is>
+          <t>https://gitjaipur.com/</t>
+        </is>
+      </c>
+      <c r="N717" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="9" t="n">
+        <v>717</v>
+      </c>
+      <c r="B718" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C718" s="9" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="D718" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E718" s="9" t="inlineStr">
+        <is>
+          <t>Anand International College of Engineering</t>
+        </is>
+      </c>
+      <c r="F718" s="9" t="inlineStr"/>
+      <c r="G718" s="9" t="inlineStr"/>
+      <c r="H718" s="9" t="inlineStr">
+        <is>
+          <t>info@anandice.ac.in</t>
+        </is>
+      </c>
+      <c r="I718" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M718" s="9" t="inlineStr">
+        <is>
+          <t>https://anandice.ac.in/contact-us/</t>
+        </is>
+      </c>
+      <c r="N718" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="9" t="n">
+        <v>718</v>
+      </c>
+      <c r="B719" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C719" s="9" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="D719" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E719" s="9" t="inlineStr">
+        <is>
+          <t>Chandigarh Engineering College-CGC, Landran, Mohali</t>
+        </is>
+      </c>
+      <c r="F719" s="9" t="inlineStr"/>
+      <c r="G719" s="9" t="inlineStr"/>
+      <c r="H719" s="9" t="inlineStr">
+        <is>
+          <t>info@cgc.ac.in</t>
+        </is>
+      </c>
+      <c r="I719" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M719" s="9" t="inlineStr">
+        <is>
+          <t>https://cec.cgc.ac.in/contact-us</t>
+        </is>
+      </c>
+      <c r="N719" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="9" t="n">
+        <v>719</v>
+      </c>
+      <c r="B720" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C720" s="9" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="D720" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E720" s="9" t="inlineStr">
+        <is>
+          <t>Malout Institute of Management and Information Technology, Malout</t>
+        </is>
+      </c>
+      <c r="F720" s="9" t="inlineStr"/>
+      <c r="G720" s="9" t="inlineStr"/>
+      <c r="H720" s="9" t="inlineStr">
+        <is>
+          <t>info@mimitmalout.ac.in</t>
+        </is>
+      </c>
+      <c r="I720" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M720" s="9" t="inlineStr">
+        <is>
+          <t>https://mimitmalout.ac.in/Contact.aspx</t>
+        </is>
+      </c>
+      <c r="N720" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="9" t="n">
+        <v>720</v>
+      </c>
+      <c r="B721" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C721" s="9" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="D721" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E721" s="9" t="inlineStr">
+        <is>
+          <t>Kalinga Institute of Industrial Technology</t>
+        </is>
+      </c>
+      <c r="F721" s="9" t="inlineStr"/>
+      <c r="G721" s="9" t="inlineStr"/>
+      <c r="H721" s="9" t="inlineStr">
+        <is>
+          <t>kiit@kiit.ac.in</t>
+        </is>
+      </c>
+      <c r="I721" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M721" s="9" t="inlineStr">
+        <is>
+          <t>https://kiit.ac.in/contact/</t>
+        </is>
+      </c>
+      <c r="N721" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="9" t="n">
+        <v>721</v>
+      </c>
+      <c r="B722" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C722" s="9" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="D722" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E722" s="9" t="inlineStr">
+        <is>
+          <t>Rustamji Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F722" s="9" t="inlineStr"/>
+      <c r="G722" s="9" t="inlineStr"/>
+      <c r="H722" s="9" t="inlineStr">
+        <is>
+          <t>info@rjit.ac.in</t>
+        </is>
+      </c>
+      <c r="I722" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M722" s="9" t="inlineStr">
+        <is>
+          <t>https://rjit.ac.in/contact.php</t>
+        </is>
+      </c>
+      <c r="N722" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="9" t="n">
+        <v>722</v>
+      </c>
+      <c r="B723" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C723" s="9" t="inlineStr">
+        <is>
+          <t>Kerala</t>
+        </is>
+      </c>
+      <c r="D723" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E723" s="9" t="inlineStr">
+        <is>
+          <t>Musaliar College of Engineering</t>
+        </is>
+      </c>
+      <c r="F723" s="9" t="inlineStr"/>
+      <c r="G723" s="9" t="inlineStr"/>
+      <c r="H723" s="9" t="inlineStr">
+        <is>
+          <t>principal@musaliarcollege.com</t>
+        </is>
+      </c>
+      <c r="I723" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M723" s="9" t="inlineStr">
+        <is>
+          <t>https://musaliarcollege.com/contact/</t>
+        </is>
+      </c>
+      <c r="N723" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="9" t="n">
+        <v>723</v>
+      </c>
+      <c r="B724" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C724" s="9" t="inlineStr">
+        <is>
+          <t>Himachal Pradesh</t>
+        </is>
+      </c>
+      <c r="D724" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E724" s="9" t="inlineStr">
+        <is>
+          <t>Himalayan Institute of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="F724" s="9" t="inlineStr"/>
+      <c r="G724" s="9" t="inlineStr"/>
+      <c r="H724" s="9" t="inlineStr">
+        <is>
+          <t>admission@hgpi.in</t>
+        </is>
+      </c>
+      <c r="I724" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M724" s="9" t="inlineStr">
+        <is>
+          <t>https://hgpi.in/academics/hiet</t>
+        </is>
+      </c>
+      <c r="N724" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="9" t="n">
+        <v>724</v>
+      </c>
+      <c r="B725" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C725" s="9" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="D725" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E725" s="9" t="inlineStr">
+        <is>
+          <t>Advanced Institute of Technology and Management</t>
+        </is>
+      </c>
+      <c r="F725" s="9" t="inlineStr"/>
+      <c r="G725" s="9" t="inlineStr"/>
+      <c r="H725" s="9" t="inlineStr">
+        <is>
+          <t>info@advancedinstitutions.com</t>
+        </is>
+      </c>
+      <c r="I725" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M725" s="9" t="inlineStr">
+        <is>
+          <t>https://www.advanced.edu.in/</t>
+        </is>
+      </c>
+      <c r="N725" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="9" t="n">
+        <v>725</v>
+      </c>
+      <c r="B726" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C726" s="9" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="D726" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E726" s="9" t="inlineStr">
+        <is>
+          <t>Nimra College of Engineering and Technology</t>
+        </is>
+      </c>
+      <c r="F726" s="9" t="inlineStr"/>
+      <c r="G726" s="9" t="inlineStr"/>
+      <c r="H726" s="9" t="inlineStr">
+        <is>
+          <t>principal_nimra@yahoo.co.in</t>
+        </is>
+      </c>
+      <c r="I726" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M726" s="9" t="inlineStr">
+        <is>
+          <t>https://nimracet.in/contact-us.html</t>
+        </is>
+      </c>
+      <c r="N726" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="9" t="n">
+        <v>726</v>
+      </c>
+      <c r="B727" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C727" s="9" t="inlineStr">
+        <is>
+          <t>Chandigarh</t>
+        </is>
+      </c>
+      <c r="D727" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E727" s="9" t="inlineStr">
+        <is>
+          <t>University Institute of Engineering and Technology, Panjab University</t>
+        </is>
+      </c>
+      <c r="F727" s="9" t="inlineStr"/>
+      <c r="G727" s="9" t="inlineStr"/>
+      <c r="H727" s="9" t="inlineStr">
+        <is>
+          <t>directoruiet@pu.ac.in</t>
+        </is>
+      </c>
+      <c r="I727" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M727" s="9" t="inlineStr">
+        <is>
+          <t>https://uiet.puchd.ac.in/?page_id=273</t>
+        </is>
+      </c>
+      <c r="N727" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="9" t="n">
+        <v>727</v>
+      </c>
+      <c r="B728" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C728" s="9" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D728" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E728" s="9" t="inlineStr">
+        <is>
+          <t>Maharaja Agrasen Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F728" s="9" t="inlineStr"/>
+      <c r="G728" s="9" t="inlineStr"/>
+      <c r="H728" s="9" t="inlineStr">
+        <is>
+          <t>mait@mait.ac.in</t>
+        </is>
+      </c>
+      <c r="I728" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M728" s="9" t="inlineStr">
+        <is>
+          <t>https://www.mait.ac.in/index.php/contact-us</t>
+        </is>
+      </c>
+      <c r="N728" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="9" t="n">
+        <v>728</v>
+      </c>
+      <c r="B729" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C729" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D729" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E729" s="9" t="inlineStr">
+        <is>
+          <t>Government College of Engineering &amp; Ceramic Technology</t>
+        </is>
+      </c>
+      <c r="F729" s="9" t="inlineStr"/>
+      <c r="G729" s="9" t="inlineStr"/>
+      <c r="H729" s="9" t="inlineStr">
+        <is>
+          <t>principal.gcect@gcect.ac.in</t>
+        </is>
+      </c>
+      <c r="I729" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M729" s="9" t="inlineStr">
+        <is>
+          <t>https://gcect.ac.in/contact-us/</t>
+        </is>
+      </c>
+      <c r="N729" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="9" t="n">
+        <v>729</v>
+      </c>
+      <c r="B730" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C730" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D730" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E730" s="9" t="inlineStr">
+        <is>
+          <t>Kalyani Government Engineering College</t>
+        </is>
+      </c>
+      <c r="F730" s="9" t="inlineStr"/>
+      <c r="G730" s="9" t="inlineStr"/>
+      <c r="H730" s="9" t="inlineStr">
+        <is>
+          <t>contact@kgec.edu.in</t>
+        </is>
+      </c>
+      <c r="I730" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M730" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kgec.edu.in/</t>
+        </is>
+      </c>
+      <c r="N730" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="9" t="n">
+        <v>730</v>
+      </c>
+      <c r="B731" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C731" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D731" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E731" s="9" t="inlineStr">
+        <is>
+          <t>Hemnalini Memorial College of Engineering</t>
+        </is>
+      </c>
+      <c r="F731" s="9" t="inlineStr"/>
+      <c r="G731" s="9" t="inlineStr"/>
+      <c r="H731" s="9" t="inlineStr">
+        <is>
+          <t>hmce2021@gmail.com</t>
+        </is>
+      </c>
+      <c r="I731" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M731" s="9" t="inlineStr">
+        <is>
+          <t>https://www.hmcekalyani.org/ContactUs.aspx</t>
+        </is>
+      </c>
+      <c r="N731" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="9" t="n">
+        <v>731</v>
+      </c>
+      <c r="B732" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C732" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D732" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E732" s="9" t="inlineStr">
+        <is>
+          <t>Siliguri Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F732" s="9" t="inlineStr"/>
+      <c r="G732" s="9" t="inlineStr"/>
+      <c r="H732" s="9" t="inlineStr">
+        <is>
+          <t>info@sittechno.org</t>
+        </is>
+      </c>
+      <c r="I732" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M732" s="9" t="inlineStr">
+        <is>
+          <t>https://www.sittechno.org/contact-us-5e4f8f9bd01ee.html</t>
+        </is>
+      </c>
+      <c r="N732" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="9" t="n">
+        <v>732</v>
+      </c>
+      <c r="B733" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C733" s="9" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D733" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E733" s="9" t="inlineStr">
+        <is>
+          <t>Deccan College of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="F733" s="9" t="inlineStr"/>
+      <c r="G733" s="9" t="inlineStr"/>
+      <c r="H733" s="9" t="inlineStr">
+        <is>
+          <t>dcet@deccancollege.ac.in</t>
+        </is>
+      </c>
+      <c r="I733" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M733" s="9" t="inlineStr">
+        <is>
+          <t>https://deccancollege.ac.in/contact-us/</t>
+        </is>
+      </c>
+      <c r="N733" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="9" t="n">
+        <v>733</v>
+      </c>
+      <c r="B734" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C734" s="9" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="D734" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E734" s="9" t="inlineStr">
+        <is>
+          <t>Idhaya Engineering College for Women</t>
+        </is>
+      </c>
+      <c r="F734" s="9" t="inlineStr"/>
+      <c r="G734" s="9" t="inlineStr"/>
+      <c r="H734" s="9" t="inlineStr">
+        <is>
+          <t>idhaya@iecw.edu.in</t>
+        </is>
+      </c>
+      <c r="I734" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M734" s="9" t="inlineStr">
+        <is>
+          <t>https://iecw.edu.in/</t>
+        </is>
+      </c>
+      <c r="N734" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="9" t="n">
+        <v>734</v>
+      </c>
+      <c r="B735" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C735" s="9" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="D735" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E735" s="9" t="inlineStr">
+        <is>
+          <t>Jodhpur Institute of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="F735" s="9" t="inlineStr"/>
+      <c r="G735" s="9" t="inlineStr"/>
+      <c r="H735" s="9" t="inlineStr">
+        <is>
+          <t>info@jietjodhpur.ac.in</t>
+        </is>
+      </c>
+      <c r="I735" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M735" s="9" t="inlineStr">
+        <is>
+          <t>https://www.jietjodhpur.ac.in/</t>
+        </is>
+      </c>
+      <c r="N735" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="9" t="n">
+        <v>735</v>
+      </c>
+      <c r="B736" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C736" s="9" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="D736" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E736" s="9" t="inlineStr">
+        <is>
+          <t>Ramgarhia Institute of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="F736" s="9" t="inlineStr"/>
+      <c r="G736" s="9" t="inlineStr"/>
+      <c r="H736" s="9" t="inlineStr">
+        <is>
+          <t>info@riet.ac.in</t>
+        </is>
+      </c>
+      <c r="I736" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M736" s="9" t="inlineStr">
+        <is>
+          <t>https://www.riet.ac.in/</t>
+        </is>
+      </c>
+      <c r="N736" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="9" t="n">
+        <v>736</v>
+      </c>
+      <c r="B737" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C737" s="9" t="inlineStr">
+        <is>
+          <t>Puducherry</t>
+        </is>
+      </c>
+      <c r="D737" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E737" s="9" t="inlineStr">
+        <is>
+          <t>Alpha College of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="F737" s="9" t="inlineStr"/>
+      <c r="G737" s="9" t="inlineStr"/>
+      <c r="H737" s="9" t="inlineStr">
+        <is>
+          <t>admin@aceatech.in</t>
+        </is>
+      </c>
+      <c r="I737" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M737" s="9" t="inlineStr">
+        <is>
+          <t>https://www.aceatech.in/</t>
+        </is>
+      </c>
+      <c r="N737" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="9" t="n">
+        <v>737</v>
+      </c>
+      <c r="B738" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C738" s="9" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="D738" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E738" s="9" t="inlineStr">
+        <is>
+          <t>Silicon Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F738" s="9" t="inlineStr"/>
+      <c r="G738" s="9" t="inlineStr"/>
+      <c r="H738" s="9" t="inlineStr">
+        <is>
+          <t>info@silicon.ac.in</t>
+        </is>
+      </c>
+      <c r="I738" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M738" s="9" t="inlineStr">
+        <is>
+          <t>https://silicon.ac.in/contact-us/</t>
+        </is>
+      </c>
+      <c r="N738" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="9" t="n">
+        <v>738</v>
+      </c>
+      <c r="B739" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C739" s="9" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="D739" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E739" s="9" t="inlineStr">
+        <is>
+          <t>Gopal Krishna College of Engineering &amp; Technology, Jeypore</t>
+        </is>
+      </c>
+      <c r="F739" s="9" t="inlineStr"/>
+      <c r="G739" s="9" t="inlineStr"/>
+      <c r="H739" s="9" t="inlineStr">
+        <is>
+          <t>gkcet12311@gmail.com</t>
+        </is>
+      </c>
+      <c r="I739" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M739" s="9" t="inlineStr">
+        <is>
+          <t>https://gkcet.co.in/contact-us</t>
+        </is>
+      </c>
+      <c r="N739" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="9" t="n">
+        <v>739</v>
+      </c>
+      <c r="B740" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C740" s="9" t="inlineStr">
+        <is>
+          <t>Kerala</t>
+        </is>
+      </c>
+      <c r="D740" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E740" s="9" t="inlineStr">
+        <is>
+          <t>Government Engineering College, Barton Hill</t>
+        </is>
+      </c>
+      <c r="F740" s="9" t="inlineStr"/>
+      <c r="G740" s="9" t="inlineStr"/>
+      <c r="H740" s="9" t="inlineStr">
+        <is>
+          <t>principal@gecbh.ac.in</t>
+        </is>
+      </c>
+      <c r="I740" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M740" s="9" t="inlineStr">
+        <is>
+          <t>https://gecbh.ac.in/</t>
+        </is>
+      </c>
+      <c r="N740" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="9" t="n">
+        <v>740</v>
+      </c>
+      <c r="B741" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C741" s="9" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="D741" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E741" s="9" t="inlineStr">
+        <is>
+          <t>National Institute of Food Technology Entrepreneurship and Management</t>
+        </is>
+      </c>
+      <c r="F741" s="9" t="inlineStr"/>
+      <c r="G741" s="9" t="inlineStr"/>
+      <c r="H741" s="9" t="inlineStr">
+        <is>
+          <t>info@niftem.ac.in</t>
+        </is>
+      </c>
+      <c r="I741" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M741" s="9" t="inlineStr">
+        <is>
+          <t>https://www.niftem.ac.in/</t>
+        </is>
+      </c>
+      <c r="N741" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="9" t="n">
+        <v>741</v>
+      </c>
+      <c r="B742" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C742" s="9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D742" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E742" s="9" t="inlineStr">
+        <is>
+          <t>Bengal College of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="F742" s="9" t="inlineStr"/>
+      <c r="G742" s="9" t="inlineStr"/>
+      <c r="H742" s="9" t="inlineStr">
+        <is>
+          <t>contact@bcetdgp.ac.in</t>
+        </is>
+      </c>
+      <c r="I742" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M742" s="9" t="inlineStr">
+        <is>
+          <t>https://bcetdgp.ac.in/HTML/CSE/contact.html</t>
+        </is>
+      </c>
+      <c r="N742" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="9" t="n">
+        <v>742</v>
+      </c>
+      <c r="B743" s="9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C743" s="9" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D743" s="9" t="inlineStr">
+        <is>
+          <t>Engineering College</t>
+        </is>
+      </c>
+      <c r="E743" s="9" t="inlineStr">
+        <is>
+          <t>Guru Tegh Bahadur 4th Centenary Engineering College</t>
+        </is>
+      </c>
+      <c r="F743" s="9" t="inlineStr"/>
+      <c r="G743" s="9" t="inlineStr"/>
+      <c r="H743" s="9" t="inlineStr">
+        <is>
+          <t>gtb4cec@gmail.com</t>
+        </is>
+      </c>
+      <c r="I743" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="M743" s="9" t="inlineStr">
+        <is>
+          <t>https://gtb4cec.org/contact-us</t>
+        </is>
+      </c>
+      <c r="N743" s="9" t="inlineStr">
+        <is>
+          <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O207"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -43618,7 +46438,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>162</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="10">

--- a/data/Incubation_Outreach_Tracker.xlsx
+++ b/data/Incubation_Outreach_Tracker.xlsx
@@ -12994,7 +12994,7 @@
       </c>
       <c r="I199" s="14" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J199" s="14" t="inlineStr">
@@ -13018,7 +13018,11 @@
           <t>Upgraded from blocked: name + email verified live on official page.</t>
         </is>
       </c>
-      <c r="O199" s="14" t="n"/>
+      <c r="O199" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
       <c r="P199" s="13" t="n"/>
       <c r="Q199" s="13" t="n"/>
     </row>
@@ -34654,7 +34658,7 @@
       </c>
       <c r="I511" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J511" s="9" t="inlineStr">
@@ -34675,6 +34679,11 @@
       <c r="N511" s="9" t="inlineStr">
         <is>
           <t>Name + email verified live on official page.</t>
+        </is>
+      </c>
+      <c r="O511" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -34909,7 +34918,7 @@
       </c>
       <c r="I516" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J516" s="9" t="inlineStr">
@@ -34930,6 +34939,11 @@
       <c r="N516" s="9" t="inlineStr">
         <is>
           <t>Director's name confirmed on TNAU site; email itself not independently visible on a public page — verify before send.</t>
+        </is>
+      </c>
+      <c r="O516" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -34974,7 +34988,7 @@
       </c>
       <c r="I517" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J517" s="9" t="inlineStr">
@@ -34995,6 +35009,11 @@
       <c r="N517" s="9" t="inlineStr">
         <is>
           <t>Name + email verified live on official page.</t>
+        </is>
+      </c>
+      <c r="O517" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -35034,7 +35053,7 @@
       </c>
       <c r="I518" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J518" s="9" t="inlineStr">
@@ -35055,6 +35074,11 @@
       <c r="N518" s="9" t="inlineStr">
         <is>
           <t>Council email confirmed live on official IIC page.</t>
+        </is>
+      </c>
+      <c r="O518" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -35099,7 +35123,7 @@
       </c>
       <c r="I519" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J519" s="9" t="inlineStr">
@@ -35120,6 +35144,11 @@
       <c r="N519" s="9" t="inlineStr">
         <is>
           <t>Name + email verified (listed as Public Information Officer with this address).</t>
+        </is>
+      </c>
+      <c r="O519" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -35209,7 +35238,7 @@
       </c>
       <c r="I521" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J521" s="9" t="inlineStr">
@@ -35230,6 +35259,11 @@
       <c r="N521" s="9" t="inlineStr">
         <is>
           <t>Name + email verified live on official NISP committee page.</t>
+        </is>
+      </c>
+      <c r="O521" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -35274,7 +35308,7 @@
       </c>
       <c r="I522" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J522" s="9" t="inlineStr">
@@ -35295,6 +35329,11 @@
       <c r="N522" s="9" t="inlineStr">
         <is>
           <t>Name + email verified; centre also has its own CIIE@dypiu.ac.in address as alternate.</t>
+        </is>
+      </c>
+      <c r="O522" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -35334,7 +35373,7 @@
       </c>
       <c r="I523" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J523" s="9" t="inlineStr">
@@ -35355,6 +35394,11 @@
       <c r="N523" s="9" t="inlineStr">
         <is>
           <t>Program Manager (Madhuree Kanetkar) email is obfuscated on site; enquiry@flame.edu.in is the only visible address — generic, not FCEI-specific.</t>
+        </is>
+      </c>
+      <c r="O523" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -35394,7 +35438,7 @@
       </c>
       <c r="I524" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J524" s="9" t="inlineStr">
@@ -35415,6 +35459,11 @@
       <c r="N524" s="9" t="inlineStr">
         <is>
           <t>Email confirmed live as the primary VentureStudio contact.</t>
+        </is>
+      </c>
+      <c r="O524" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -35589,7 +35638,7 @@
       </c>
       <c r="I528" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J528" s="9" t="inlineStr">
@@ -35610,6 +35659,11 @@
       <c r="N528" s="9" t="inlineStr">
         <is>
           <t>Confirmed live but explicitly the general enquiries address, not I2E-specific.</t>
+        </is>
+      </c>
+      <c r="O528" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -35699,7 +35753,7 @@
       </c>
       <c r="I530" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J530" s="9" t="inlineStr">
@@ -35720,6 +35774,11 @@
       <c r="N530" s="9" t="inlineStr">
         <is>
           <t>Name + email verified on official BIIC team page.</t>
+        </is>
+      </c>
+      <c r="O530" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -35804,7 +35863,7 @@
       </c>
       <c r="I532" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J532" s="9" t="inlineStr">
@@ -35825,6 +35884,11 @@
       <c r="N532" s="9" t="inlineStr">
         <is>
           <t>Claimed contact 'Dr. Saptarshi Chatterjee' is a Biotech professor with no incubation role — likely bad match in source data. Verified role-based address found instead (alt: birac.e-yuva@adamasuniversity.ac.in).</t>
+        </is>
+      </c>
+      <c r="O532" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -35914,7 +35978,7 @@
       </c>
       <c r="I534" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J534" s="9" t="inlineStr">
@@ -35935,6 +35999,11 @@
       <c r="N534" s="9" t="inlineStr">
         <is>
           <t>Role confirmed on official core-team page; email is the centre's shared address, not personal.</t>
+        </is>
+      </c>
+      <c r="O534" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -35969,7 +36038,7 @@
       </c>
       <c r="I535" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J535" s="9" t="inlineStr">
@@ -35990,6 +36059,11 @@
       <c r="N535" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O535" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -36024,7 +36098,7 @@
       </c>
       <c r="I536" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J536" s="9" t="inlineStr">
@@ -36045,6 +36119,11 @@
       <c r="N536" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O536" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -36079,7 +36158,7 @@
       </c>
       <c r="I537" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J537" s="9" t="inlineStr">
@@ -36100,6 +36179,11 @@
       <c r="N537" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O537" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -36134,7 +36218,7 @@
       </c>
       <c r="I538" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J538" s="9" t="inlineStr">
@@ -36155,6 +36239,11 @@
       <c r="N538" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O538" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -36189,7 +36278,7 @@
       </c>
       <c r="I539" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J539" s="9" t="inlineStr">
@@ -36210,6 +36299,11 @@
       <c r="N539" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O539" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -36244,7 +36338,7 @@
       </c>
       <c r="I540" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J540" s="9" t="inlineStr">
@@ -36265,6 +36359,11 @@
       <c r="N540" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O540" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -36299,7 +36398,7 @@
       </c>
       <c r="I541" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J541" s="9" t="inlineStr">
@@ -36320,6 +36419,11 @@
       <c r="N541" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O541" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -36354,7 +36458,7 @@
       </c>
       <c r="I542" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J542" s="9" t="inlineStr">
@@ -36375,6 +36479,11 @@
       <c r="N542" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O542" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -36409,7 +36518,7 @@
       </c>
       <c r="I543" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J543" s="9" t="inlineStr">
@@ -36430,6 +36539,11 @@
       <c r="N543" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O543" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -36464,7 +36578,7 @@
       </c>
       <c r="I544" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J544" s="9" t="inlineStr">
@@ -36485,6 +36599,11 @@
       <c r="N544" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O544" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -36519,7 +36638,7 @@
       </c>
       <c r="I545" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J545" s="9" t="inlineStr">
@@ -36540,6 +36659,11 @@
       <c r="N545" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O545" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -36574,7 +36698,7 @@
       </c>
       <c r="I546" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J546" s="9" t="inlineStr">
@@ -36595,6 +36719,11 @@
       <c r="N546" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O546" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -36629,7 +36758,7 @@
       </c>
       <c r="I547" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J547" s="9" t="inlineStr">
@@ -36650,6 +36779,11 @@
       <c r="N547" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O547" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -36684,7 +36818,7 @@
       </c>
       <c r="I548" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J548" s="9" t="inlineStr">
@@ -36705,6 +36839,11 @@
       <c r="N548" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O548" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -36739,7 +36878,7 @@
       </c>
       <c r="I549" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J549" s="9" t="inlineStr">
@@ -36760,6 +36899,11 @@
       <c r="N549" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O549" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -36794,7 +36938,7 @@
       </c>
       <c r="I550" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J550" s="9" t="inlineStr">
@@ -36815,6 +36959,11 @@
       <c r="N550" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O550" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -36849,7 +36998,7 @@
       </c>
       <c r="I551" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J551" s="9" t="inlineStr">
@@ -36870,6 +37019,11 @@
       <c r="N551" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O551" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -36904,7 +37058,7 @@
       </c>
       <c r="I552" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J552" s="9" t="inlineStr">
@@ -36925,6 +37079,11 @@
       <c r="N552" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O552" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -36959,7 +37118,7 @@
       </c>
       <c r="I553" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J553" s="9" t="inlineStr">
@@ -36980,6 +37139,11 @@
       <c r="N553" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O553" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -37014,7 +37178,7 @@
       </c>
       <c r="I554" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J554" s="9" t="inlineStr">
@@ -37035,6 +37199,11 @@
       <c r="N554" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O554" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -37069,7 +37238,7 @@
       </c>
       <c r="I555" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J555" s="9" t="inlineStr">
@@ -37090,6 +37259,11 @@
       <c r="N555" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O555" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -37124,7 +37298,7 @@
       </c>
       <c r="I556" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J556" s="9" t="inlineStr">
@@ -37145,6 +37319,11 @@
       <c r="N556" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O556" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -37179,7 +37358,7 @@
       </c>
       <c r="I557" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J557" s="9" t="inlineStr">
@@ -37200,6 +37379,11 @@
       <c r="N557" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O557" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -37234,7 +37418,7 @@
       </c>
       <c r="I558" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J558" s="9" t="inlineStr">
@@ -37255,6 +37439,11 @@
       <c r="N558" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O558" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -37289,7 +37478,7 @@
       </c>
       <c r="I559" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J559" s="9" t="inlineStr">
@@ -37310,6 +37499,11 @@
       <c r="N559" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O559" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -37344,7 +37538,7 @@
       </c>
       <c r="I560" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J560" s="9" t="inlineStr">
@@ -37365,6 +37559,11 @@
       <c r="N560" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O560" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -37399,7 +37598,7 @@
       </c>
       <c r="I561" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J561" s="9" t="inlineStr">
@@ -37420,6 +37619,11 @@
       <c r="N561" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O561" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -37454,7 +37658,7 @@
       </c>
       <c r="I562" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J562" s="9" t="inlineStr">
@@ -37475,6 +37679,11 @@
       <c r="N562" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O562" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -37509,7 +37718,7 @@
       </c>
       <c r="I563" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J563" s="9" t="inlineStr">
@@ -37530,6 +37739,11 @@
       <c r="N563" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O563" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -37564,7 +37778,7 @@
       </c>
       <c r="I564" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J564" s="9" t="inlineStr">
@@ -37585,6 +37799,11 @@
       <c r="N564" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O564" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -37619,7 +37838,7 @@
       </c>
       <c r="I565" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J565" s="9" t="inlineStr">
@@ -37640,6 +37859,11 @@
       <c r="N565" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O565" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -37674,7 +37898,7 @@
       </c>
       <c r="I566" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J566" s="9" t="inlineStr">
@@ -37695,6 +37919,11 @@
       <c r="N566" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O566" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -37729,7 +37958,7 @@
       </c>
       <c r="I567" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J567" s="9" t="inlineStr">
@@ -37750,6 +37979,11 @@
       <c r="N567" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O567" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -37784,7 +38018,7 @@
       </c>
       <c r="I568" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J568" s="9" t="inlineStr">
@@ -37805,6 +38039,11 @@
       <c r="N568" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O568" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -37839,7 +38078,7 @@
       </c>
       <c r="I569" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J569" s="9" t="inlineStr">
@@ -37860,6 +38099,11 @@
       <c r="N569" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O569" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -37894,7 +38138,7 @@
       </c>
       <c r="I570" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J570" s="9" t="inlineStr">
@@ -37915,6 +38159,11 @@
       <c r="N570" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O570" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -37949,7 +38198,7 @@
       </c>
       <c r="I571" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J571" s="9" t="inlineStr">
@@ -37970,6 +38219,11 @@
       <c r="N571" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O571" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -38004,7 +38258,7 @@
       </c>
       <c r="I572" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J572" s="9" t="inlineStr">
@@ -38025,6 +38279,11 @@
       <c r="N572" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O572" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -38059,7 +38318,7 @@
       </c>
       <c r="I573" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J573" s="9" t="inlineStr">
@@ -38080,6 +38339,11 @@
       <c r="N573" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O573" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -38114,7 +38378,7 @@
       </c>
       <c r="I574" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J574" s="9" t="inlineStr">
@@ -38135,6 +38399,11 @@
       <c r="N574" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O574" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -38169,7 +38438,7 @@
       </c>
       <c r="I575" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J575" s="9" t="inlineStr">
@@ -38190,6 +38459,11 @@
       <c r="N575" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O575" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -38224,7 +38498,7 @@
       </c>
       <c r="I576" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J576" s="9" t="inlineStr">
@@ -38245,6 +38519,11 @@
       <c r="N576" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O576" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -38279,7 +38558,7 @@
       </c>
       <c r="I577" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J577" s="9" t="inlineStr">
@@ -38300,6 +38579,11 @@
       <c r="N577" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O577" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -38334,7 +38618,7 @@
       </c>
       <c r="I578" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J578" s="9" t="inlineStr">
@@ -38355,6 +38639,11 @@
       <c r="N578" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O578" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -38389,7 +38678,7 @@
       </c>
       <c r="I579" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J579" s="9" t="inlineStr">
@@ -38410,6 +38699,11 @@
       <c r="N579" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O579" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -38444,7 +38738,7 @@
       </c>
       <c r="I580" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J580" s="9" t="inlineStr">
@@ -38465,6 +38759,11 @@
       <c r="N580" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O580" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -38499,7 +38798,7 @@
       </c>
       <c r="I581" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J581" s="9" t="inlineStr">
@@ -38520,6 +38819,11 @@
       <c r="N581" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O581" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -38554,7 +38858,7 @@
       </c>
       <c r="I582" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J582" s="9" t="inlineStr">
@@ -38575,6 +38879,11 @@
       <c r="N582" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O582" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -38609,7 +38918,7 @@
       </c>
       <c r="I583" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J583" s="9" t="inlineStr">
@@ -38630,6 +38939,11 @@
       <c r="N583" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O583" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -38664,7 +38978,7 @@
       </c>
       <c r="I584" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J584" s="9" t="inlineStr">
@@ -38685,6 +38999,11 @@
       <c r="N584" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O584" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -38719,7 +39038,7 @@
       </c>
       <c r="I585" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J585" s="9" t="inlineStr">
@@ -38740,6 +39059,11 @@
       <c r="N585" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O585" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -38774,7 +39098,7 @@
       </c>
       <c r="I586" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J586" s="9" t="inlineStr">
@@ -38795,6 +39119,11 @@
       <c r="N586" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O586" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -38829,7 +39158,7 @@
       </c>
       <c r="I587" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J587" s="9" t="inlineStr">
@@ -38850,6 +39179,11 @@
       <c r="N587" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O587" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -38884,7 +39218,7 @@
       </c>
       <c r="I588" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J588" s="9" t="inlineStr">
@@ -38905,6 +39239,11 @@
       <c r="N588" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O588" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -38939,7 +39278,7 @@
       </c>
       <c r="I589" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J589" s="9" t="inlineStr">
@@ -38960,6 +39299,11 @@
       <c r="N589" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O589" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -38994,7 +39338,7 @@
       </c>
       <c r="I590" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J590" s="9" t="inlineStr">
@@ -39015,6 +39359,11 @@
       <c r="N590" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O590" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -39049,7 +39398,7 @@
       </c>
       <c r="I591" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J591" s="9" t="inlineStr">
@@ -39070,6 +39419,11 @@
       <c r="N591" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O591" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -39104,7 +39458,7 @@
       </c>
       <c r="I592" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J592" s="9" t="inlineStr">
@@ -39125,6 +39479,11 @@
       <c r="N592" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O592" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -39159,7 +39518,7 @@
       </c>
       <c r="I593" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J593" s="9" t="inlineStr">
@@ -39180,6 +39539,11 @@
       <c r="N593" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O593" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -39214,7 +39578,7 @@
       </c>
       <c r="I594" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J594" s="9" t="inlineStr">
@@ -39235,6 +39599,11 @@
       <c r="N594" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O594" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -39269,7 +39638,7 @@
       </c>
       <c r="I595" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J595" s="9" t="inlineStr">
@@ -39290,6 +39659,11 @@
       <c r="N595" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O595" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -39324,7 +39698,7 @@
       </c>
       <c r="I596" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J596" s="9" t="inlineStr">
@@ -39345,6 +39719,11 @@
       <c r="N596" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O596" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -39379,7 +39758,7 @@
       </c>
       <c r="I597" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J597" s="9" t="inlineStr">
@@ -39400,6 +39779,11 @@
       <c r="N597" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O597" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -39434,7 +39818,7 @@
       </c>
       <c r="I598" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J598" s="9" t="inlineStr">
@@ -39455,6 +39839,11 @@
       <c r="N598" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O598" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -39489,7 +39878,7 @@
       </c>
       <c r="I599" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J599" s="9" t="inlineStr">
@@ -39510,6 +39899,11 @@
       <c r="N599" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O599" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -39544,7 +39938,7 @@
       </c>
       <c r="I600" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="J600" s="9" t="inlineStr">
@@ -39565,6 +39959,11 @@
       <c r="N600" s="9" t="inlineStr">
         <is>
           <t>Academic/admissions office contact from JoSAA 2026-27 official directory (spot-checked against live official pages); asked to forward to incubation/entrepreneurship cell if one exists.</t>
+        </is>
+      </c>
+      <c r="O600" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -39646,7 +40045,7 @@
       </c>
       <c r="I602" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M602" s="9" t="inlineStr">
@@ -39659,7 +40058,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O602" s="9" t="n"/>
+      <c r="O602" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" s="9" t="n">
@@ -39694,7 +40097,7 @@
       </c>
       <c r="I603" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M603" s="9" t="inlineStr">
@@ -39707,7 +40110,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O603" s="9" t="n"/>
+      <c r="O603" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" s="9" t="n">
@@ -39742,7 +40149,7 @@
       </c>
       <c r="I604" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M604" s="9" t="inlineStr">
@@ -39755,7 +40162,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O604" s="9" t="n"/>
+      <c r="O604" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" s="9" t="n">
@@ -39790,7 +40201,7 @@
       </c>
       <c r="I605" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M605" s="9" t="inlineStr">
@@ -39803,7 +40214,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O605" s="9" t="n"/>
+      <c r="O605" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" s="9" t="n">
@@ -39838,7 +40253,7 @@
       </c>
       <c r="I606" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M606" s="9" t="inlineStr">
@@ -39851,7 +40266,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O606" s="9" t="n"/>
+      <c r="O606" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" s="9" t="n">
@@ -39886,7 +40305,7 @@
       </c>
       <c r="I607" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M607" s="9" t="inlineStr">
@@ -39899,7 +40318,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O607" s="9" t="n"/>
+      <c r="O607" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" s="9" t="n">
@@ -39934,7 +40357,7 @@
       </c>
       <c r="I608" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M608" s="9" t="inlineStr">
@@ -39947,7 +40370,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O608" s="9" t="n"/>
+      <c r="O608" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" s="9" t="n">
@@ -39982,7 +40409,7 @@
       </c>
       <c r="I609" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M609" s="9" t="inlineStr">
@@ -39995,7 +40422,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O609" s="9" t="n"/>
+      <c r="O609" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" s="9" t="n">
@@ -40030,7 +40461,7 @@
       </c>
       <c r="I610" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M610" s="9" t="inlineStr">
@@ -40043,7 +40474,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O610" s="9" t="n"/>
+      <c r="O610" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" s="9" t="n">
@@ -40078,7 +40513,7 @@
       </c>
       <c r="I611" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M611" s="9" t="inlineStr">
@@ -40091,7 +40526,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O611" s="9" t="n"/>
+      <c r="O611" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" s="9" t="n">
@@ -40126,7 +40565,7 @@
       </c>
       <c r="I612" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M612" s="9" t="inlineStr">
@@ -40139,7 +40578,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O612" s="9" t="n"/>
+      <c r="O612" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" s="9" t="n">
@@ -40174,7 +40617,7 @@
       </c>
       <c r="I613" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M613" s="9" t="inlineStr">
@@ -40187,7 +40630,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O613" s="9" t="n"/>
+      <c r="O613" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" s="9" t="n">
@@ -40222,7 +40669,7 @@
       </c>
       <c r="I614" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M614" s="9" t="inlineStr">
@@ -40235,7 +40682,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O614" s="9" t="n"/>
+      <c r="O614" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" s="9" t="n">
@@ -40270,7 +40721,7 @@
       </c>
       <c r="I615" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M615" s="9" t="inlineStr">
@@ -40283,7 +40734,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O615" s="9" t="n"/>
+      <c r="O615" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" s="9" t="n">
@@ -40318,7 +40773,7 @@
       </c>
       <c r="I616" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M616" s="9" t="inlineStr">
@@ -40331,7 +40786,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O616" s="9" t="n"/>
+      <c r="O616" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" s="9" t="n">
@@ -40366,7 +40825,7 @@
       </c>
       <c r="I617" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M617" s="9" t="inlineStr">
@@ -40379,7 +40838,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O617" s="9" t="n"/>
+      <c r="O617" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" s="9" t="n">
@@ -40414,7 +40877,7 @@
       </c>
       <c r="I618" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M618" s="9" t="inlineStr">
@@ -40427,7 +40890,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O618" s="9" t="n"/>
+      <c r="O618" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" s="9" t="n">
@@ -40462,7 +40929,7 @@
       </c>
       <c r="I619" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M619" s="9" t="inlineStr">
@@ -40475,7 +40942,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O619" s="9" t="n"/>
+      <c r="O619" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" s="9" t="n">
@@ -40510,7 +40981,7 @@
       </c>
       <c r="I620" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M620" s="9" t="inlineStr">
@@ -40523,7 +40994,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O620" s="9" t="n"/>
+      <c r="O620" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" s="9" t="n">
@@ -40558,7 +41033,7 @@
       </c>
       <c r="I621" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M621" s="9" t="inlineStr">
@@ -40571,7 +41046,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O621" s="9" t="n"/>
+      <c r="O621" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" s="9" t="n">
@@ -40606,7 +41085,7 @@
       </c>
       <c r="I622" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M622" s="9" t="inlineStr">
@@ -40619,7 +41098,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O622" s="9" t="n"/>
+      <c r="O622" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" s="9" t="n">
@@ -40654,7 +41137,7 @@
       </c>
       <c r="I623" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M623" s="9" t="inlineStr">
@@ -40667,7 +41150,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O623" s="9" t="n"/>
+      <c r="O623" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" s="9" t="n">
@@ -40702,7 +41189,7 @@
       </c>
       <c r="I624" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M624" s="9" t="inlineStr">
@@ -40715,7 +41202,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O624" s="9" t="n"/>
+      <c r="O624" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" s="9" t="n">
@@ -40750,7 +41241,7 @@
       </c>
       <c r="I625" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M625" s="9" t="inlineStr">
@@ -40763,7 +41254,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O625" s="9" t="n"/>
+      <c r="O625" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" s="9" t="n">
@@ -40798,7 +41293,7 @@
       </c>
       <c r="I626" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M626" s="9" t="inlineStr">
@@ -40811,7 +41306,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O626" s="9" t="n"/>
+      <c r="O626" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" s="9" t="n">
@@ -40846,7 +41345,7 @@
       </c>
       <c r="I627" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M627" s="9" t="inlineStr">
@@ -40859,7 +41358,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O627" s="9" t="n"/>
+      <c r="O627" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" s="9" t="n">
@@ -40894,7 +41397,7 @@
       </c>
       <c r="I628" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M628" s="9" t="inlineStr">
@@ -40907,7 +41410,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O628" s="9" t="n"/>
+      <c r="O628" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" s="9" t="n">
@@ -40942,7 +41449,7 @@
       </c>
       <c r="I629" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M629" s="9" t="inlineStr">
@@ -40955,7 +41462,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O629" s="9" t="n"/>
+      <c r="O629" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" s="9" t="n">
@@ -40990,7 +41501,7 @@
       </c>
       <c r="I630" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M630" s="9" t="inlineStr">
@@ -41003,7 +41514,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O630" s="9" t="n"/>
+      <c r="O630" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" s="9" t="n">
@@ -41038,7 +41553,7 @@
       </c>
       <c r="I631" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M631" s="9" t="inlineStr">
@@ -41051,7 +41566,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O631" s="9" t="n"/>
+      <c r="O631" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" s="9" t="n">
@@ -41086,7 +41605,7 @@
       </c>
       <c r="I632" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M632" s="9" t="inlineStr">
@@ -41099,7 +41618,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O632" s="9" t="n"/>
+      <c r="O632" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" s="9" t="n">
@@ -41134,7 +41657,7 @@
       </c>
       <c r="I633" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M633" s="9" t="inlineStr">
@@ -41147,7 +41670,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O633" s="9" t="n"/>
+      <c r="O633" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" s="9" t="n">
@@ -41182,7 +41709,7 @@
       </c>
       <c r="I634" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M634" s="9" t="inlineStr">
@@ -41195,7 +41722,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O634" s="9" t="n"/>
+      <c r="O634" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" s="9" t="n">
@@ -41230,7 +41761,7 @@
       </c>
       <c r="I635" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M635" s="9" t="inlineStr">
@@ -41243,7 +41774,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O635" s="9" t="n"/>
+      <c r="O635" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" s="9" t="n">
@@ -41278,7 +41813,7 @@
       </c>
       <c r="I636" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M636" s="9" t="inlineStr">
@@ -41291,7 +41826,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O636" s="9" t="n"/>
+      <c r="O636" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" s="9" t="n">
@@ -41326,7 +41865,7 @@
       </c>
       <c r="I637" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M637" s="9" t="inlineStr">
@@ -41339,7 +41878,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O637" s="9" t="n"/>
+      <c r="O637" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" s="9" t="n">
@@ -41374,7 +41917,7 @@
       </c>
       <c r="I638" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M638" s="9" t="inlineStr">
@@ -41387,7 +41930,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O638" s="9" t="n"/>
+      <c r="O638" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" s="9" t="n">
@@ -41422,7 +41969,7 @@
       </c>
       <c r="I639" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M639" s="9" t="inlineStr">
@@ -41435,7 +41982,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O639" s="9" t="n"/>
+      <c r="O639" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" s="9" t="n">
@@ -41470,7 +42021,7 @@
       </c>
       <c r="I640" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M640" s="9" t="inlineStr">
@@ -41483,7 +42034,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O640" s="9" t="n"/>
+      <c r="O640" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" s="9" t="n">
@@ -41518,7 +42073,7 @@
       </c>
       <c r="I641" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M641" s="9" t="inlineStr">
@@ -41531,7 +42086,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O641" s="9" t="n"/>
+      <c r="O641" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" s="9" t="n">
@@ -41566,7 +42125,7 @@
       </c>
       <c r="I642" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M642" s="9" t="inlineStr">
@@ -41579,7 +42138,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O642" s="9" t="n"/>
+      <c r="O642" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" s="9" t="n">
@@ -41614,7 +42177,7 @@
       </c>
       <c r="I643" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M643" s="9" t="inlineStr">
@@ -41627,7 +42190,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O643" s="9" t="n"/>
+      <c r="O643" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" s="9" t="n">
@@ -41662,7 +42229,7 @@
       </c>
       <c r="I644" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M644" s="9" t="inlineStr">
@@ -41675,7 +42242,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O644" s="9" t="n"/>
+      <c r="O644" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" s="9" t="n">
@@ -41710,7 +42281,7 @@
       </c>
       <c r="I645" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M645" s="9" t="inlineStr">
@@ -41723,7 +42294,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O645" s="9" t="n"/>
+      <c r="O645" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" s="9" t="n">
@@ -41758,7 +42333,7 @@
       </c>
       <c r="I646" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M646" s="9" t="inlineStr">
@@ -41771,7 +42346,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O646" s="9" t="n"/>
+      <c r="O646" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" s="9" t="n">
@@ -41806,7 +42385,7 @@
       </c>
       <c r="I647" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M647" s="9" t="inlineStr">
@@ -41819,7 +42398,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O647" s="9" t="n"/>
+      <c r="O647" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" s="9" t="n">
@@ -41854,7 +42437,7 @@
       </c>
       <c r="I648" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M648" s="9" t="inlineStr">
@@ -41867,7 +42450,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O648" s="9" t="n"/>
+      <c r="O648" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" s="9" t="n">
@@ -41902,7 +42489,7 @@
       </c>
       <c r="I649" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M649" s="9" t="inlineStr">
@@ -41915,7 +42502,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O649" s="9" t="n"/>
+      <c r="O649" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="A650" s="9" t="n">
@@ -41950,7 +42541,7 @@
       </c>
       <c r="I650" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M650" s="9" t="inlineStr">
@@ -41963,7 +42554,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O650" s="9" t="n"/>
+      <c r="O650" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" s="9" t="n">
@@ -41998,7 +42593,7 @@
       </c>
       <c r="I651" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M651" s="9" t="inlineStr">
@@ -42011,7 +42606,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O651" s="9" t="n"/>
+      <c r="O651" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" s="9" t="n">
@@ -42046,7 +42645,7 @@
       </c>
       <c r="I652" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M652" s="9" t="inlineStr">
@@ -42059,7 +42658,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O652" s="9" t="n"/>
+      <c r="O652" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" s="9" t="n">
@@ -42094,7 +42697,7 @@
       </c>
       <c r="I653" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M653" s="9" t="inlineStr">
@@ -42107,7 +42710,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O653" s="9" t="n"/>
+      <c r="O653" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" s="9" t="n">
@@ -42142,7 +42749,7 @@
       </c>
       <c r="I654" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M654" s="9" t="inlineStr">
@@ -42155,7 +42762,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O654" s="9" t="n"/>
+      <c r="O654" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" s="9" t="n">
@@ -42190,7 +42801,7 @@
       </c>
       <c r="I655" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M655" s="9" t="inlineStr">
@@ -42203,7 +42814,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O655" s="9" t="n"/>
+      <c r="O655" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" s="9" t="n">
@@ -42238,7 +42853,7 @@
       </c>
       <c r="I656" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M656" s="9" t="inlineStr">
@@ -42251,7 +42866,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O656" s="9" t="n"/>
+      <c r="O656" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" s="9" t="n">
@@ -42286,7 +42905,7 @@
       </c>
       <c r="I657" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M657" s="9" t="inlineStr">
@@ -42299,7 +42918,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O657" s="9" t="n"/>
+      <c r="O657" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" s="9" t="n">
@@ -42334,7 +42957,7 @@
       </c>
       <c r="I658" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M658" s="9" t="inlineStr">
@@ -42347,7 +42970,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O658" s="9" t="n"/>
+      <c r="O658" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" s="9" t="n">
@@ -42382,7 +43009,7 @@
       </c>
       <c r="I659" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M659" s="9" t="inlineStr">
@@ -42395,7 +43022,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O659" s="9" t="n"/>
+      <c r="O659" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" s="9" t="n">
@@ -42430,7 +43061,7 @@
       </c>
       <c r="I660" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M660" s="9" t="inlineStr">
@@ -42443,7 +43074,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O660" s="9" t="n"/>
+      <c r="O660" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" s="9" t="n">
@@ -42478,7 +43113,7 @@
       </c>
       <c r="I661" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M661" s="9" t="inlineStr">
@@ -42491,7 +43126,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O661" s="9" t="n"/>
+      <c r="O661" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" s="9" t="n">
@@ -42526,7 +43165,7 @@
       </c>
       <c r="I662" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M662" s="9" t="inlineStr">
@@ -42539,7 +43178,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O662" s="9" t="n"/>
+      <c r="O662" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" s="9" t="n">
@@ -42574,7 +43217,7 @@
       </c>
       <c r="I663" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M663" s="9" t="inlineStr">
@@ -42587,7 +43230,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O663" s="9" t="n"/>
+      <c r="O663" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" s="9" t="n">
@@ -42622,7 +43269,7 @@
       </c>
       <c r="I664" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M664" s="9" t="inlineStr">
@@ -42635,7 +43282,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O664" s="9" t="n"/>
+      <c r="O664" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" s="9" t="n">
@@ -42670,7 +43321,7 @@
       </c>
       <c r="I665" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M665" s="9" t="inlineStr">
@@ -42683,7 +43334,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O665" s="9" t="n"/>
+      <c r="O665" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" s="9" t="n">
@@ -42718,7 +43373,7 @@
       </c>
       <c r="I666" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M666" s="9" t="inlineStr">
@@ -42731,7 +43386,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O666" s="9" t="n"/>
+      <c r="O666" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" s="9" t="n">
@@ -42766,7 +43425,7 @@
       </c>
       <c r="I667" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M667" s="9" t="inlineStr">
@@ -42779,7 +43438,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O667" s="9" t="n"/>
+      <c r="O667" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" s="9" t="n">
@@ -42814,7 +43477,7 @@
       </c>
       <c r="I668" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M668" s="9" t="inlineStr">
@@ -42827,7 +43490,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O668" s="9" t="n"/>
+      <c r="O668" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" s="9" t="n">
@@ -42862,7 +43529,7 @@
       </c>
       <c r="I669" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M669" s="9" t="inlineStr">
@@ -42875,7 +43542,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O669" s="9" t="n"/>
+      <c r="O669" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" s="9" t="n">
@@ -42910,7 +43581,7 @@
       </c>
       <c r="I670" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M670" s="9" t="inlineStr">
@@ -42923,7 +43594,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O670" s="9" t="n"/>
+      <c r="O670" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" s="9" t="n">
@@ -42958,7 +43633,7 @@
       </c>
       <c r="I671" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M671" s="9" t="inlineStr">
@@ -42971,7 +43646,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O671" s="9" t="n"/>
+      <c r="O671" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" s="9" t="n">
@@ -43006,7 +43685,7 @@
       </c>
       <c r="I672" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M672" s="9" t="inlineStr">
@@ -43019,7 +43698,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O672" s="9" t="n"/>
+      <c r="O672" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" s="9" t="n">
@@ -43054,7 +43737,7 @@
       </c>
       <c r="I673" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M673" s="9" t="inlineStr">
@@ -43067,7 +43750,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O673" s="9" t="n"/>
+      <c r="O673" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="A674" s="9" t="n">
@@ -43102,7 +43789,7 @@
       </c>
       <c r="I674" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M674" s="9" t="inlineStr">
@@ -43115,7 +43802,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O674" s="9" t="n"/>
+      <c r="O674" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" s="9" t="n">
@@ -43150,7 +43841,7 @@
       </c>
       <c r="I675" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M675" s="9" t="inlineStr">
@@ -43163,7 +43854,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O675" s="9" t="n"/>
+      <c r="O675" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="676">
       <c r="A676" s="9" t="n">
@@ -43198,7 +43893,7 @@
       </c>
       <c r="I676" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M676" s="9" t="inlineStr">
@@ -43211,7 +43906,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O676" s="9" t="n"/>
+      <c r="O676" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" s="9" t="n">
@@ -43246,7 +43945,7 @@
       </c>
       <c r="I677" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M677" s="9" t="inlineStr">
@@ -43259,7 +43958,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O677" s="9" t="n"/>
+      <c r="O677" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="A678" s="9" t="n">
@@ -43294,7 +43997,7 @@
       </c>
       <c r="I678" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M678" s="9" t="inlineStr">
@@ -43307,7 +44010,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O678" s="9" t="n"/>
+      <c r="O678" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="679">
       <c r="A679" s="9" t="n">
@@ -43342,7 +44049,7 @@
       </c>
       <c r="I679" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M679" s="9" t="inlineStr">
@@ -43355,7 +44062,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O679" s="9" t="n"/>
+      <c r="O679" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="680">
       <c r="A680" s="9" t="n">
@@ -43390,7 +44101,7 @@
       </c>
       <c r="I680" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M680" s="9" t="inlineStr">
@@ -43403,7 +44114,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O680" s="9" t="n"/>
+      <c r="O680" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" s="9" t="n">
@@ -43438,7 +44153,7 @@
       </c>
       <c r="I681" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M681" s="9" t="inlineStr">
@@ -43451,7 +44166,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O681" s="9" t="n"/>
+      <c r="O681" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" s="9" t="n">
@@ -43486,7 +44205,7 @@
       </c>
       <c r="I682" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M682" s="9" t="inlineStr">
@@ -43499,7 +44218,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O682" s="9" t="n"/>
+      <c r="O682" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" s="9" t="n">
@@ -43534,7 +44257,7 @@
       </c>
       <c r="I683" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M683" s="9" t="inlineStr">
@@ -43547,7 +44270,11 @@
           <t>AICTE UG Supplemental list - verified against official site</t>
         </is>
       </c>
-      <c r="O683" s="9" t="n"/>
+      <c r="O683" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" s="9" t="n">
@@ -43582,7 +44309,7 @@
       </c>
       <c r="I684" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M684" s="9" t="inlineStr">
@@ -43593,6 +44320,11 @@
       <c r="N684" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O684" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -43629,7 +44361,7 @@
       </c>
       <c r="I685" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M685" s="9" t="inlineStr">
@@ -43640,6 +44372,11 @@
       <c r="N685" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O685" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -43676,7 +44413,7 @@
       </c>
       <c r="I686" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M686" s="9" t="inlineStr">
@@ -43687,6 +44424,11 @@
       <c r="N686" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O686" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -43723,7 +44465,7 @@
       </c>
       <c r="I687" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M687" s="9" t="inlineStr">
@@ -43734,6 +44476,11 @@
       <c r="N687" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O687" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -43770,7 +44517,7 @@
       </c>
       <c r="I688" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M688" s="9" t="inlineStr">
@@ -43781,6 +44528,11 @@
       <c r="N688" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O688" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -43817,7 +44569,7 @@
       </c>
       <c r="I689" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M689" s="9" t="inlineStr">
@@ -43828,6 +44580,11 @@
       <c r="N689" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O689" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -43864,7 +44621,7 @@
       </c>
       <c r="I690" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M690" s="9" t="inlineStr">
@@ -43875,6 +44632,11 @@
       <c r="N690" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O690" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -43911,7 +44673,7 @@
       </c>
       <c r="I691" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M691" s="9" t="inlineStr">
@@ -43922,6 +44684,11 @@
       <c r="N691" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O691" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -43958,7 +44725,7 @@
       </c>
       <c r="I692" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M692" s="9" t="inlineStr">
@@ -43969,6 +44736,11 @@
       <c r="N692" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O692" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -44005,7 +44777,7 @@
       </c>
       <c r="I693" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M693" s="9" t="inlineStr">
@@ -44016,6 +44788,11 @@
       <c r="N693" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O693" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -44052,7 +44829,7 @@
       </c>
       <c r="I694" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M694" s="9" t="inlineStr">
@@ -44063,6 +44840,11 @@
       <c r="N694" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O694" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -44099,7 +44881,7 @@
       </c>
       <c r="I695" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M695" s="9" t="inlineStr">
@@ -44110,6 +44892,11 @@
       <c r="N695" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O695" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -44146,7 +44933,7 @@
       </c>
       <c r="I696" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M696" s="9" t="inlineStr">
@@ -44157,6 +44944,11 @@
       <c r="N696" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O696" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -44193,7 +44985,7 @@
       </c>
       <c r="I697" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M697" s="9" t="inlineStr">
@@ -44204,6 +44996,11 @@
       <c r="N697" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O697" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -44240,7 +45037,7 @@
       </c>
       <c r="I698" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M698" s="9" t="inlineStr">
@@ -44251,6 +45048,11 @@
       <c r="N698" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O698" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -44287,7 +45089,7 @@
       </c>
       <c r="I699" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M699" s="9" t="inlineStr">
@@ -44298,6 +45100,11 @@
       <c r="N699" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O699" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -44334,7 +45141,7 @@
       </c>
       <c r="I700" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M700" s="9" t="inlineStr">
@@ -44345,6 +45152,11 @@
       <c r="N700" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O700" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -44381,7 +45193,7 @@
       </c>
       <c r="I701" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M701" s="9" t="inlineStr">
@@ -44392,6 +45204,11 @@
       <c r="N701" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O701" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -44428,7 +45245,7 @@
       </c>
       <c r="I702" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M702" s="9" t="inlineStr">
@@ -44439,6 +45256,11 @@
       <c r="N702" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O702" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -44475,7 +45297,7 @@
       </c>
       <c r="I703" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M703" s="9" t="inlineStr">
@@ -44486,6 +45308,11 @@
       <c r="N703" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O703" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -44522,7 +45349,7 @@
       </c>
       <c r="I704" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M704" s="9" t="inlineStr">
@@ -44533,6 +45360,11 @@
       <c r="N704" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O704" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -44569,7 +45401,7 @@
       </c>
       <c r="I705" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M705" s="9" t="inlineStr">
@@ -44580,6 +45412,11 @@
       <c r="N705" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O705" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -44616,7 +45453,7 @@
       </c>
       <c r="I706" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M706" s="9" t="inlineStr">
@@ -44627,6 +45464,11 @@
       <c r="N706" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O706" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -44663,7 +45505,7 @@
       </c>
       <c r="I707" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M707" s="9" t="inlineStr">
@@ -44674,6 +45516,11 @@
       <c r="N707" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O707" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -44710,7 +45557,7 @@
       </c>
       <c r="I708" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M708" s="9" t="inlineStr">
@@ -44721,6 +45568,11 @@
       <c r="N708" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O708" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -44757,7 +45609,7 @@
       </c>
       <c r="I709" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M709" s="9" t="inlineStr">
@@ -44768,6 +45620,11 @@
       <c r="N709" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O709" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -44804,7 +45661,7 @@
       </c>
       <c r="I710" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M710" s="9" t="inlineStr">
@@ -44815,6 +45672,11 @@
       <c r="N710" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O710" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -44851,7 +45713,7 @@
       </c>
       <c r="I711" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M711" s="9" t="inlineStr">
@@ -44862,6 +45724,11 @@
       <c r="N711" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O711" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -44898,7 +45765,7 @@
       </c>
       <c r="I712" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M712" s="9" t="inlineStr">
@@ -44909,6 +45776,11 @@
       <c r="N712" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O712" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -44945,7 +45817,7 @@
       </c>
       <c r="I713" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M713" s="9" t="inlineStr">
@@ -44956,6 +45828,11 @@
       <c r="N713" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O713" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -44992,7 +45869,7 @@
       </c>
       <c r="I714" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M714" s="9" t="inlineStr">
@@ -45003,6 +45880,11 @@
       <c r="N714" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O714" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -45039,7 +45921,7 @@
       </c>
       <c r="I715" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M715" s="9" t="inlineStr">
@@ -45050,6 +45932,11 @@
       <c r="N715" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O715" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -45086,7 +45973,7 @@
       </c>
       <c r="I716" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M716" s="9" t="inlineStr">
@@ -45097,6 +45984,11 @@
       <c r="N716" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O716" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -45133,7 +46025,7 @@
       </c>
       <c r="I717" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M717" s="9" t="inlineStr">
@@ -45144,6 +46036,11 @@
       <c r="N717" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O717" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -45180,7 +46077,7 @@
       </c>
       <c r="I718" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M718" s="9" t="inlineStr">
@@ -45191,6 +46088,11 @@
       <c r="N718" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O718" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -45227,7 +46129,7 @@
       </c>
       <c r="I719" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M719" s="9" t="inlineStr">
@@ -45238,6 +46140,11 @@
       <c r="N719" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O719" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -45274,7 +46181,7 @@
       </c>
       <c r="I720" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M720" s="9" t="inlineStr">
@@ -45285,6 +46192,11 @@
       <c r="N720" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O720" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -45321,7 +46233,7 @@
       </c>
       <c r="I721" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M721" s="9" t="inlineStr">
@@ -45332,6 +46244,11 @@
       <c r="N721" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O721" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -45368,7 +46285,7 @@
       </c>
       <c r="I722" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M722" s="9" t="inlineStr">
@@ -45379,6 +46296,11 @@
       <c r="N722" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O722" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -45415,7 +46337,7 @@
       </c>
       <c r="I723" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M723" s="9" t="inlineStr">
@@ -45426,6 +46348,11 @@
       <c r="N723" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O723" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -45462,7 +46389,7 @@
       </c>
       <c r="I724" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M724" s="9" t="inlineStr">
@@ -45473,6 +46400,11 @@
       <c r="N724" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O724" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -45509,7 +46441,7 @@
       </c>
       <c r="I725" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M725" s="9" t="inlineStr">
@@ -45520,6 +46452,11 @@
       <c r="N725" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O725" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -45556,7 +46493,7 @@
       </c>
       <c r="I726" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M726" s="9" t="inlineStr">
@@ -45567,6 +46504,11 @@
       <c r="N726" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O726" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -45603,7 +46545,7 @@
       </c>
       <c r="I727" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M727" s="9" t="inlineStr">
@@ -45614,6 +46556,11 @@
       <c r="N727" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O727" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -45650,7 +46597,7 @@
       </c>
       <c r="I728" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M728" s="9" t="inlineStr">
@@ -45661,6 +46608,11 @@
       <c r="N728" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O728" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -45697,7 +46649,7 @@
       </c>
       <c r="I729" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M729" s="9" t="inlineStr">
@@ -45708,6 +46660,11 @@
       <c r="N729" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O729" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -45744,7 +46701,7 @@
       </c>
       <c r="I730" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M730" s="9" t="inlineStr">
@@ -45755,6 +46712,11 @@
       <c r="N730" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O730" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -45791,7 +46753,7 @@
       </c>
       <c r="I731" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M731" s="9" t="inlineStr">
@@ -45802,6 +46764,11 @@
       <c r="N731" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O731" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -45838,7 +46805,7 @@
       </c>
       <c r="I732" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M732" s="9" t="inlineStr">
@@ -45849,6 +46816,11 @@
       <c r="N732" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O732" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -45885,7 +46857,7 @@
       </c>
       <c r="I733" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M733" s="9" t="inlineStr">
@@ -45896,6 +46868,11 @@
       <c r="N733" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O733" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -45932,7 +46909,7 @@
       </c>
       <c r="I734" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M734" s="9" t="inlineStr">
@@ -45943,6 +46920,11 @@
       <c r="N734" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O734" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -45979,7 +46961,7 @@
       </c>
       <c r="I735" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M735" s="9" t="inlineStr">
@@ -45990,6 +46972,11 @@
       <c r="N735" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O735" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -46026,7 +47013,7 @@
       </c>
       <c r="I736" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M736" s="9" t="inlineStr">
@@ -46037,6 +47024,11 @@
       <c r="N736" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O736" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -46073,7 +47065,7 @@
       </c>
       <c r="I737" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M737" s="9" t="inlineStr">
@@ -46084,6 +47076,11 @@
       <c r="N737" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O737" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -46120,7 +47117,7 @@
       </c>
       <c r="I738" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M738" s="9" t="inlineStr">
@@ -46131,6 +47128,11 @@
       <c r="N738" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O738" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -46167,7 +47169,7 @@
       </c>
       <c r="I739" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M739" s="9" t="inlineStr">
@@ -46178,6 +47180,11 @@
       <c r="N739" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O739" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -46214,7 +47221,7 @@
       </c>
       <c r="I740" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M740" s="9" t="inlineStr">
@@ -46225,6 +47232,11 @@
       <c r="N740" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O740" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -46261,7 +47273,7 @@
       </c>
       <c r="I741" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M741" s="9" t="inlineStr">
@@ -46272,6 +47284,11 @@
       <c r="N741" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O741" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -46308,7 +47325,7 @@
       </c>
       <c r="I742" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M742" s="9" t="inlineStr">
@@ -46319,6 +47336,11 @@
       <c r="N742" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O742" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -46355,7 +47377,7 @@
       </c>
       <c r="I743" s="9" t="inlineStr">
         <is>
-          <t>Drafted (not sent)</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="M743" s="9" t="inlineStr">
@@ -46366,6 +47388,11 @@
       <c r="N743" s="9" t="inlineStr">
         <is>
           <t>AICTE UG Supplemental list - verified against official site</t>
+        </is>
+      </c>
+      <c r="O743" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -46408,7 +47435,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>289</v>
+        <v>511</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="10">
@@ -46438,7 +47465,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="10">

--- a/data/Incubation_Outreach_Tracker.xlsx
+++ b/data/Incubation_Outreach_Tracker.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q743"/>
+  <dimension ref="A1:Q892"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="9" min="1" max="1"/>
@@ -10770,17 +10770,29 @@
         </is>
       </c>
       <c r="G166" s="14" t="n"/>
-      <c r="H166" s="14" t="n"/>
+      <c r="H166" s="14" t="inlineStr">
+        <is>
+          <t>squinfo@squ.edu.om</t>
+        </is>
+      </c>
       <c r="I166" s="14" t="inlineStr">
         <is>
-          <t>Blocked: contact form only</t>
+          <t>On hold (prior contact)</t>
         </is>
       </c>
       <c r="J166" s="14" t="n"/>
       <c r="K166" s="14" t="n"/>
       <c r="L166" s="14" t="n"/>
-      <c r="M166" s="14" t="n"/>
-      <c r="N166" s="14" t="n"/>
+      <c r="M166" s="14" t="inlineStr">
+        <is>
+          <t>https://jeps.squ.edu.om/journal/contact</t>
+        </is>
+      </c>
+      <c r="N166" s="14" t="inlineStr">
+        <is>
+          <t>Previously blocked (contact form only); general email now found in follow-up research | Prior contact found (sent 2026-09-26 to abusaid@squ.edu.om)</t>
+        </is>
+      </c>
       <c r="O166" s="14" t="n"/>
       <c r="P166" s="13" t="n"/>
       <c r="Q166" s="13" t="n"/>
@@ -10970,17 +10982,41 @@
         </is>
       </c>
       <c r="G170" s="14" t="n"/>
-      <c r="H170" s="14" t="n"/>
+      <c r="H170" s="14" t="inlineStr">
+        <is>
+          <t>admissions@aubh.edu.bh</t>
+        </is>
+      </c>
       <c r="I170" s="14" t="inlineStr">
         <is>
-          <t>Blocked: no email found</t>
-        </is>
-      </c>
-      <c r="J170" s="14" t="n"/>
-      <c r="K170" s="14" t="n"/>
-      <c r="L170" s="14" t="n"/>
-      <c r="M170" s="14" t="n"/>
-      <c r="N170" s="14" t="n"/>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J170" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K170" s="14" t="inlineStr">
+        <is>
+          <t>External Mentor for American University of Bahrain</t>
+        </is>
+      </c>
+      <c r="L170" s="14" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M170" s="14" t="inlineStr">
+        <is>
+          <t>https://aubh.edu.bh/contact</t>
+        </is>
+      </c>
+      <c r="N170" s="14" t="inlineStr">
+        <is>
+          <t>Previously blocked (no email found); admissions email now found in follow-up research</t>
+        </is>
+      </c>
       <c r="O170" s="14" t="n"/>
       <c r="P170" s="13" t="n"/>
       <c r="Q170" s="13" t="n"/>
@@ -47395,6 +47431,9643 @@
           <t>2026-09-27</t>
         </is>
       </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="9" t="n">
+        <v>743</v>
+      </c>
+      <c r="B744" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C744" s="9" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D744" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E744" s="9" t="inlineStr">
+        <is>
+          <t>Zayed University - Abu Dhabi Campus</t>
+        </is>
+      </c>
+      <c r="F744" s="9" t="inlineStr"/>
+      <c r="G744" s="9" t="inlineStr"/>
+      <c r="H744" s="9" t="inlineStr">
+        <is>
+          <t>dgs@zu.ac.ae</t>
+        </is>
+      </c>
+      <c r="I744" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J744" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K744" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Zayed University - Abu Dhabi Campus</t>
+        </is>
+      </c>
+      <c r="L744" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M744" s="9" t="inlineStr">
+        <is>
+          <t>https://www.zu.ac.ae/main/en/gsd/contact-us</t>
+        </is>
+      </c>
+      <c r="N744" s="9" t="inlineStr">
+        <is>
+          <t>Deanship of Graduate Studies</t>
+        </is>
+      </c>
+      <c r="O744" s="9" t="inlineStr"/>
+      <c r="P744" s="9" t="inlineStr"/>
+      <c r="Q744" s="9" t="inlineStr"/>
+    </row>
+    <row r="745">
+      <c r="A745" s="9" t="n">
+        <v>744</v>
+      </c>
+      <c r="B745" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C745" s="9" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D745" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E745" s="9" t="inlineStr">
+        <is>
+          <t>Abu Dhabi University</t>
+        </is>
+      </c>
+      <c r="F745" s="9" t="inlineStr"/>
+      <c r="G745" s="9" t="inlineStr"/>
+      <c r="H745" s="9" t="inlineStr">
+        <is>
+          <t>admissions@adu.ac.ae</t>
+        </is>
+      </c>
+      <c r="I745" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J745" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K745" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Abu Dhabi University</t>
+        </is>
+      </c>
+      <c r="L745" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M745" s="9" t="inlineStr">
+        <is>
+          <t>https://www.adu.ac.ae/about-adu/get-in-touch1/get-in-touch</t>
+        </is>
+      </c>
+      <c r="N745" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O745" s="9" t="inlineStr"/>
+      <c r="P745" s="9" t="inlineStr"/>
+      <c r="Q745" s="9" t="inlineStr"/>
+    </row>
+    <row r="746">
+      <c r="A746" s="9" t="n">
+        <v>745</v>
+      </c>
+      <c r="B746" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C746" s="9" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D746" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E746" s="9" t="inlineStr">
+        <is>
+          <t>Al Ain University</t>
+        </is>
+      </c>
+      <c r="F746" s="9" t="inlineStr"/>
+      <c r="G746" s="9" t="inlineStr"/>
+      <c r="H746" s="9" t="inlineStr">
+        <is>
+          <t>engineering@aau.ac.ae</t>
+        </is>
+      </c>
+      <c r="I746" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J746" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K746" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Al Ain University</t>
+        </is>
+      </c>
+      <c r="L746" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M746" s="9" t="inlineStr">
+        <is>
+          <t>https://engineering.aau.ac.ae/en/about-the-college/contact-us</t>
+        </is>
+      </c>
+      <c r="N746" s="9" t="inlineStr">
+        <is>
+          <t>College of Engineering</t>
+        </is>
+      </c>
+      <c r="O746" s="9" t="inlineStr"/>
+      <c r="P746" s="9" t="inlineStr"/>
+      <c r="Q746" s="9" t="inlineStr"/>
+    </row>
+    <row r="747">
+      <c r="A747" s="9" t="n">
+        <v>746</v>
+      </c>
+      <c r="B747" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C747" s="9" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D747" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E747" s="9" t="inlineStr">
+        <is>
+          <t>New York University Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F747" s="9" t="inlineStr"/>
+      <c r="G747" s="9" t="inlineStr"/>
+      <c r="H747" s="9" t="inlineStr">
+        <is>
+          <t>nyuad@nyu.edu</t>
+        </is>
+      </c>
+      <c r="I747" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J747" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K747" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for New York University Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="L747" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M747" s="9" t="inlineStr">
+        <is>
+          <t>https://nyuad.nyu.edu/en/about/contact-and-location/contact.html</t>
+        </is>
+      </c>
+      <c r="N747" s="9" t="inlineStr">
+        <is>
+          <t>General Welcome Center</t>
+        </is>
+      </c>
+      <c r="O747" s="9" t="inlineStr"/>
+      <c r="P747" s="9" t="inlineStr"/>
+      <c r="Q747" s="9" t="inlineStr"/>
+    </row>
+    <row r="748">
+      <c r="A748" s="9" t="n">
+        <v>747</v>
+      </c>
+      <c r="B748" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C748" s="9" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D748" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E748" s="9" t="inlineStr">
+        <is>
+          <t>Rabdan Academy</t>
+        </is>
+      </c>
+      <c r="F748" s="9" t="inlineStr"/>
+      <c r="G748" s="9" t="inlineStr"/>
+      <c r="H748" s="9" t="inlineStr">
+        <is>
+          <t>info@ra.ac.ae</t>
+        </is>
+      </c>
+      <c r="I748" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J748" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K748" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Rabdan Academy</t>
+        </is>
+      </c>
+      <c r="L748" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M748" s="9" t="inlineStr">
+        <is>
+          <t>https://ra.ac.ae/en/contact-us</t>
+        </is>
+      </c>
+      <c r="N748" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O748" s="9" t="inlineStr"/>
+      <c r="P748" s="9" t="inlineStr"/>
+      <c r="Q748" s="9" t="inlineStr"/>
+    </row>
+    <row r="749">
+      <c r="A749" s="9" t="n">
+        <v>748</v>
+      </c>
+      <c r="B749" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C749" s="9" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D749" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E749" s="9" t="inlineStr">
+        <is>
+          <t>Zayed University - Dubai Campus</t>
+        </is>
+      </c>
+      <c r="F749" s="9" t="inlineStr"/>
+      <c r="G749" s="9" t="inlineStr"/>
+      <c r="H749" s="9" t="inlineStr">
+        <is>
+          <t>dgs@zu.ac.ae</t>
+        </is>
+      </c>
+      <c r="I749" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J749" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K749" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Zayed University - Dubai Campus</t>
+        </is>
+      </c>
+      <c r="L749" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M749" s="9" t="inlineStr">
+        <is>
+          <t>https://www.zu.ac.ae/main/en/gsd/contact-us</t>
+        </is>
+      </c>
+      <c r="N749" s="9" t="inlineStr">
+        <is>
+          <t>Institution-wide graduate studies contact</t>
+        </is>
+      </c>
+      <c r="O749" s="9" t="inlineStr"/>
+      <c r="P749" s="9" t="inlineStr"/>
+      <c r="Q749" s="9" t="inlineStr"/>
+    </row>
+    <row r="750">
+      <c r="A750" s="9" t="n">
+        <v>749</v>
+      </c>
+      <c r="B750" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C750" s="9" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D750" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E750" s="9" t="inlineStr">
+        <is>
+          <t>Emirates Aviation University</t>
+        </is>
+      </c>
+      <c r="F750" s="9" t="inlineStr"/>
+      <c r="G750" s="9" t="inlineStr"/>
+      <c r="H750" s="9" t="inlineStr">
+        <is>
+          <t>eau.info@emirates.com</t>
+        </is>
+      </c>
+      <c r="I750" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J750" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K750" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Emirates Aviation University</t>
+        </is>
+      </c>
+      <c r="L750" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M750" s="9" t="inlineStr">
+        <is>
+          <t>https://www.eau.ac.ae/en/contact-us/?id=1555987</t>
+        </is>
+      </c>
+      <c r="N750" s="9" t="inlineStr">
+        <is>
+          <t>General information</t>
+        </is>
+      </c>
+      <c r="O750" s="9" t="inlineStr"/>
+      <c r="P750" s="9" t="inlineStr"/>
+      <c r="Q750" s="9" t="inlineStr"/>
+    </row>
+    <row r="751">
+      <c r="A751" s="9" t="n">
+        <v>750</v>
+      </c>
+      <c r="B751" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C751" s="9" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D751" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E751" s="9" t="inlineStr">
+        <is>
+          <t>Canadian University Dubai</t>
+        </is>
+      </c>
+      <c r="F751" s="9" t="inlineStr"/>
+      <c r="G751" s="9" t="inlineStr"/>
+      <c r="H751" s="9" t="inlineStr">
+        <is>
+          <t>info@cud.ac.ae</t>
+        </is>
+      </c>
+      <c r="I751" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J751" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K751" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Canadian University Dubai</t>
+        </is>
+      </c>
+      <c r="L751" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M751" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cud.ac.ae/contact</t>
+        </is>
+      </c>
+      <c r="N751" s="9" t="inlineStr">
+        <is>
+          <t>Official general contact</t>
+        </is>
+      </c>
+      <c r="O751" s="9" t="inlineStr"/>
+      <c r="P751" s="9" t="inlineStr"/>
+      <c r="Q751" s="9" t="inlineStr"/>
+    </row>
+    <row r="752">
+      <c r="A752" s="9" t="n">
+        <v>751</v>
+      </c>
+      <c r="B752" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C752" s="9" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D752" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E752" s="9" t="inlineStr">
+        <is>
+          <t>British University in Dubai</t>
+        </is>
+      </c>
+      <c r="F752" s="9" t="inlineStr"/>
+      <c r="G752" s="9" t="inlineStr"/>
+      <c r="H752" s="9" t="inlineStr">
+        <is>
+          <t>ug.admissions@buid.ac.ae</t>
+        </is>
+      </c>
+      <c r="I752" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J752" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K752" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for British University in Dubai</t>
+        </is>
+      </c>
+      <c r="L752" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M752" s="9" t="inlineStr">
+        <is>
+          <t>https://www.buid.ac.ae/discover-buid/contact-us/</t>
+        </is>
+      </c>
+      <c r="N752" s="9" t="inlineStr">
+        <is>
+          <t>Undergrad admissions (main email obfuscated)</t>
+        </is>
+      </c>
+      <c r="O752" s="9" t="inlineStr"/>
+      <c r="P752" s="9" t="inlineStr"/>
+      <c r="Q752" s="9" t="inlineStr"/>
+    </row>
+    <row r="753">
+      <c r="A753" s="9" t="n">
+        <v>752</v>
+      </c>
+      <c r="B753" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C753" s="9" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D753" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E753" s="9" t="inlineStr">
+        <is>
+          <t>Murdoch University Dubai</t>
+        </is>
+      </c>
+      <c r="F753" s="9" t="inlineStr"/>
+      <c r="G753" s="9" t="inlineStr"/>
+      <c r="H753" s="9" t="inlineStr">
+        <is>
+          <t>info@murdochuniversitydubai.com</t>
+        </is>
+      </c>
+      <c r="I753" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J753" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K753" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Murdoch University Dubai</t>
+        </is>
+      </c>
+      <c r="L753" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M753" s="9" t="inlineStr">
+        <is>
+          <t>https://www.murdochuniversitydubai.com/contact/</t>
+        </is>
+      </c>
+      <c r="N753" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O753" s="9" t="inlineStr"/>
+      <c r="P753" s="9" t="inlineStr"/>
+      <c r="Q753" s="9" t="inlineStr"/>
+    </row>
+    <row r="754">
+      <c r="A754" s="9" t="n">
+        <v>753</v>
+      </c>
+      <c r="B754" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C754" s="9" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D754" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E754" s="9" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology Dubai</t>
+        </is>
+      </c>
+      <c r="F754" s="9" t="inlineStr"/>
+      <c r="G754" s="9" t="inlineStr"/>
+      <c r="H754" s="9" t="inlineStr">
+        <is>
+          <t>dubai@rit.edu</t>
+        </is>
+      </c>
+      <c r="I754" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J754" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K754" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Rochester Institute of Technology Dubai</t>
+        </is>
+      </c>
+      <c r="L754" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M754" s="9" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/dubai/about-rit</t>
+        </is>
+      </c>
+      <c r="N754" s="9" t="inlineStr">
+        <is>
+          <t>General campus contact</t>
+        </is>
+      </c>
+      <c r="O754" s="9" t="inlineStr"/>
+      <c r="P754" s="9" t="inlineStr"/>
+      <c r="Q754" s="9" t="inlineStr"/>
+    </row>
+    <row r="755">
+      <c r="A755" s="9" t="n">
+        <v>754</v>
+      </c>
+      <c r="B755" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C755" s="9" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D755" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E755" s="9" t="inlineStr">
+        <is>
+          <t>Manipal Academy of Higher Education Dubai</t>
+        </is>
+      </c>
+      <c r="F755" s="9" t="inlineStr"/>
+      <c r="G755" s="9" t="inlineStr"/>
+      <c r="H755" s="9" t="inlineStr">
+        <is>
+          <t>info@manipaldubai.com</t>
+        </is>
+      </c>
+      <c r="I755" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J755" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K755" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Manipal Academy of Higher Education Dubai</t>
+        </is>
+      </c>
+      <c r="L755" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M755" s="9" t="inlineStr">
+        <is>
+          <t>https://www.manipaldubai.com/contact-us</t>
+        </is>
+      </c>
+      <c r="N755" s="9" t="inlineStr">
+        <is>
+          <t>General info; admissions@manipaldubai.com also listed</t>
+        </is>
+      </c>
+      <c r="O755" s="9" t="inlineStr"/>
+      <c r="P755" s="9" t="inlineStr"/>
+      <c r="Q755" s="9" t="inlineStr"/>
+    </row>
+    <row r="756">
+      <c r="A756" s="9" t="n">
+        <v>755</v>
+      </c>
+      <c r="B756" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C756" s="9" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D756" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E756" s="9" t="inlineStr">
+        <is>
+          <t>University of Kalba</t>
+        </is>
+      </c>
+      <c r="F756" s="9" t="inlineStr"/>
+      <c r="G756" s="9" t="inlineStr"/>
+      <c r="H756" s="9" t="inlineStr">
+        <is>
+          <t>info@ukb.ac.ae</t>
+        </is>
+      </c>
+      <c r="I756" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J756" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K756" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Kalba</t>
+        </is>
+      </c>
+      <c r="L756" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M756" s="9" t="inlineStr">
+        <is>
+          <t>https://ukb.ac.ae/en/contact-us</t>
+        </is>
+      </c>
+      <c r="N756" s="9" t="inlineStr">
+        <is>
+          <t>Primary contact email</t>
+        </is>
+      </c>
+      <c r="O756" s="9" t="inlineStr"/>
+      <c r="P756" s="9" t="inlineStr"/>
+      <c r="Q756" s="9" t="inlineStr"/>
+    </row>
+    <row r="757">
+      <c r="A757" s="9" t="n">
+        <v>756</v>
+      </c>
+      <c r="B757" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C757" s="9" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D757" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E757" s="9" t="inlineStr">
+        <is>
+          <t>Gulf Medical University</t>
+        </is>
+      </c>
+      <c r="F757" s="9" t="inlineStr"/>
+      <c r="G757" s="9" t="inlineStr"/>
+      <c r="H757" s="9" t="inlineStr">
+        <is>
+          <t>admissions@gmu.ac.ae</t>
+        </is>
+      </c>
+      <c r="I757" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J757" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K757" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Gulf Medical University</t>
+        </is>
+      </c>
+      <c r="L757" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M757" s="9" t="inlineStr">
+        <is>
+          <t>https://gmu.ac.ae/aboutgmu/contact-us/</t>
+        </is>
+      </c>
+      <c r="N757" s="9" t="inlineStr">
+        <is>
+          <t>Also registrar@gmu.ac.ae, hr@gmu.ac.ae</t>
+        </is>
+      </c>
+      <c r="O757" s="9" t="inlineStr"/>
+      <c r="P757" s="9" t="inlineStr"/>
+      <c r="Q757" s="9" t="inlineStr"/>
+    </row>
+    <row r="758">
+      <c r="A758" s="9" t="n">
+        <v>757</v>
+      </c>
+      <c r="B758" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C758" s="9" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D758" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E758" s="9" t="inlineStr">
+        <is>
+          <t>American University of Ras Al Khaimah (AURAK)</t>
+        </is>
+      </c>
+      <c r="F758" s="9" t="inlineStr"/>
+      <c r="G758" s="9" t="inlineStr"/>
+      <c r="H758" s="9" t="inlineStr">
+        <is>
+          <t>inquiry@aurak.ac.ae</t>
+        </is>
+      </c>
+      <c r="I758" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J758" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K758" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for American University of Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="L758" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M758" s="9" t="inlineStr">
+        <is>
+          <t>https://aurak.ac.ae/contact</t>
+        </is>
+      </c>
+      <c r="N758" s="9" t="inlineStr">
+        <is>
+          <t>General inquiries</t>
+        </is>
+      </c>
+      <c r="O758" s="9" t="inlineStr"/>
+      <c r="P758" s="9" t="inlineStr"/>
+      <c r="Q758" s="9" t="inlineStr"/>
+    </row>
+    <row r="759">
+      <c r="A759" s="9" t="n">
+        <v>758</v>
+      </c>
+      <c r="B759" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C759" s="9" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D759" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E759" s="9" t="inlineStr">
+        <is>
+          <t>Ras Al Khaimah Medical and Health Sciences University</t>
+        </is>
+      </c>
+      <c r="F759" s="9" t="inlineStr"/>
+      <c r="G759" s="9" t="inlineStr"/>
+      <c r="H759" s="9" t="inlineStr">
+        <is>
+          <t>info@rakmhsu.ac.ae</t>
+        </is>
+      </c>
+      <c r="I759" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J759" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K759" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Ras Al Khaimah Medical and Health Sciences University</t>
+        </is>
+      </c>
+      <c r="L759" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M759" s="9" t="inlineStr">
+        <is>
+          <t>https://www.rakmhsu.ac.ae/contact</t>
+        </is>
+      </c>
+      <c r="N759" s="9" t="inlineStr">
+        <is>
+          <t>General inquiries</t>
+        </is>
+      </c>
+      <c r="O759" s="9" t="inlineStr"/>
+      <c r="P759" s="9" t="inlineStr"/>
+      <c r="Q759" s="9" t="inlineStr"/>
+    </row>
+    <row r="760">
+      <c r="A760" s="9" t="n">
+        <v>759</v>
+      </c>
+      <c r="B760" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C760" s="9" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D760" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E760" s="9" t="inlineStr">
+        <is>
+          <t>Saudi Electronic University</t>
+        </is>
+      </c>
+      <c r="F760" s="9" t="inlineStr"/>
+      <c r="G760" s="9" t="inlineStr"/>
+      <c r="H760" s="9" t="inlineStr">
+        <is>
+          <t>DL@seu.edu.sa</t>
+        </is>
+      </c>
+      <c r="I760" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J760" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K760" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Saudi Electronic University</t>
+        </is>
+      </c>
+      <c r="L760" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M760" s="9" t="inlineStr">
+        <is>
+          <t>https://seu.edu.sa/en/administrations/knowledge-resource-administration/contact-us/</t>
+        </is>
+      </c>
+      <c r="N760" s="9" t="inlineStr">
+        <is>
+          <t>Knowledge Resource Admin; portal also at contactus.seu.edu.sa</t>
+        </is>
+      </c>
+      <c r="O760" s="9" t="inlineStr"/>
+      <c r="P760" s="9" t="inlineStr"/>
+      <c r="Q760" s="9" t="inlineStr"/>
+    </row>
+    <row r="761">
+      <c r="A761" s="9" t="n">
+        <v>760</v>
+      </c>
+      <c r="B761" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C761" s="9" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D761" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E761" s="9" t="inlineStr">
+        <is>
+          <t>University of Jeddah</t>
+        </is>
+      </c>
+      <c r="F761" s="9" t="inlineStr"/>
+      <c r="G761" s="9" t="inlineStr"/>
+      <c r="H761" s="9" t="inlineStr">
+        <is>
+          <t>info@uj.edu.sa</t>
+        </is>
+      </c>
+      <c r="I761" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J761" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K761" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Jeddah</t>
+        </is>
+      </c>
+      <c r="L761" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M761" s="9" t="inlineStr">
+        <is>
+          <t>https://www.uj.edu.sa/en/contact-us</t>
+        </is>
+      </c>
+      <c r="N761" s="9" t="inlineStr">
+        <is>
+          <t>General inquiries</t>
+        </is>
+      </c>
+      <c r="O761" s="9" t="inlineStr"/>
+      <c r="P761" s="9" t="inlineStr"/>
+      <c r="Q761" s="9" t="inlineStr"/>
+    </row>
+    <row r="762">
+      <c r="A762" s="9" t="n">
+        <v>761</v>
+      </c>
+      <c r="B762" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C762" s="9" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D762" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E762" s="9" t="inlineStr">
+        <is>
+          <t>Taif University</t>
+        </is>
+      </c>
+      <c r="F762" s="9" t="inlineStr"/>
+      <c r="G762" s="9" t="inlineStr"/>
+      <c r="H762" s="9" t="inlineStr">
+        <is>
+          <t>GraduateStudies@tu.edu.sa</t>
+        </is>
+      </c>
+      <c r="I762" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J762" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K762" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Taif University</t>
+        </is>
+      </c>
+      <c r="L762" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M762" s="9" t="inlineStr">
+        <is>
+          <t>https://www.tu.edu.sa/En/Deanship-of-Graduate-Studies/110/Pages/20495/Contact-Us</t>
+        </is>
+      </c>
+      <c r="N762" s="9" t="inlineStr">
+        <is>
+          <t>Alt: DeanshipofGraduate@tu.edu.sa</t>
+        </is>
+      </c>
+      <c r="O762" s="9" t="inlineStr"/>
+      <c r="P762" s="9" t="inlineStr"/>
+      <c r="Q762" s="9" t="inlineStr"/>
+    </row>
+    <row r="763">
+      <c r="A763" s="9" t="n">
+        <v>762</v>
+      </c>
+      <c r="B763" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C763" s="9" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D763" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E763" s="9" t="inlineStr">
+        <is>
+          <t>Islamic University of Medina</t>
+        </is>
+      </c>
+      <c r="F763" s="9" t="inlineStr"/>
+      <c r="G763" s="9" t="inlineStr"/>
+      <c r="H763" s="9" t="inlineStr">
+        <is>
+          <t>development@iu.edu.sa</t>
+        </is>
+      </c>
+      <c r="I763" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J763" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K763" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Islamic University of Medina</t>
+        </is>
+      </c>
+      <c r="L763" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M763" s="9" t="inlineStr">
+        <is>
+          <t>https://iu.edu.sa/D0115-1</t>
+        </is>
+      </c>
+      <c r="N763" s="9" t="inlineStr">
+        <is>
+          <t>Deanship contact</t>
+        </is>
+      </c>
+      <c r="O763" s="9" t="inlineStr"/>
+      <c r="P763" s="9" t="inlineStr"/>
+      <c r="Q763" s="9" t="inlineStr"/>
+    </row>
+    <row r="764">
+      <c r="A764" s="9" t="n">
+        <v>763</v>
+      </c>
+      <c r="B764" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C764" s="9" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D764" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E764" s="9" t="inlineStr">
+        <is>
+          <t>Imam Abdulrahman Bin Faisal University</t>
+        </is>
+      </c>
+      <c r="F764" s="9" t="inlineStr"/>
+      <c r="G764" s="9" t="inlineStr"/>
+      <c r="H764" s="9" t="inlineStr">
+        <is>
+          <t>QAA@iau.edu.sa</t>
+        </is>
+      </c>
+      <c r="I764" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J764" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K764" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Imam Abdulrahman Bin Faisal University</t>
+        </is>
+      </c>
+      <c r="L764" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M764" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iau.edu.sa/en/administration/deanships/deanship-of-quality-and-academic-accreditation/contact</t>
+        </is>
+      </c>
+      <c r="N764" s="9" t="inlineStr">
+        <is>
+          <t>Deanship of Quality &amp; Academic Accreditation</t>
+        </is>
+      </c>
+      <c r="O764" s="9" t="inlineStr"/>
+      <c r="P764" s="9" t="inlineStr"/>
+      <c r="Q764" s="9" t="inlineStr"/>
+    </row>
+    <row r="765">
+      <c r="A765" s="9" t="n">
+        <v>764</v>
+      </c>
+      <c r="B765" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C765" s="9" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D765" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E765" s="9" t="inlineStr">
+        <is>
+          <t>King Faisal University</t>
+        </is>
+      </c>
+      <c r="F765" s="9" t="inlineStr"/>
+      <c r="G765" s="9" t="inlineStr"/>
+      <c r="H765" s="9" t="inlineStr">
+        <is>
+          <t>contact@kfu.edu.sa</t>
+        </is>
+      </c>
+      <c r="I765" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J765" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K765" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for King Faisal University</t>
+        </is>
+      </c>
+      <c r="L765" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M765" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kfu.edu.sa/en/Departments/SeniorManagement/Pages/email.aspx</t>
+        </is>
+      </c>
+      <c r="N765" s="9" t="inlineStr">
+        <is>
+          <t>Media/PR dept; alt info@kfu.edu.sa</t>
+        </is>
+      </c>
+      <c r="O765" s="9" t="inlineStr"/>
+      <c r="P765" s="9" t="inlineStr"/>
+      <c r="Q765" s="9" t="inlineStr"/>
+    </row>
+    <row r="766">
+      <c r="A766" s="9" t="n">
+        <v>765</v>
+      </c>
+      <c r="B766" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C766" s="9" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D766" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E766" s="9" t="inlineStr">
+        <is>
+          <t>King Khalid University</t>
+        </is>
+      </c>
+      <c r="F766" s="9" t="inlineStr"/>
+      <c r="G766" s="9" t="inlineStr"/>
+      <c r="H766" s="9" t="inlineStr">
+        <is>
+          <t>mubasher@kku.edu.sa</t>
+        </is>
+      </c>
+      <c r="I766" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J766" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K766" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for King Khalid University</t>
+        </is>
+      </c>
+      <c r="L766" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M766" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kku.edu.sa/en/node/102023</t>
+        </is>
+      </c>
+      <c r="N766" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O766" s="9" t="inlineStr"/>
+      <c r="P766" s="9" t="inlineStr"/>
+      <c r="Q766" s="9" t="inlineStr"/>
+    </row>
+    <row r="767">
+      <c r="A767" s="9" t="n">
+        <v>766</v>
+      </c>
+      <c r="B767" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C767" s="9" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D767" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E767" s="9" t="inlineStr">
+        <is>
+          <t>Qassim University</t>
+        </is>
+      </c>
+      <c r="F767" s="9" t="inlineStr"/>
+      <c r="G767" s="9" t="inlineStr"/>
+      <c r="H767" s="9" t="inlineStr">
+        <is>
+          <t>info@qu.edu.sa</t>
+        </is>
+      </c>
+      <c r="I767" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J767" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K767" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Qassim University</t>
+        </is>
+      </c>
+      <c r="L767" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M767" s="9" t="inlineStr">
+        <is>
+          <t>https://www.qu.edu.sa/en/contact-us/</t>
+        </is>
+      </c>
+      <c r="N767" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O767" s="9" t="inlineStr"/>
+      <c r="P767" s="9" t="inlineStr"/>
+      <c r="Q767" s="9" t="inlineStr"/>
+    </row>
+    <row r="768">
+      <c r="A768" s="9" t="n">
+        <v>767</v>
+      </c>
+      <c r="B768" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C768" s="9" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D768" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E768" s="9" t="inlineStr">
+        <is>
+          <t>Jouf University</t>
+        </is>
+      </c>
+      <c r="F768" s="9" t="inlineStr"/>
+      <c r="G768" s="9" t="inlineStr"/>
+      <c r="H768" s="9" t="inlineStr">
+        <is>
+          <t>contact@ju.edu.sa</t>
+        </is>
+      </c>
+      <c r="I768" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J768" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K768" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Jouf University</t>
+        </is>
+      </c>
+      <c r="L768" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M768" s="9" t="inlineStr">
+        <is>
+          <t>https://ju.edu.sa/en/node/200</t>
+        </is>
+      </c>
+      <c r="N768" s="9" t="inlineStr">
+        <is>
+          <t>Alt: services@ju.edu.sa</t>
+        </is>
+      </c>
+      <c r="O768" s="9" t="inlineStr"/>
+      <c r="P768" s="9" t="inlineStr"/>
+      <c r="Q768" s="9" t="inlineStr"/>
+    </row>
+    <row r="769">
+      <c r="A769" s="9" t="n">
+        <v>768</v>
+      </c>
+      <c r="B769" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C769" s="9" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D769" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E769" s="9" t="inlineStr">
+        <is>
+          <t>Al Baha University</t>
+        </is>
+      </c>
+      <c r="F769" s="9" t="inlineStr"/>
+      <c r="G769" s="9" t="inlineStr"/>
+      <c r="H769" s="9" t="inlineStr">
+        <is>
+          <t>dqaa@bu.edu.sa</t>
+        </is>
+      </c>
+      <c r="I769" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J769" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K769" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Al Baha University</t>
+        </is>
+      </c>
+      <c r="L769" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M769" s="9" t="inlineStr">
+        <is>
+          <t>https://bu.edu.sa/en/web/deanship-of-quality-and-development/contact-us</t>
+        </is>
+      </c>
+      <c r="N769" s="9" t="inlineStr">
+        <is>
+          <t>Deanship of Quality and Development</t>
+        </is>
+      </c>
+      <c r="O769" s="9" t="inlineStr"/>
+      <c r="P769" s="9" t="inlineStr"/>
+      <c r="Q769" s="9" t="inlineStr"/>
+    </row>
+    <row r="770">
+      <c r="A770" s="9" t="n">
+        <v>769</v>
+      </c>
+      <c r="B770" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C770" s="9" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D770" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E770" s="9" t="inlineStr">
+        <is>
+          <t>Najran University</t>
+        </is>
+      </c>
+      <c r="F770" s="9" t="inlineStr"/>
+      <c r="G770" s="9" t="inlineStr"/>
+      <c r="H770" s="9" t="inlineStr">
+        <is>
+          <t>care@nu.edu.sa</t>
+        </is>
+      </c>
+      <c r="I770" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J770" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K770" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Najran University</t>
+        </is>
+      </c>
+      <c r="L770" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M770" s="9" t="inlineStr">
+        <is>
+          <t>https://portal.nu.edu.sa/en/contactForm</t>
+        </is>
+      </c>
+      <c r="N770" s="9" t="inlineStr">
+        <is>
+          <t>General inquiries</t>
+        </is>
+      </c>
+      <c r="O770" s="9" t="inlineStr"/>
+      <c r="P770" s="9" t="inlineStr"/>
+      <c r="Q770" s="9" t="inlineStr"/>
+    </row>
+    <row r="771">
+      <c r="A771" s="9" t="n">
+        <v>770</v>
+      </c>
+      <c r="B771" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C771" s="9" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D771" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E771" s="9" t="inlineStr">
+        <is>
+          <t>Al Yamamah University</t>
+        </is>
+      </c>
+      <c r="F771" s="9" t="inlineStr"/>
+      <c r="G771" s="9" t="inlineStr"/>
+      <c r="H771" s="9" t="inlineStr">
+        <is>
+          <t>info@yu.edu.sa</t>
+        </is>
+      </c>
+      <c r="I771" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J771" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K771" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Al Yamamah University</t>
+        </is>
+      </c>
+      <c r="L771" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M771" s="9" t="inlineStr">
+        <is>
+          <t>https://yu.edu.sa/contact/</t>
+        </is>
+      </c>
+      <c r="N771" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O771" s="9" t="inlineStr"/>
+      <c r="P771" s="9" t="inlineStr"/>
+      <c r="Q771" s="9" t="inlineStr"/>
+    </row>
+    <row r="772">
+      <c r="A772" s="9" t="n">
+        <v>771</v>
+      </c>
+      <c r="B772" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C772" s="9" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D772" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E772" s="9" t="inlineStr">
+        <is>
+          <t>Dar Al Uloom University</t>
+        </is>
+      </c>
+      <c r="F772" s="9" t="inlineStr"/>
+      <c r="G772" s="9" t="inlineStr"/>
+      <c r="H772" s="9" t="inlineStr">
+        <is>
+          <t>info@dau.edu.sa</t>
+        </is>
+      </c>
+      <c r="I772" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J772" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K772" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Dar Al Uloom University</t>
+        </is>
+      </c>
+      <c r="L772" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M772" s="9" t="inlineStr">
+        <is>
+          <t>https://dau.edu.sa/en/about-university/about-university/</t>
+        </is>
+      </c>
+      <c r="N772" s="9" t="inlineStr">
+        <is>
+          <t>General institutional email</t>
+        </is>
+      </c>
+      <c r="O772" s="9" t="inlineStr"/>
+      <c r="P772" s="9" t="inlineStr"/>
+      <c r="Q772" s="9" t="inlineStr"/>
+    </row>
+    <row r="773">
+      <c r="A773" s="9" t="n">
+        <v>772</v>
+      </c>
+      <c r="B773" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C773" s="9" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D773" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E773" s="9" t="inlineStr">
+        <is>
+          <t>Prince Mohammad Bin Fahd University</t>
+        </is>
+      </c>
+      <c r="F773" s="9" t="inlineStr"/>
+      <c r="G773" s="9" t="inlineStr"/>
+      <c r="H773" s="9" t="inlineStr">
+        <is>
+          <t>Info@pmu.edu.sa</t>
+        </is>
+      </c>
+      <c r="I773" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J773" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K773" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Prince Mohammad Bin Fahd University</t>
+        </is>
+      </c>
+      <c r="L773" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M773" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pmu.edu.sa/about/contact_us</t>
+        </is>
+      </c>
+      <c r="N773" s="9" t="inlineStr">
+        <is>
+          <t>General information</t>
+        </is>
+      </c>
+      <c r="O773" s="9" t="inlineStr"/>
+      <c r="P773" s="9" t="inlineStr"/>
+      <c r="Q773" s="9" t="inlineStr"/>
+    </row>
+    <row r="774">
+      <c r="A774" s="9" t="n">
+        <v>773</v>
+      </c>
+      <c r="B774" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C774" s="9" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D774" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E774" s="9" t="inlineStr">
+        <is>
+          <t>Sulaiman Al Rajhi University</t>
+        </is>
+      </c>
+      <c r="F774" s="9" t="inlineStr"/>
+      <c r="G774" s="9" t="inlineStr"/>
+      <c r="H774" s="9" t="inlineStr">
+        <is>
+          <t>info@sr.edu.sa</t>
+        </is>
+      </c>
+      <c r="I774" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J774" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K774" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Sulaiman Al Rajhi University</t>
+        </is>
+      </c>
+      <c r="L774" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M774" s="9" t="inlineStr">
+        <is>
+          <t>https://sr.edu.sa/site/contact-us/</t>
+        </is>
+      </c>
+      <c r="N774" s="9" t="inlineStr">
+        <is>
+          <t>Alt: admission@sr.edu.sa</t>
+        </is>
+      </c>
+      <c r="O774" s="9" t="inlineStr"/>
+      <c r="P774" s="9" t="inlineStr"/>
+      <c r="Q774" s="9" t="inlineStr"/>
+    </row>
+    <row r="775">
+      <c r="A775" s="9" t="n">
+        <v>774</v>
+      </c>
+      <c r="B775" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C775" s="9" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D775" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E775" s="9" t="inlineStr">
+        <is>
+          <t>Qatar University</t>
+        </is>
+      </c>
+      <c r="F775" s="9" t="inlineStr"/>
+      <c r="G775" s="9" t="inlineStr"/>
+      <c r="H775" s="9" t="inlineStr">
+        <is>
+          <t>researchsupport@qu.edu.qa</t>
+        </is>
+      </c>
+      <c r="I775" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J775" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K775" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Qatar University</t>
+        </is>
+      </c>
+      <c r="L775" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M775" s="9" t="inlineStr">
+        <is>
+          <t>https://www.qu.edu.qa/en-us/Research/about/Pages/contact-us.aspx</t>
+        </is>
+      </c>
+      <c r="N775" s="9" t="inlineStr">
+        <is>
+          <t>Research Support (Grants &amp; Contracts)</t>
+        </is>
+      </c>
+      <c r="O775" s="9" t="inlineStr"/>
+      <c r="P775" s="9" t="inlineStr"/>
+      <c r="Q775" s="9" t="inlineStr"/>
+    </row>
+    <row r="776">
+      <c r="A776" s="9" t="n">
+        <v>775</v>
+      </c>
+      <c r="B776" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C776" s="9" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D776" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E776" s="9" t="inlineStr">
+        <is>
+          <t>Hamad Bin Khalifa University</t>
+        </is>
+      </c>
+      <c r="F776" s="9" t="inlineStr"/>
+      <c r="G776" s="9" t="inlineStr"/>
+      <c r="H776" s="9" t="inlineStr">
+        <is>
+          <t>researchsupport@hbku.edu.qa</t>
+        </is>
+      </c>
+      <c r="I776" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J776" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K776" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Hamad Bin Khalifa University</t>
+        </is>
+      </c>
+      <c r="L776" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M776" s="9" t="inlineStr">
+        <is>
+          <t>https://www.hbku.edu.qa/en/contact-us</t>
+        </is>
+      </c>
+      <c r="N776" s="9" t="inlineStr">
+        <is>
+          <t>Also sro@hbku.edu.qa</t>
+        </is>
+      </c>
+      <c r="O776" s="9" t="inlineStr"/>
+      <c r="P776" s="9" t="inlineStr"/>
+      <c r="Q776" s="9" t="inlineStr"/>
+    </row>
+    <row r="777">
+      <c r="A777" s="9" t="n">
+        <v>776</v>
+      </c>
+      <c r="B777" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C777" s="9" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D777" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E777" s="9" t="inlineStr">
+        <is>
+          <t>Community College of Qatar</t>
+        </is>
+      </c>
+      <c r="F777" s="9" t="inlineStr"/>
+      <c r="G777" s="9" t="inlineStr"/>
+      <c r="H777" s="9" t="inlineStr">
+        <is>
+          <t>library@ccq.edu.qa</t>
+        </is>
+      </c>
+      <c r="I777" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J777" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K777" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Community College of Qatar</t>
+        </is>
+      </c>
+      <c r="L777" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M777" s="9" t="inlineStr">
+        <is>
+          <t>https://www.community.edu.qa/</t>
+        </is>
+      </c>
+      <c r="N777" s="9" t="inlineStr">
+        <is>
+          <t>Only email on homepage</t>
+        </is>
+      </c>
+      <c r="O777" s="9" t="inlineStr"/>
+      <c r="P777" s="9" t="inlineStr"/>
+      <c r="Q777" s="9" t="inlineStr"/>
+    </row>
+    <row r="778">
+      <c r="A778" s="9" t="n">
+        <v>777</v>
+      </c>
+      <c r="B778" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C778" s="9" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D778" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E778" s="9" t="inlineStr">
+        <is>
+          <t>University Foundation College</t>
+        </is>
+      </c>
+      <c r="F778" s="9" t="inlineStr"/>
+      <c r="G778" s="9" t="inlineStr"/>
+      <c r="H778" s="9" t="inlineStr">
+        <is>
+          <t>info@ufc.edu.qa</t>
+        </is>
+      </c>
+      <c r="I778" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J778" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K778" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University Foundation College</t>
+        </is>
+      </c>
+      <c r="L778" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M778" s="9" t="inlineStr">
+        <is>
+          <t>https://ufc.edu.qa/contact-us/</t>
+        </is>
+      </c>
+      <c r="N778" s="9" t="inlineStr">
+        <is>
+          <t>General enquiries</t>
+        </is>
+      </c>
+      <c r="O778" s="9" t="inlineStr"/>
+      <c r="P778" s="9" t="inlineStr"/>
+      <c r="Q778" s="9" t="inlineStr"/>
+    </row>
+    <row r="779">
+      <c r="A779" s="9" t="n">
+        <v>778</v>
+      </c>
+      <c r="B779" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C779" s="9" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D779" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E779" s="9" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University in Qatar</t>
+        </is>
+      </c>
+      <c r="F779" s="9" t="inlineStr"/>
+      <c r="G779" s="9" t="inlineStr"/>
+      <c r="H779" s="9" t="inlineStr">
+        <is>
+          <t>ug-admission@qatar.cmu.edu</t>
+        </is>
+      </c>
+      <c r="I779" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J779" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K779" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Carnegie Mellon University in Qatar</t>
+        </is>
+      </c>
+      <c r="L779" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M779" s="9" t="inlineStr">
+        <is>
+          <t>https://admission.qatar.cmu.edu/register/contact-admission-office</t>
+        </is>
+      </c>
+      <c r="N779" s="9" t="inlineStr">
+        <is>
+          <t>Office of Admission</t>
+        </is>
+      </c>
+      <c r="O779" s="9" t="inlineStr"/>
+      <c r="P779" s="9" t="inlineStr"/>
+      <c r="Q779" s="9" t="inlineStr"/>
+    </row>
+    <row r="780">
+      <c r="A780" s="9" t="n">
+        <v>779</v>
+      </c>
+      <c r="B780" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C780" s="9" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D780" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E780" s="9" t="inlineStr">
+        <is>
+          <t>Georgetown University in Qatar</t>
+        </is>
+      </c>
+      <c r="F780" s="9" t="inlineStr"/>
+      <c r="G780" s="9" t="inlineStr"/>
+      <c r="H780" s="9" t="inlineStr">
+        <is>
+          <t>guqadmissions@georgetown.edu</t>
+        </is>
+      </c>
+      <c r="I780" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J780" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K780" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Georgetown University in Qatar</t>
+        </is>
+      </c>
+      <c r="L780" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M780" s="9" t="inlineStr">
+        <is>
+          <t>https://admissions.qatar.georgetown.edu/apply/GUQatar_Admissions_Brochure.pdf</t>
+        </is>
+      </c>
+      <c r="N780" s="9" t="inlineStr">
+        <is>
+          <t>Office of Admissions</t>
+        </is>
+      </c>
+      <c r="O780" s="9" t="inlineStr"/>
+      <c r="P780" s="9" t="inlineStr"/>
+      <c r="Q780" s="9" t="inlineStr"/>
+    </row>
+    <row r="781">
+      <c r="A781" s="9" t="n">
+        <v>780</v>
+      </c>
+      <c r="B781" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C781" s="9" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D781" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E781" s="9" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University School of the Arts in Qatar</t>
+        </is>
+      </c>
+      <c r="F781" s="9" t="inlineStr"/>
+      <c r="G781" s="9" t="inlineStr"/>
+      <c r="H781" s="9" t="inlineStr">
+        <is>
+          <t>vcuqlibrary@vcu.edu</t>
+        </is>
+      </c>
+      <c r="I781" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J781" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K781" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for VCU School of the Arts in Qatar</t>
+        </is>
+      </c>
+      <c r="L781" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M781" s="9" t="inlineStr">
+        <is>
+          <t>https://qatar.vcu.edu/contacts/</t>
+        </is>
+      </c>
+      <c r="N781" s="9" t="inlineStr">
+        <is>
+          <t>Main email obfuscated; library verified</t>
+        </is>
+      </c>
+      <c r="O781" s="9" t="inlineStr"/>
+      <c r="P781" s="9" t="inlineStr"/>
+      <c r="Q781" s="9" t="inlineStr"/>
+    </row>
+    <row r="782">
+      <c r="A782" s="9" t="n">
+        <v>781</v>
+      </c>
+      <c r="B782" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C782" s="9" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D782" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E782" s="9" t="inlineStr">
+        <is>
+          <t>Weill Cornell Medicine-Qatar</t>
+        </is>
+      </c>
+      <c r="F782" s="9" t="inlineStr"/>
+      <c r="G782" s="9" t="inlineStr"/>
+      <c r="H782" s="9" t="inlineStr">
+        <is>
+          <t>khm2002@qatar-med.cornell.edu</t>
+        </is>
+      </c>
+      <c r="I782" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J782" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K782" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Weill Cornell Medicine-Qatar</t>
+        </is>
+      </c>
+      <c r="L782" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M782" s="9" t="inlineStr">
+        <is>
+          <t>https://qatar-weill.cornell.edu/research/contact-us</t>
+        </is>
+      </c>
+      <c r="N782" s="9" t="inlineStr">
+        <is>
+          <t>Senior Associate Dean for Research</t>
+        </is>
+      </c>
+      <c r="O782" s="9" t="inlineStr"/>
+      <c r="P782" s="9" t="inlineStr"/>
+      <c r="Q782" s="9" t="inlineStr"/>
+    </row>
+    <row r="783">
+      <c r="A783" s="9" t="n">
+        <v>782</v>
+      </c>
+      <c r="B783" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C783" s="9" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D783" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E783" s="9" t="inlineStr">
+        <is>
+          <t>HEC Paris in Qatar</t>
+        </is>
+      </c>
+      <c r="F783" s="9" t="inlineStr"/>
+      <c r="G783" s="9" t="inlineStr"/>
+      <c r="H783" s="9" t="inlineStr">
+        <is>
+          <t>qatar-info@hec.fr</t>
+        </is>
+      </c>
+      <c r="I783" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J783" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K783" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for HEC Paris in Qatar</t>
+        </is>
+      </c>
+      <c r="L783" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M783" s="9" t="inlineStr">
+        <is>
+          <t>https://www.qatar.exed.hec.edu/contact</t>
+        </is>
+      </c>
+      <c r="N783" s="9" t="inlineStr">
+        <is>
+          <t>Customer support/general</t>
+        </is>
+      </c>
+      <c r="O783" s="9" t="inlineStr"/>
+      <c r="P783" s="9" t="inlineStr"/>
+      <c r="Q783" s="9" t="inlineStr"/>
+    </row>
+    <row r="784">
+      <c r="A784" s="9" t="n">
+        <v>783</v>
+      </c>
+      <c r="B784" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C784" s="9" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D784" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E784" s="9" t="inlineStr">
+        <is>
+          <t>University of Aberdeen Qatar Campus</t>
+        </is>
+      </c>
+      <c r="F784" s="9" t="inlineStr"/>
+      <c r="G784" s="9" t="inlineStr"/>
+      <c r="H784" s="9" t="inlineStr">
+        <is>
+          <t>info@afg-aberdeen.edu.qa</t>
+        </is>
+      </c>
+      <c r="I784" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J784" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K784" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Aberdeen Qatar Campus</t>
+        </is>
+      </c>
+      <c r="L784" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M784" s="9" t="inlineStr">
+        <is>
+          <t>https://www.abdn.ac.uk/qatar/contact-us/</t>
+        </is>
+      </c>
+      <c r="N784" s="9" t="inlineStr">
+        <is>
+          <t>Via AFG College partnership</t>
+        </is>
+      </c>
+      <c r="O784" s="9" t="inlineStr"/>
+      <c r="P784" s="9" t="inlineStr"/>
+      <c r="Q784" s="9" t="inlineStr"/>
+    </row>
+    <row r="785">
+      <c r="A785" s="9" t="n">
+        <v>784</v>
+      </c>
+      <c r="B785" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C785" s="9" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D785" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E785" s="9" t="inlineStr">
+        <is>
+          <t>Ulster University Qatar</t>
+        </is>
+      </c>
+      <c r="F785" s="9" t="inlineStr"/>
+      <c r="G785" s="9" t="inlineStr"/>
+      <c r="H785" s="9" t="inlineStr">
+        <is>
+          <t>info@cuq-ulster.edu.qa</t>
+        </is>
+      </c>
+      <c r="I785" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J785" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K785" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Ulster University Qatar</t>
+        </is>
+      </c>
+      <c r="L785" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M785" s="9" t="inlineStr">
+        <is>
+          <t>https://cuq-ulster.edu.qa/</t>
+        </is>
+      </c>
+      <c r="N785" s="9" t="inlineStr">
+        <is>
+          <t>Via City University Qatar/Ulster partnership</t>
+        </is>
+      </c>
+      <c r="O785" s="9" t="inlineStr"/>
+      <c r="P785" s="9" t="inlineStr"/>
+      <c r="Q785" s="9" t="inlineStr"/>
+    </row>
+    <row r="786">
+      <c r="A786" s="9" t="n">
+        <v>785</v>
+      </c>
+      <c r="B786" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C786" s="9" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D786" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E786" s="9" t="inlineStr">
+        <is>
+          <t>Northumbria University Qatar</t>
+        </is>
+      </c>
+      <c r="F786" s="9" t="inlineStr"/>
+      <c r="G786" s="9" t="inlineStr"/>
+      <c r="H786" s="9" t="inlineStr">
+        <is>
+          <t>info@qfba.edu.qa</t>
+        </is>
+      </c>
+      <c r="I786" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J786" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K786" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Northumbria University Qatar</t>
+        </is>
+      </c>
+      <c r="L786" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M786" s="9" t="inlineStr">
+        <is>
+          <t>https://www.qfba.edu.qa/terms-and-conditions/contact_info</t>
+        </is>
+      </c>
+      <c r="N786" s="9" t="inlineStr">
+        <is>
+          <t>Via Qatar Finance and Business Academy</t>
+        </is>
+      </c>
+      <c r="O786" s="9" t="inlineStr"/>
+      <c r="P786" s="9" t="inlineStr"/>
+      <c r="Q786" s="9" t="inlineStr"/>
+    </row>
+    <row r="787">
+      <c r="A787" s="9" t="n">
+        <v>786</v>
+      </c>
+      <c r="B787" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C787" s="9" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D787" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E787" s="9" t="inlineStr">
+        <is>
+          <t>Arkansas State University Qatar</t>
+        </is>
+      </c>
+      <c r="F787" s="9" t="inlineStr"/>
+      <c r="G787" s="9" t="inlineStr"/>
+      <c r="H787" s="9" t="inlineStr">
+        <is>
+          <t>info@astateqatar.com</t>
+        </is>
+      </c>
+      <c r="I787" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J787" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K787" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Arkansas State University Qatar</t>
+        </is>
+      </c>
+      <c r="L787" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M787" s="9" t="inlineStr">
+        <is>
+          <t>https://astateqatar.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="N787" s="9" t="inlineStr">
+        <is>
+          <t>Confirmed via official admissions PDF</t>
+        </is>
+      </c>
+      <c r="O787" s="9" t="inlineStr"/>
+      <c r="P787" s="9" t="inlineStr"/>
+      <c r="Q787" s="9" t="inlineStr"/>
+    </row>
+    <row r="788">
+      <c r="A788" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="B788" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C788" s="9" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D788" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E788" s="9" t="inlineStr">
+        <is>
+          <t>Liverpool John Moores University Qatar</t>
+        </is>
+      </c>
+      <c r="F788" s="9" t="inlineStr"/>
+      <c r="G788" s="9" t="inlineStr"/>
+      <c r="H788" s="9" t="inlineStr">
+        <is>
+          <t>hello@oryx.edu.qa</t>
+        </is>
+      </c>
+      <c r="I788" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J788" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K788" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Liverpool John Moores University Qatar</t>
+        </is>
+      </c>
+      <c r="L788" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M788" s="9" t="inlineStr">
+        <is>
+          <t>https://oryx.edu.qa/contact/</t>
+        </is>
+      </c>
+      <c r="N788" s="9" t="inlineStr">
+        <is>
+          <t>Via Oryx Universal College partnership</t>
+        </is>
+      </c>
+      <c r="O788" s="9" t="inlineStr"/>
+      <c r="P788" s="9" t="inlineStr"/>
+      <c r="Q788" s="9" t="inlineStr"/>
+    </row>
+    <row r="789">
+      <c r="A789" s="9" t="n">
+        <v>788</v>
+      </c>
+      <c r="B789" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C789" s="9" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="D789" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E789" s="9" t="inlineStr">
+        <is>
+          <t>Abdullah Al Salem University</t>
+        </is>
+      </c>
+      <c r="F789" s="9" t="inlineStr"/>
+      <c r="G789" s="9" t="inlineStr"/>
+      <c r="H789" s="9" t="inlineStr">
+        <is>
+          <t>info@aasu.edu.kw</t>
+        </is>
+      </c>
+      <c r="I789" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J789" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K789" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Abdullah Al Salem University</t>
+        </is>
+      </c>
+      <c r="L789" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M789" s="9" t="inlineStr">
+        <is>
+          <t>https://aasu.edu.kw/ContactUs/</t>
+        </is>
+      </c>
+      <c r="N789" s="9" t="inlineStr">
+        <is>
+          <t>General inquiries</t>
+        </is>
+      </c>
+      <c r="O789" s="9" t="inlineStr"/>
+      <c r="P789" s="9" t="inlineStr"/>
+      <c r="Q789" s="9" t="inlineStr"/>
+    </row>
+    <row r="790">
+      <c r="A790" s="9" t="n">
+        <v>789</v>
+      </c>
+      <c r="B790" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C790" s="9" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="D790" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E790" s="9" t="inlineStr">
+        <is>
+          <t>American University of Kuwait</t>
+        </is>
+      </c>
+      <c r="F790" s="9" t="inlineStr"/>
+      <c r="G790" s="9" t="inlineStr"/>
+      <c r="H790" s="9" t="inlineStr">
+        <is>
+          <t>info@auk.edu.kw</t>
+        </is>
+      </c>
+      <c r="I790" s="9" t="inlineStr">
+        <is>
+          <t>On hold (prior contact)</t>
+        </is>
+      </c>
+      <c r="J790" s="9" t="inlineStr"/>
+      <c r="K790" s="9" t="inlineStr"/>
+      <c r="L790" s="9" t="inlineStr"/>
+      <c r="M790" s="9" t="inlineStr">
+        <is>
+          <t>https://auk.edu.kw/who-we-are/contact-us</t>
+        </is>
+      </c>
+      <c r="N790" s="9" t="inlineStr">
+        <is>
+          <t>General inquiries | Prior contact found (sent 2026-09-26 to nalkharafi@auk.edu.kw)</t>
+        </is>
+      </c>
+      <c r="O790" s="9" t="inlineStr"/>
+      <c r="P790" s="9" t="inlineStr"/>
+      <c r="Q790" s="9" t="inlineStr"/>
+    </row>
+    <row r="791">
+      <c r="A791" s="9" t="n">
+        <v>790</v>
+      </c>
+      <c r="B791" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C791" s="9" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="D791" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E791" s="9" t="inlineStr">
+        <is>
+          <t>American International University Kuwait</t>
+        </is>
+      </c>
+      <c r="F791" s="9" t="inlineStr"/>
+      <c r="G791" s="9" t="inlineStr"/>
+      <c r="H791" s="9" t="inlineStr">
+        <is>
+          <t>info@aiu.edu.kw</t>
+        </is>
+      </c>
+      <c r="I791" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J791" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K791" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for American International University Kuwait</t>
+        </is>
+      </c>
+      <c r="L791" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M791" s="9" t="inlineStr">
+        <is>
+          <t>https://www.aiu.edu.kw/contact</t>
+        </is>
+      </c>
+      <c r="N791" s="9" t="inlineStr">
+        <is>
+          <t>General inquiries</t>
+        </is>
+      </c>
+      <c r="O791" s="9" t="inlineStr"/>
+      <c r="P791" s="9" t="inlineStr"/>
+      <c r="Q791" s="9" t="inlineStr"/>
+    </row>
+    <row r="792">
+      <c r="A792" s="9" t="n">
+        <v>791</v>
+      </c>
+      <c r="B792" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C792" s="9" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="D792" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E792" s="9" t="inlineStr">
+        <is>
+          <t>Arab Open University Kuwait</t>
+        </is>
+      </c>
+      <c r="F792" s="9" t="inlineStr"/>
+      <c r="G792" s="9" t="inlineStr"/>
+      <c r="H792" s="9" t="inlineStr">
+        <is>
+          <t>info@aou.edu.kw</t>
+        </is>
+      </c>
+      <c r="I792" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J792" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K792" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Arab Open University Kuwait</t>
+        </is>
+      </c>
+      <c r="L792" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M792" s="9" t="inlineStr">
+        <is>
+          <t>https://www.aou.edu.kw/about/Pages/contact-us.aspx</t>
+        </is>
+      </c>
+      <c r="N792" s="9" t="inlineStr">
+        <is>
+          <t>General info</t>
+        </is>
+      </c>
+      <c r="O792" s="9" t="inlineStr"/>
+      <c r="P792" s="9" t="inlineStr"/>
+      <c r="Q792" s="9" t="inlineStr"/>
+    </row>
+    <row r="793">
+      <c r="A793" s="9" t="n">
+        <v>792</v>
+      </c>
+      <c r="B793" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C793" s="9" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="D793" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E793" s="9" t="inlineStr">
+        <is>
+          <t>International University of Kuwait</t>
+        </is>
+      </c>
+      <c r="F793" s="9" t="inlineStr"/>
+      <c r="G793" s="9" t="inlineStr"/>
+      <c r="H793" s="9" t="inlineStr">
+        <is>
+          <t>Info@iuk.edu.kw</t>
+        </is>
+      </c>
+      <c r="I793" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J793" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K793" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for International University of Kuwait</t>
+        </is>
+      </c>
+      <c r="L793" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M793" s="9" t="inlineStr">
+        <is>
+          <t>https://www.iuk.edu.kw/contact_iuk</t>
+        </is>
+      </c>
+      <c r="N793" s="9" t="inlineStr">
+        <is>
+          <t>General info</t>
+        </is>
+      </c>
+      <c r="O793" s="9" t="inlineStr"/>
+      <c r="P793" s="9" t="inlineStr"/>
+      <c r="Q793" s="9" t="inlineStr"/>
+    </row>
+    <row r="794">
+      <c r="A794" s="9" t="n">
+        <v>793</v>
+      </c>
+      <c r="B794" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C794" s="9" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="D794" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E794" s="9" t="inlineStr">
+        <is>
+          <t>Box Hill College Kuwait</t>
+        </is>
+      </c>
+      <c r="F794" s="9" t="inlineStr"/>
+      <c r="G794" s="9" t="inlineStr"/>
+      <c r="H794" s="9" t="inlineStr">
+        <is>
+          <t>info@bhck.edu.kw</t>
+        </is>
+      </c>
+      <c r="I794" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J794" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K794" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Box Hill College Kuwait</t>
+        </is>
+      </c>
+      <c r="L794" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M794" s="9" t="inlineStr">
+        <is>
+          <t>https://bhck.edu.kw/contact-us/</t>
+        </is>
+      </c>
+      <c r="N794" s="9" t="inlineStr">
+        <is>
+          <t>Also admissionsgroup@bhck.edu.kw</t>
+        </is>
+      </c>
+      <c r="O794" s="9" t="inlineStr"/>
+      <c r="P794" s="9" t="inlineStr"/>
+      <c r="Q794" s="9" t="inlineStr"/>
+    </row>
+    <row r="795">
+      <c r="A795" s="9" t="n">
+        <v>794</v>
+      </c>
+      <c r="B795" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C795" s="9" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="D795" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E795" s="9" t="inlineStr">
+        <is>
+          <t>Public Authority for Applied Education and Training</t>
+        </is>
+      </c>
+      <c r="F795" s="9" t="inlineStr"/>
+      <c r="G795" s="9" t="inlineStr"/>
+      <c r="H795" s="9" t="inlineStr">
+        <is>
+          <t>GITHelpDesk@paaet.edu.kw</t>
+        </is>
+      </c>
+      <c r="I795" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J795" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K795" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Public Authority for Applied Education and Training</t>
+        </is>
+      </c>
+      <c r="L795" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M795" s="9" t="inlineStr">
+        <is>
+          <t>https://www.paaet.edu.kw/en/contact</t>
+        </is>
+      </c>
+      <c r="N795" s="9" t="inlineStr">
+        <is>
+          <t>Help Desk address, use with caution</t>
+        </is>
+      </c>
+      <c r="O795" s="9" t="inlineStr"/>
+      <c r="P795" s="9" t="inlineStr"/>
+      <c r="Q795" s="9" t="inlineStr"/>
+    </row>
+    <row r="796">
+      <c r="A796" s="9" t="n">
+        <v>795</v>
+      </c>
+      <c r="B796" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C796" s="9" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="D796" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E796" s="9" t="inlineStr">
+        <is>
+          <t>Arabian Gulf University</t>
+        </is>
+      </c>
+      <c r="F796" s="9" t="inlineStr"/>
+      <c r="G796" s="9" t="inlineStr"/>
+      <c r="H796" s="9" t="inlineStr">
+        <is>
+          <t>INFO@AGU.EDU.BH</t>
+        </is>
+      </c>
+      <c r="I796" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J796" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K796" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Arabian Gulf University</t>
+        </is>
+      </c>
+      <c r="L796" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M796" s="9" t="inlineStr">
+        <is>
+          <t>https://www.agu.edu.bh/contact-us-2</t>
+        </is>
+      </c>
+      <c r="N796" s="9" t="inlineStr">
+        <is>
+          <t>Also Admission@, StudentAffairs@</t>
+        </is>
+      </c>
+      <c r="O796" s="9" t="inlineStr"/>
+      <c r="P796" s="9" t="inlineStr"/>
+      <c r="Q796" s="9" t="inlineStr"/>
+    </row>
+    <row r="797">
+      <c r="A797" s="9" t="n">
+        <v>796</v>
+      </c>
+      <c r="B797" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C797" s="9" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="D797" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E797" s="9" t="inlineStr">
+        <is>
+          <t>British University of Bahrain</t>
+        </is>
+      </c>
+      <c r="F797" s="9" t="inlineStr"/>
+      <c r="G797" s="9" t="inlineStr"/>
+      <c r="H797" s="9" t="inlineStr">
+        <is>
+          <t>info@bub.bh</t>
+        </is>
+      </c>
+      <c r="I797" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J797" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K797" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for British University of Bahrain</t>
+        </is>
+      </c>
+      <c r="L797" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M797" s="9" t="inlineStr">
+        <is>
+          <t>https://bub.bh/contact-us</t>
+        </is>
+      </c>
+      <c r="N797" s="9" t="inlineStr">
+        <is>
+          <t>General enquiries</t>
+        </is>
+      </c>
+      <c r="O797" s="9" t="inlineStr"/>
+      <c r="P797" s="9" t="inlineStr"/>
+      <c r="Q797" s="9" t="inlineStr"/>
+    </row>
+    <row r="798">
+      <c r="A798" s="9" t="n">
+        <v>797</v>
+      </c>
+      <c r="B798" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C798" s="9" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="D798" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E798" s="9" t="inlineStr">
+        <is>
+          <t>Royal University for Women</t>
+        </is>
+      </c>
+      <c r="F798" s="9" t="inlineStr"/>
+      <c r="G798" s="9" t="inlineStr"/>
+      <c r="H798" s="9" t="inlineStr">
+        <is>
+          <t>info@ruw.edu.bh</t>
+        </is>
+      </c>
+      <c r="I798" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J798" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K798" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Royal University for Women</t>
+        </is>
+      </c>
+      <c r="L798" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M798" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ruw.edu.bh/q=contact-details</t>
+        </is>
+      </c>
+      <c r="N798" s="9" t="inlineStr">
+        <is>
+          <t>Admissions general</t>
+        </is>
+      </c>
+      <c r="O798" s="9" t="inlineStr"/>
+      <c r="P798" s="9" t="inlineStr"/>
+      <c r="Q798" s="9" t="inlineStr"/>
+    </row>
+    <row r="799">
+      <c r="A799" s="9" t="n">
+        <v>798</v>
+      </c>
+      <c r="B799" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C799" s="9" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="D799" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E799" s="9" t="inlineStr">
+        <is>
+          <t>Gulf University Bahrain</t>
+        </is>
+      </c>
+      <c r="F799" s="9" t="inlineStr"/>
+      <c r="G799" s="9" t="inlineStr"/>
+      <c r="H799" s="9" t="inlineStr">
+        <is>
+          <t>info@gulfuniversity.edu.bh</t>
+        </is>
+      </c>
+      <c r="I799" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J799" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K799" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Gulf University Bahrain</t>
+        </is>
+      </c>
+      <c r="L799" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M799" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gulfuniversity.edu.bh/contact-us</t>
+        </is>
+      </c>
+      <c r="N799" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O799" s="9" t="inlineStr"/>
+      <c r="P799" s="9" t="inlineStr"/>
+      <c r="Q799" s="9" t="inlineStr"/>
+    </row>
+    <row r="800">
+      <c r="A800" s="9" t="n">
+        <v>799</v>
+      </c>
+      <c r="B800" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C800" s="9" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="D800" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E800" s="9" t="inlineStr">
+        <is>
+          <t>Kingdom University</t>
+        </is>
+      </c>
+      <c r="F800" s="9" t="inlineStr"/>
+      <c r="G800" s="9" t="inlineStr"/>
+      <c r="H800" s="9" t="inlineStr">
+        <is>
+          <t>info@ku.edu.bh</t>
+        </is>
+      </c>
+      <c r="I800" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J800" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K800" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Kingdom University</t>
+        </is>
+      </c>
+      <c r="L800" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M800" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ku.edu.bh/contact-us</t>
+        </is>
+      </c>
+      <c r="N800" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O800" s="9" t="inlineStr"/>
+      <c r="P800" s="9" t="inlineStr"/>
+      <c r="Q800" s="9" t="inlineStr"/>
+    </row>
+    <row r="801">
+      <c r="A801" s="9" t="n">
+        <v>800</v>
+      </c>
+      <c r="B801" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C801" s="9" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="D801" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E801" s="9" t="inlineStr">
+        <is>
+          <t>University College of Bahrain</t>
+        </is>
+      </c>
+      <c r="F801" s="9" t="inlineStr"/>
+      <c r="G801" s="9" t="inlineStr"/>
+      <c r="H801" s="9" t="inlineStr">
+        <is>
+          <t>info@ucb.edu.bh</t>
+        </is>
+      </c>
+      <c r="I801" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J801" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K801" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University College of Bahrain</t>
+        </is>
+      </c>
+      <c r="L801" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M801" s="9" t="inlineStr">
+        <is>
+          <t>https://ucb.edu.bh/contact-us/</t>
+        </is>
+      </c>
+      <c r="N801" s="9" t="inlineStr">
+        <is>
+          <t>General info</t>
+        </is>
+      </c>
+      <c r="O801" s="9" t="inlineStr"/>
+      <c r="P801" s="9" t="inlineStr"/>
+      <c r="Q801" s="9" t="inlineStr"/>
+    </row>
+    <row r="802">
+      <c r="A802" s="9" t="n">
+        <v>801</v>
+      </c>
+      <c r="B802" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C802" s="9" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="D802" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E802" s="9" t="inlineStr">
+        <is>
+          <t>AMA International University Bahrain</t>
+        </is>
+      </c>
+      <c r="F802" s="9" t="inlineStr"/>
+      <c r="G802" s="9" t="inlineStr"/>
+      <c r="H802" s="9" t="inlineStr">
+        <is>
+          <t>amaiub@amaiu.edu.bh</t>
+        </is>
+      </c>
+      <c r="I802" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J802" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K802" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for AMA International University Bahrain</t>
+        </is>
+      </c>
+      <c r="L802" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M802" s="9" t="inlineStr">
+        <is>
+          <t>https://mymedschool.org (confirmed via amaiu.edu.bh domain)</t>
+        </is>
+      </c>
+      <c r="N802" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O802" s="9" t="inlineStr"/>
+      <c r="P802" s="9" t="inlineStr"/>
+      <c r="Q802" s="9" t="inlineStr"/>
+    </row>
+    <row r="803">
+      <c r="A803" s="9" t="n">
+        <v>802</v>
+      </c>
+      <c r="B803" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C803" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D803" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E803" s="9" t="inlineStr">
+        <is>
+          <t>University of Technology and Applied Sciences Muscat</t>
+        </is>
+      </c>
+      <c r="F803" s="9" t="inlineStr"/>
+      <c r="G803" s="9" t="inlineStr"/>
+      <c r="H803" s="9" t="inlineStr">
+        <is>
+          <t>document@utas.edu.om</t>
+        </is>
+      </c>
+      <c r="I803" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J803" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K803" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Technology and Applied Sciences Muscat</t>
+        </is>
+      </c>
+      <c r="L803" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M803" s="9" t="inlineStr">
+        <is>
+          <t>https://gov.om (UTAS general inquiries)</t>
+        </is>
+      </c>
+      <c r="N803" s="9" t="inlineStr">
+        <is>
+          <t>University-wide general inquiries</t>
+        </is>
+      </c>
+      <c r="O803" s="9" t="inlineStr"/>
+      <c r="P803" s="9" t="inlineStr"/>
+      <c r="Q803" s="9" t="inlineStr"/>
+    </row>
+    <row r="804">
+      <c r="A804" s="9" t="n">
+        <v>803</v>
+      </c>
+      <c r="B804" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C804" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D804" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E804" s="9" t="inlineStr">
+        <is>
+          <t>University of Technology and Applied Sciences Nizwa</t>
+        </is>
+      </c>
+      <c r="F804" s="9" t="inlineStr"/>
+      <c r="G804" s="9" t="inlineStr"/>
+      <c r="H804" s="9" t="inlineStr">
+        <is>
+          <t>niz.etc.info@utas.edu.om</t>
+        </is>
+      </c>
+      <c r="I804" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J804" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K804" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Technology and Applied Sciences Nizwa</t>
+        </is>
+      </c>
+      <c r="L804" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M804" s="9" t="inlineStr">
+        <is>
+          <t>https://www.utas.edu.om/nizwa</t>
+        </is>
+      </c>
+      <c r="N804" s="9" t="inlineStr">
+        <is>
+          <t>General inquiry</t>
+        </is>
+      </c>
+      <c r="O804" s="9" t="inlineStr"/>
+      <c r="P804" s="9" t="inlineStr"/>
+      <c r="Q804" s="9" t="inlineStr"/>
+    </row>
+    <row r="805">
+      <c r="A805" s="9" t="n">
+        <v>804</v>
+      </c>
+      <c r="B805" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C805" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D805" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E805" s="9" t="inlineStr">
+        <is>
+          <t>University of Technology and Applied Sciences Salalah</t>
+        </is>
+      </c>
+      <c r="F805" s="9" t="inlineStr"/>
+      <c r="G805" s="9" t="inlineStr"/>
+      <c r="H805" s="9" t="inlineStr">
+        <is>
+          <t>info.sal@cas.edu.om</t>
+        </is>
+      </c>
+      <c r="I805" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J805" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K805" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Technology and Applied Sciences Salalah</t>
+        </is>
+      </c>
+      <c r="L805" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M805" s="9" t="inlineStr">
+        <is>
+          <t>https://www.utas.edu.om/Branches/Salalah-CAS</t>
+        </is>
+      </c>
+      <c r="N805" s="9" t="inlineStr">
+        <is>
+          <t>Branch contact</t>
+        </is>
+      </c>
+      <c r="O805" s="9" t="inlineStr"/>
+      <c r="P805" s="9" t="inlineStr"/>
+      <c r="Q805" s="9" t="inlineStr"/>
+    </row>
+    <row r="806">
+      <c r="A806" s="9" t="n">
+        <v>805</v>
+      </c>
+      <c r="B806" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C806" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D806" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E806" s="9" t="inlineStr">
+        <is>
+          <t>University of Technology and Applied Sciences Sur</t>
+        </is>
+      </c>
+      <c r="F806" s="9" t="inlineStr"/>
+      <c r="G806" s="9" t="inlineStr"/>
+      <c r="H806" s="9" t="inlineStr">
+        <is>
+          <t>mail.sur@cas.edu.om</t>
+        </is>
+      </c>
+      <c r="I806" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J806" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K806" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Technology and Applied Sciences Sur</t>
+        </is>
+      </c>
+      <c r="L806" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M806" s="9" t="inlineStr">
+        <is>
+          <t>https://www.utas.edu.om/Branches/Sur</t>
+        </is>
+      </c>
+      <c r="N806" s="9" t="inlineStr">
+        <is>
+          <t>Branch contact</t>
+        </is>
+      </c>
+      <c r="O806" s="9" t="inlineStr"/>
+      <c r="P806" s="9" t="inlineStr"/>
+      <c r="Q806" s="9" t="inlineStr"/>
+    </row>
+    <row r="807">
+      <c r="A807" s="9" t="n">
+        <v>806</v>
+      </c>
+      <c r="B807" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C807" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D807" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E807" s="9" t="inlineStr">
+        <is>
+          <t>University of Technology and Applied Sciences Ibra</t>
+        </is>
+      </c>
+      <c r="F807" s="9" t="inlineStr"/>
+      <c r="G807" s="9" t="inlineStr"/>
+      <c r="H807" s="9" t="inlineStr">
+        <is>
+          <t>admin@ict.edu.om</t>
+        </is>
+      </c>
+      <c r="I807" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J807" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K807" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Technology and Applied Sciences Ibra</t>
+        </is>
+      </c>
+      <c r="L807" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M807" s="9" t="inlineStr">
+        <is>
+          <t>https://www.utas.edu.om/Branches/Ibra</t>
+        </is>
+      </c>
+      <c r="N807" s="9" t="inlineStr">
+        <is>
+          <t>Branch contact</t>
+        </is>
+      </c>
+      <c r="O807" s="9" t="inlineStr"/>
+      <c r="P807" s="9" t="inlineStr"/>
+      <c r="Q807" s="9" t="inlineStr"/>
+    </row>
+    <row r="808">
+      <c r="A808" s="9" t="n">
+        <v>807</v>
+      </c>
+      <c r="B808" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C808" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D808" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E808" s="9" t="inlineStr">
+        <is>
+          <t>University of Technology and Applied Sciences Sohar</t>
+        </is>
+      </c>
+      <c r="F808" s="9" t="inlineStr"/>
+      <c r="G808" s="9" t="inlineStr"/>
+      <c r="H808" s="9" t="inlineStr">
+        <is>
+          <t>dean_office.soh@cas.edu.om</t>
+        </is>
+      </c>
+      <c r="I808" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J808" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K808" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Technology and Applied Sciences Sohar</t>
+        </is>
+      </c>
+      <c r="L808" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M808" s="9" t="inlineStr">
+        <is>
+          <t>https://www.utas.edu.om/Branches/Suhar</t>
+        </is>
+      </c>
+      <c r="N808" s="9" t="inlineStr">
+        <is>
+          <t>Also info.soh@cas.edu.om</t>
+        </is>
+      </c>
+      <c r="O808" s="9" t="inlineStr"/>
+      <c r="P808" s="9" t="inlineStr"/>
+      <c r="Q808" s="9" t="inlineStr"/>
+    </row>
+    <row r="809">
+      <c r="A809" s="9" t="n">
+        <v>808</v>
+      </c>
+      <c r="B809" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C809" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D809" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E809" s="9" t="inlineStr">
+        <is>
+          <t>University of Technology and Applied Sciences Shinas</t>
+        </is>
+      </c>
+      <c r="F809" s="9" t="inlineStr"/>
+      <c r="G809" s="9" t="inlineStr"/>
+      <c r="H809" s="9" t="inlineStr">
+        <is>
+          <t>mmc@utas.edu.om</t>
+        </is>
+      </c>
+      <c r="I809" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J809" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K809" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Technology and Applied Sciences Shinas</t>
+        </is>
+      </c>
+      <c r="L809" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M809" s="9" t="inlineStr">
+        <is>
+          <t>https://www.utas.edu.om/shinas</t>
+        </is>
+      </c>
+      <c r="N809" s="9" t="inlineStr">
+        <is>
+          <t>General inquiry</t>
+        </is>
+      </c>
+      <c r="O809" s="9" t="inlineStr"/>
+      <c r="P809" s="9" t="inlineStr"/>
+      <c r="Q809" s="9" t="inlineStr"/>
+    </row>
+    <row r="810">
+      <c r="A810" s="9" t="n">
+        <v>809</v>
+      </c>
+      <c r="B810" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C810" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D810" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E810" s="9" t="inlineStr">
+        <is>
+          <t>University of Technology and Applied Sciences Ibri</t>
+        </is>
+      </c>
+      <c r="F810" s="9" t="inlineStr"/>
+      <c r="G810" s="9" t="inlineStr"/>
+      <c r="H810" s="9" t="inlineStr">
+        <is>
+          <t>ibrict@ibrict.edu.om</t>
+        </is>
+      </c>
+      <c r="I810" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J810" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K810" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Technology and Applied Sciences Ibri</t>
+        </is>
+      </c>
+      <c r="L810" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M810" s="9" t="inlineStr">
+        <is>
+          <t>https://www.utas.edu.om/ibri</t>
+        </is>
+      </c>
+      <c r="N810" s="9" t="inlineStr">
+        <is>
+          <t>General inquiry</t>
+        </is>
+      </c>
+      <c r="O810" s="9" t="inlineStr"/>
+      <c r="P810" s="9" t="inlineStr"/>
+      <c r="Q810" s="9" t="inlineStr"/>
+    </row>
+    <row r="811">
+      <c r="A811" s="9" t="n">
+        <v>810</v>
+      </c>
+      <c r="B811" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C811" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D811" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E811" s="9" t="inlineStr">
+        <is>
+          <t>University of Technology and Applied Sciences Musannah</t>
+        </is>
+      </c>
+      <c r="F811" s="9" t="inlineStr"/>
+      <c r="G811" s="9" t="inlineStr"/>
+      <c r="H811" s="9" t="inlineStr">
+        <is>
+          <t>utasa.info@act.edu.om</t>
+        </is>
+      </c>
+      <c r="I811" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J811" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K811" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Technology and Applied Sciences Musannah</t>
+        </is>
+      </c>
+      <c r="L811" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M811" s="9" t="inlineStr">
+        <is>
+          <t>https://www.utas.edu.om/mussanah</t>
+        </is>
+      </c>
+      <c r="N811" s="9" t="inlineStr">
+        <is>
+          <t>Branch general inquiry</t>
+        </is>
+      </c>
+      <c r="O811" s="9" t="inlineStr"/>
+      <c r="P811" s="9" t="inlineStr"/>
+      <c r="Q811" s="9" t="inlineStr"/>
+    </row>
+    <row r="812">
+      <c r="A812" s="9" t="n">
+        <v>811</v>
+      </c>
+      <c r="B812" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C812" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D812" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E812" s="9" t="inlineStr">
+        <is>
+          <t>German University of Technology in Oman</t>
+        </is>
+      </c>
+      <c r="F812" s="9" t="inlineStr"/>
+      <c r="G812" s="9" t="inlineStr"/>
+      <c r="H812" s="9" t="inlineStr">
+        <is>
+          <t>info@gutech.edu.om</t>
+        </is>
+      </c>
+      <c r="I812" s="9" t="inlineStr">
+        <is>
+          <t>On hold (prior contact)</t>
+        </is>
+      </c>
+      <c r="J812" s="9" t="inlineStr"/>
+      <c r="K812" s="9" t="inlineStr"/>
+      <c r="L812" s="9" t="inlineStr"/>
+      <c r="M812" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gutech.edu.om/contact</t>
+        </is>
+      </c>
+      <c r="N812" s="9" t="inlineStr">
+        <is>
+          <t>Also study@gutech.edu.om | Prior contact found (thread to ees@gutech.edu.om, 2026-09-26)</t>
+        </is>
+      </c>
+      <c r="O812" s="9" t="inlineStr"/>
+      <c r="P812" s="9" t="inlineStr"/>
+      <c r="Q812" s="9" t="inlineStr"/>
+    </row>
+    <row r="813">
+      <c r="A813" s="9" t="n">
+        <v>812</v>
+      </c>
+      <c r="B813" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C813" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D813" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E813" s="9" t="inlineStr">
+        <is>
+          <t>University of Nizwa</t>
+        </is>
+      </c>
+      <c r="F813" s="9" t="inlineStr"/>
+      <c r="G813" s="9" t="inlineStr"/>
+      <c r="H813" s="9" t="inlineStr">
+        <is>
+          <t>fi-admin@unizwa.edu.om</t>
+        </is>
+      </c>
+      <c r="I813" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J813" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K813" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Nizwa</t>
+        </is>
+      </c>
+      <c r="L813" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M813" s="9" t="inlineStr">
+        <is>
+          <t>https://www.unizwa.edu.om/contactus</t>
+        </is>
+      </c>
+      <c r="N813" s="9" t="inlineStr">
+        <is>
+          <t>General Information</t>
+        </is>
+      </c>
+      <c r="O813" s="9" t="inlineStr"/>
+      <c r="P813" s="9" t="inlineStr"/>
+      <c r="Q813" s="9" t="inlineStr"/>
+    </row>
+    <row r="814">
+      <c r="A814" s="9" t="n">
+        <v>813</v>
+      </c>
+      <c r="B814" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C814" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D814" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E814" s="9" t="inlineStr">
+        <is>
+          <t>Sohar University</t>
+        </is>
+      </c>
+      <c r="F814" s="9" t="inlineStr"/>
+      <c r="G814" s="9" t="inlineStr"/>
+      <c r="H814" s="9" t="inlineStr">
+        <is>
+          <t>rd@su.edu.om</t>
+        </is>
+      </c>
+      <c r="I814" s="9" t="inlineStr">
+        <is>
+          <t>On hold (prior contact)</t>
+        </is>
+      </c>
+      <c r="J814" s="9" t="inlineStr"/>
+      <c r="K814" s="9" t="inlineStr"/>
+      <c r="L814" s="9" t="inlineStr"/>
+      <c r="M814" s="9" t="inlineStr">
+        <is>
+          <t>https://research.su.edu.om/research-impact</t>
+        </is>
+      </c>
+      <c r="N814" s="9" t="inlineStr">
+        <is>
+          <t>Research &amp; Innovation office | Prior contact found (thread to thinai@su.edu.om, 2026-09-26)</t>
+        </is>
+      </c>
+      <c r="O814" s="9" t="inlineStr"/>
+      <c r="P814" s="9" t="inlineStr"/>
+      <c r="Q814" s="9" t="inlineStr"/>
+    </row>
+    <row r="815">
+      <c r="A815" s="9" t="n">
+        <v>814</v>
+      </c>
+      <c r="B815" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C815" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D815" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E815" s="9" t="inlineStr">
+        <is>
+          <t>A'Sharqiyah University</t>
+        </is>
+      </c>
+      <c r="F815" s="9" t="inlineStr"/>
+      <c r="G815" s="9" t="inlineStr"/>
+      <c r="H815" s="9" t="inlineStr">
+        <is>
+          <t>info@asu.edu.om</t>
+        </is>
+      </c>
+      <c r="I815" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J815" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K815" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for A'Sharqiyah University</t>
+        </is>
+      </c>
+      <c r="L815" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M815" s="9" t="inlineStr">
+        <is>
+          <t>https://www.asu.edu.om/QAA/Contact</t>
+        </is>
+      </c>
+      <c r="N815" s="9" t="inlineStr">
+        <is>
+          <t>General inquiries</t>
+        </is>
+      </c>
+      <c r="O815" s="9" t="inlineStr"/>
+      <c r="P815" s="9" t="inlineStr"/>
+      <c r="Q815" s="9" t="inlineStr"/>
+    </row>
+    <row r="816">
+      <c r="A816" s="9" t="n">
+        <v>815</v>
+      </c>
+      <c r="B816" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C816" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D816" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E816" s="9" t="inlineStr">
+        <is>
+          <t>Gulf College</t>
+        </is>
+      </c>
+      <c r="F816" s="9" t="inlineStr"/>
+      <c r="G816" s="9" t="inlineStr"/>
+      <c r="H816" s="9" t="inlineStr">
+        <is>
+          <t>enquiry@gulfcollege.edu.om</t>
+        </is>
+      </c>
+      <c r="I816" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J816" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K816" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Gulf College</t>
+        </is>
+      </c>
+      <c r="L816" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M816" s="9" t="inlineStr">
+        <is>
+          <t>https://gulfcollege.edu.om/submit-ticket</t>
+        </is>
+      </c>
+      <c r="N816" s="9" t="inlineStr">
+        <is>
+          <t>General enquiry</t>
+        </is>
+      </c>
+      <c r="O816" s="9" t="inlineStr"/>
+      <c r="P816" s="9" t="inlineStr"/>
+      <c r="Q816" s="9" t="inlineStr"/>
+    </row>
+    <row r="817">
+      <c r="A817" s="9" t="n">
+        <v>816</v>
+      </c>
+      <c r="B817" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C817" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D817" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E817" s="9" t="inlineStr">
+        <is>
+          <t>Modern College of Business and Science</t>
+        </is>
+      </c>
+      <c r="F817" s="9" t="inlineStr"/>
+      <c r="G817" s="9" t="inlineStr"/>
+      <c r="H817" s="9" t="inlineStr">
+        <is>
+          <t>info@mcbs.edu.om</t>
+        </is>
+      </c>
+      <c r="I817" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J817" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K817" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Modern College of Business and Science</t>
+        </is>
+      </c>
+      <c r="L817" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M817" s="9" t="inlineStr">
+        <is>
+          <t>https://www.mcbs.edu.om/contact-us</t>
+        </is>
+      </c>
+      <c r="N817" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O817" s="9" t="inlineStr"/>
+      <c r="P817" s="9" t="inlineStr"/>
+      <c r="Q817" s="9" t="inlineStr"/>
+    </row>
+    <row r="818">
+      <c r="A818" s="9" t="n">
+        <v>817</v>
+      </c>
+      <c r="B818" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C818" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D818" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E818" s="9" t="inlineStr">
+        <is>
+          <t>Oman College of Management and Technology</t>
+        </is>
+      </c>
+      <c r="F818" s="9" t="inlineStr"/>
+      <c r="G818" s="9" t="inlineStr"/>
+      <c r="H818" s="9" t="inlineStr">
+        <is>
+          <t>omancollege@ocmt.edu.om</t>
+        </is>
+      </c>
+      <c r="I818" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J818" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K818" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Oman College of Management and Technology</t>
+        </is>
+      </c>
+      <c r="L818" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M818" s="9" t="inlineStr">
+        <is>
+          <t>https://ocmt.odoo.com/contactus</t>
+        </is>
+      </c>
+      <c r="N818" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O818" s="9" t="inlineStr"/>
+      <c r="P818" s="9" t="inlineStr"/>
+      <c r="Q818" s="9" t="inlineStr"/>
+    </row>
+    <row r="819">
+      <c r="A819" s="9" t="n">
+        <v>818</v>
+      </c>
+      <c r="B819" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C819" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D819" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E819" s="9" t="inlineStr">
+        <is>
+          <t>Al Buraimi University College</t>
+        </is>
+      </c>
+      <c r="F819" s="9" t="inlineStr"/>
+      <c r="G819" s="9" t="inlineStr"/>
+      <c r="H819" s="9" t="inlineStr">
+        <is>
+          <t>info@buc.edu.om</t>
+        </is>
+      </c>
+      <c r="I819" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J819" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K819" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Al Buraimi University College</t>
+        </is>
+      </c>
+      <c r="L819" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M819" s="9" t="inlineStr">
+        <is>
+          <t>https://buc.edu.om/contact-us</t>
+        </is>
+      </c>
+      <c r="N819" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O819" s="9" t="inlineStr"/>
+      <c r="P819" s="9" t="inlineStr"/>
+      <c r="Q819" s="9" t="inlineStr"/>
+    </row>
+    <row r="820">
+      <c r="A820" s="9" t="n">
+        <v>819</v>
+      </c>
+      <c r="B820" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C820" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D820" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E820" s="9" t="inlineStr">
+        <is>
+          <t>Majan University College</t>
+        </is>
+      </c>
+      <c r="F820" s="9" t="inlineStr"/>
+      <c r="G820" s="9" t="inlineStr"/>
+      <c r="H820" s="9" t="inlineStr">
+        <is>
+          <t>info@majancollege.edu.om</t>
+        </is>
+      </c>
+      <c r="I820" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J820" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K820" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Majan University College</t>
+        </is>
+      </c>
+      <c r="L820" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M820" s="9" t="inlineStr">
+        <is>
+          <t>https://majancollege.edu.om/contact/contact-us</t>
+        </is>
+      </c>
+      <c r="N820" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O820" s="9" t="inlineStr"/>
+      <c r="P820" s="9" t="inlineStr"/>
+      <c r="Q820" s="9" t="inlineStr"/>
+    </row>
+    <row r="821">
+      <c r="A821" s="9" t="n">
+        <v>820</v>
+      </c>
+      <c r="B821" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C821" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D821" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E821" s="9" t="inlineStr">
+        <is>
+          <t>Mazoon College</t>
+        </is>
+      </c>
+      <c r="F821" s="9" t="inlineStr"/>
+      <c r="G821" s="9" t="inlineStr"/>
+      <c r="H821" s="9" t="inlineStr">
+        <is>
+          <t>info@mazcol.edu.om</t>
+        </is>
+      </c>
+      <c r="I821" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J821" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K821" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Mazoon College</t>
+        </is>
+      </c>
+      <c r="L821" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M821" s="9" t="inlineStr">
+        <is>
+          <t>https://yellowpages.om (confirmed via mazcol.edu.om domain)</t>
+        </is>
+      </c>
+      <c r="N821" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O821" s="9" t="inlineStr"/>
+      <c r="P821" s="9" t="inlineStr"/>
+      <c r="Q821" s="9" t="inlineStr"/>
+    </row>
+    <row r="822">
+      <c r="A822" s="9" t="n">
+        <v>821</v>
+      </c>
+      <c r="B822" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C822" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D822" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E822" s="9" t="inlineStr">
+        <is>
+          <t>Bayan College</t>
+        </is>
+      </c>
+      <c r="F822" s="9" t="inlineStr"/>
+      <c r="G822" s="9" t="inlineStr"/>
+      <c r="H822" s="9" t="inlineStr">
+        <is>
+          <t>info@bayancollege.edu.om</t>
+        </is>
+      </c>
+      <c r="I822" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J822" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K822" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Bayan College</t>
+        </is>
+      </c>
+      <c r="L822" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M822" s="9" t="inlineStr">
+        <is>
+          <t>https://bayancollege.edu.om/contact</t>
+        </is>
+      </c>
+      <c r="N822" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O822" s="9" t="inlineStr"/>
+      <c r="P822" s="9" t="inlineStr"/>
+      <c r="Q822" s="9" t="inlineStr"/>
+    </row>
+    <row r="823">
+      <c r="A823" s="9" t="n">
+        <v>822</v>
+      </c>
+      <c r="B823" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C823" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D823" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E823" s="9" t="inlineStr">
+        <is>
+          <t>Waljat College of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="F823" s="9" t="inlineStr"/>
+      <c r="G823" s="9" t="inlineStr"/>
+      <c r="H823" s="9" t="inlineStr">
+        <is>
+          <t>info@waljat.net</t>
+        </is>
+      </c>
+      <c r="I823" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J823" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K823" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Waljat College of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="L823" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M823" s="9" t="inlineStr">
+        <is>
+          <t>https://www.businessstartupoman.com</t>
+        </is>
+      </c>
+      <c r="N823" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O823" s="9" t="inlineStr"/>
+      <c r="P823" s="9" t="inlineStr"/>
+      <c r="Q823" s="9" t="inlineStr"/>
+    </row>
+    <row r="824">
+      <c r="A824" s="9" t="n">
+        <v>823</v>
+      </c>
+      <c r="B824" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C824" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D824" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E824" s="9" t="inlineStr">
+        <is>
+          <t>Sur University College</t>
+        </is>
+      </c>
+      <c r="F824" s="9" t="inlineStr"/>
+      <c r="G824" s="9" t="inlineStr"/>
+      <c r="H824" s="9" t="inlineStr">
+        <is>
+          <t>suc@suc.edu.om</t>
+        </is>
+      </c>
+      <c r="I824" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J824" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K824" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Sur University College</t>
+        </is>
+      </c>
+      <c r="L824" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M824" s="9" t="inlineStr">
+        <is>
+          <t>https://www.businessstartupoman.com</t>
+        </is>
+      </c>
+      <c r="N824" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O824" s="9" t="inlineStr"/>
+      <c r="P824" s="9" t="inlineStr"/>
+      <c r="Q824" s="9" t="inlineStr"/>
+    </row>
+    <row r="825">
+      <c r="A825" s="9" t="n">
+        <v>824</v>
+      </c>
+      <c r="B825" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C825" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D825" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E825" s="9" t="inlineStr">
+        <is>
+          <t>International Maritime College Oman</t>
+        </is>
+      </c>
+      <c r="F825" s="9" t="inlineStr"/>
+      <c r="G825" s="9" t="inlineStr"/>
+      <c r="H825" s="9" t="inlineStr">
+        <is>
+          <t>marketing@imco.edu.om</t>
+        </is>
+      </c>
+      <c r="I825" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J825" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K825" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for International Maritime College Oman</t>
+        </is>
+      </c>
+      <c r="L825" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M825" s="9" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/InternationalMaritimeCollegeOman (confirmed via imco.edu.om domain)</t>
+        </is>
+      </c>
+      <c r="N825" s="9" t="inlineStr">
+        <is>
+          <t>General/marketing contact</t>
+        </is>
+      </c>
+      <c r="O825" s="9" t="inlineStr"/>
+      <c r="P825" s="9" t="inlineStr"/>
+      <c r="Q825" s="9" t="inlineStr"/>
+    </row>
+    <row r="826">
+      <c r="A826" s="9" t="n">
+        <v>825</v>
+      </c>
+      <c r="B826" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C826" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D826" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E826" s="9" t="inlineStr">
+        <is>
+          <t>Australian National University</t>
+        </is>
+      </c>
+      <c r="F826" s="9" t="inlineStr"/>
+      <c r="G826" s="9" t="inlineStr"/>
+      <c r="H826" s="9" t="inlineStr">
+        <is>
+          <t>admin.eng@anu.edu.au</t>
+        </is>
+      </c>
+      <c r="I826" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J826" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K826" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Australian National University</t>
+        </is>
+      </c>
+      <c r="L826" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M826" s="9" t="inlineStr">
+        <is>
+          <t>https://eng.anu.edu.au/about</t>
+        </is>
+      </c>
+      <c r="N826" s="9" t="inlineStr">
+        <is>
+          <t>School of Engineering general enquiries</t>
+        </is>
+      </c>
+      <c r="O826" s="9" t="inlineStr"/>
+      <c r="P826" s="9" t="inlineStr"/>
+      <c r="Q826" s="9" t="inlineStr"/>
+    </row>
+    <row r="827">
+      <c r="A827" s="9" t="n">
+        <v>826</v>
+      </c>
+      <c r="B827" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C827" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D827" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E827" s="9" t="inlineStr">
+        <is>
+          <t>University of Canberra</t>
+        </is>
+      </c>
+      <c r="F827" s="9" t="inlineStr"/>
+      <c r="G827" s="9" t="inlineStr"/>
+      <c r="H827" s="9" t="inlineStr">
+        <is>
+          <t>international@canberra.edu.au</t>
+        </is>
+      </c>
+      <c r="I827" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J827" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K827" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Canberra</t>
+        </is>
+      </c>
+      <c r="L827" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M827" s="9" t="inlineStr">
+        <is>
+          <t>https://myunisearch.com/study/australia/contact</t>
+        </is>
+      </c>
+      <c r="N827" s="9" t="inlineStr">
+        <is>
+          <t>International enquiries (best verified)</t>
+        </is>
+      </c>
+      <c r="O827" s="9" t="inlineStr"/>
+      <c r="P827" s="9" t="inlineStr"/>
+      <c r="Q827" s="9" t="inlineStr"/>
+    </row>
+    <row r="828">
+      <c r="A828" s="9" t="n">
+        <v>827</v>
+      </c>
+      <c r="B828" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C828" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D828" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E828" s="9" t="inlineStr">
+        <is>
+          <t>University of Sydney</t>
+        </is>
+      </c>
+      <c r="F828" s="9" t="inlineStr"/>
+      <c r="G828" s="9" t="inlineStr"/>
+      <c r="H828" s="9" t="inlineStr">
+        <is>
+          <t>engineering.external@sydney.edu.au</t>
+        </is>
+      </c>
+      <c r="I828" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J828" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K828" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Sydney</t>
+        </is>
+      </c>
+      <c r="L828" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M828" s="9" t="inlineStr">
+        <is>
+          <t>https://www.sydney.edu.au/industry-community/partner-with-us</t>
+        </is>
+      </c>
+      <c r="N828" s="9" t="inlineStr">
+        <is>
+          <t>Faculty of Engineering industry partnerships</t>
+        </is>
+      </c>
+      <c r="O828" s="9" t="inlineStr"/>
+      <c r="P828" s="9" t="inlineStr"/>
+      <c r="Q828" s="9" t="inlineStr"/>
+    </row>
+    <row r="829">
+      <c r="A829" s="9" t="n">
+        <v>828</v>
+      </c>
+      <c r="B829" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C829" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D829" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E829" s="9" t="inlineStr">
+        <is>
+          <t>University of New South Wales</t>
+        </is>
+      </c>
+      <c r="F829" s="9" t="inlineStr"/>
+      <c r="G829" s="9" t="inlineStr"/>
+      <c r="H829" s="9" t="inlineStr">
+        <is>
+          <t>engpartners@unsw.edu.au</t>
+        </is>
+      </c>
+      <c r="I829" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J829" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K829" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of New South Wales</t>
+        </is>
+      </c>
+      <c r="L829" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M829" s="9" t="inlineStr">
+        <is>
+          <t>https://www.unsw.edu.au/engineering/alumni-industry</t>
+        </is>
+      </c>
+      <c r="N829" s="9" t="inlineStr">
+        <is>
+          <t>Industry &amp; alumni engagement</t>
+        </is>
+      </c>
+      <c r="O829" s="9" t="inlineStr"/>
+      <c r="P829" s="9" t="inlineStr"/>
+      <c r="Q829" s="9" t="inlineStr"/>
+    </row>
+    <row r="830">
+      <c r="A830" s="9" t="n">
+        <v>829</v>
+      </c>
+      <c r="B830" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C830" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D830" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E830" s="9" t="inlineStr">
+        <is>
+          <t>University of Technology Sydney</t>
+        </is>
+      </c>
+      <c r="F830" s="9" t="inlineStr"/>
+      <c r="G830" s="9" t="inlineStr"/>
+      <c r="H830" s="9" t="inlineStr">
+        <is>
+          <t>industry@uts.edu.au</t>
+        </is>
+      </c>
+      <c r="I830" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J830" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K830" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Technology Sydney</t>
+        </is>
+      </c>
+      <c r="L830" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M830" s="9" t="inlineStr">
+        <is>
+          <t>https://www.uts.edu.au/contact-us</t>
+        </is>
+      </c>
+      <c r="N830" s="9" t="inlineStr">
+        <is>
+          <t>Industry engagement</t>
+        </is>
+      </c>
+      <c r="O830" s="9" t="inlineStr"/>
+      <c r="P830" s="9" t="inlineStr"/>
+      <c r="Q830" s="9" t="inlineStr"/>
+    </row>
+    <row r="831">
+      <c r="A831" s="9" t="n">
+        <v>830</v>
+      </c>
+      <c r="B831" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C831" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D831" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E831" s="9" t="inlineStr">
+        <is>
+          <t>Macquarie University</t>
+        </is>
+      </c>
+      <c r="F831" s="9" t="inlineStr"/>
+      <c r="G831" s="9" t="inlineStr"/>
+      <c r="H831" s="9" t="inlineStr">
+        <is>
+          <t>fse.partnerships@mq.edu.au</t>
+        </is>
+      </c>
+      <c r="I831" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J831" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K831" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Macquarie University</t>
+        </is>
+      </c>
+      <c r="L831" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M831" s="9" t="inlineStr">
+        <is>
+          <t>https://www.mq.edu.au/strategic-partnerships</t>
+        </is>
+      </c>
+      <c r="N831" s="9" t="inlineStr">
+        <is>
+          <t>Faculty of Science and Engineering partnerships</t>
+        </is>
+      </c>
+      <c r="O831" s="9" t="inlineStr"/>
+      <c r="P831" s="9" t="inlineStr"/>
+      <c r="Q831" s="9" t="inlineStr"/>
+    </row>
+    <row r="832">
+      <c r="A832" s="9" t="n">
+        <v>831</v>
+      </c>
+      <c r="B832" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C832" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D832" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E832" s="9" t="inlineStr">
+        <is>
+          <t>University of Newcastle</t>
+        </is>
+      </c>
+      <c r="F832" s="9" t="inlineStr"/>
+      <c r="G832" s="9" t="inlineStr"/>
+      <c r="H832" s="9" t="inlineStr">
+        <is>
+          <t>international-enquiries@newcastle.edu.au</t>
+        </is>
+      </c>
+      <c r="I832" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J832" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K832" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Newcastle</t>
+        </is>
+      </c>
+      <c r="L832" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M832" s="9" t="inlineStr">
+        <is>
+          <t>https://www.newcastle.edu.au (Our Uni contact page)</t>
+        </is>
+      </c>
+      <c r="N832" s="9" t="inlineStr">
+        <is>
+          <t>General/international enquiries</t>
+        </is>
+      </c>
+      <c r="O832" s="9" t="inlineStr"/>
+      <c r="P832" s="9" t="inlineStr"/>
+      <c r="Q832" s="9" t="inlineStr"/>
+    </row>
+    <row r="833">
+      <c r="A833" s="9" t="n">
+        <v>832</v>
+      </c>
+      <c r="B833" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C833" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D833" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E833" s="9" t="inlineStr">
+        <is>
+          <t>University of Wollongong</t>
+        </is>
+      </c>
+      <c r="F833" s="9" t="inlineStr"/>
+      <c r="G833" s="9" t="inlineStr"/>
+      <c r="H833" s="9" t="inlineStr">
+        <is>
+          <t>futurestudents@uow.edu.au</t>
+        </is>
+      </c>
+      <c r="I833" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J833" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K833" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Wollongong</t>
+        </is>
+      </c>
+      <c r="L833" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M833" s="9" t="inlineStr">
+        <is>
+          <t>https://www.uow.edu.au/contact-us</t>
+        </is>
+      </c>
+      <c r="N833" s="9" t="inlineStr">
+        <is>
+          <t>General enquiries</t>
+        </is>
+      </c>
+      <c r="O833" s="9" t="inlineStr"/>
+      <c r="P833" s="9" t="inlineStr"/>
+      <c r="Q833" s="9" t="inlineStr"/>
+    </row>
+    <row r="834">
+      <c r="A834" s="9" t="n">
+        <v>833</v>
+      </c>
+      <c r="B834" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C834" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D834" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E834" s="9" t="inlineStr">
+        <is>
+          <t>Western Sydney University</t>
+        </is>
+      </c>
+      <c r="F834" s="9" t="inlineStr"/>
+      <c r="G834" s="9" t="inlineStr"/>
+      <c r="H834" s="9" t="inlineStr">
+        <is>
+          <t>gateway@westernsydney.edu.au</t>
+        </is>
+      </c>
+      <c r="I834" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J834" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K834" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Western Sydney University</t>
+        </is>
+      </c>
+      <c r="L834" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M834" s="9" t="inlineStr">
+        <is>
+          <t>https://www.westernsydney.edu.au (Contact Us)</t>
+        </is>
+      </c>
+      <c r="N834" s="9" t="inlineStr">
+        <is>
+          <t>Business, industry, community and government enquiries</t>
+        </is>
+      </c>
+      <c r="O834" s="9" t="inlineStr"/>
+      <c r="P834" s="9" t="inlineStr"/>
+      <c r="Q834" s="9" t="inlineStr"/>
+    </row>
+    <row r="835">
+      <c r="A835" s="9" t="n">
+        <v>834</v>
+      </c>
+      <c r="B835" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C835" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D835" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E835" s="9" t="inlineStr">
+        <is>
+          <t>Charles Sturt University</t>
+        </is>
+      </c>
+      <c r="F835" s="9" t="inlineStr"/>
+      <c r="G835" s="9" t="inlineStr"/>
+      <c r="H835" s="9" t="inlineStr">
+        <is>
+          <t>engineering@csu.edu.au</t>
+        </is>
+      </c>
+      <c r="I835" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J835" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K835" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Charles Sturt University</t>
+        </is>
+      </c>
+      <c r="L835" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M835" s="9" t="inlineStr">
+        <is>
+          <t>https://www.csu.edu.au/engineering/contact-us</t>
+        </is>
+      </c>
+      <c r="N835" s="9" t="inlineStr">
+        <is>
+          <t>Engineering general contact</t>
+        </is>
+      </c>
+      <c r="O835" s="9" t="inlineStr"/>
+      <c r="P835" s="9" t="inlineStr"/>
+      <c r="Q835" s="9" t="inlineStr"/>
+    </row>
+    <row r="836">
+      <c r="A836" s="9" t="n">
+        <v>835</v>
+      </c>
+      <c r="B836" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C836" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D836" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E836" s="9" t="inlineStr">
+        <is>
+          <t>Southern Cross University</t>
+        </is>
+      </c>
+      <c r="F836" s="9" t="inlineStr"/>
+      <c r="G836" s="9" t="inlineStr"/>
+      <c r="H836" s="9" t="inlineStr">
+        <is>
+          <t>fseinfo@scu.edu.au</t>
+        </is>
+      </c>
+      <c r="I836" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J836" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K836" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Southern Cross University</t>
+        </is>
+      </c>
+      <c r="L836" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M836" s="9" t="inlineStr">
+        <is>
+          <t>https://www.scu.edu.au/science-and-engineering</t>
+        </is>
+      </c>
+      <c r="N836" s="9" t="inlineStr">
+        <is>
+          <t>Faculty of Science and Engineering</t>
+        </is>
+      </c>
+      <c r="O836" s="9" t="inlineStr"/>
+      <c r="P836" s="9" t="inlineStr"/>
+      <c r="Q836" s="9" t="inlineStr"/>
+    </row>
+    <row r="837">
+      <c r="A837" s="9" t="n">
+        <v>836</v>
+      </c>
+      <c r="B837" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C837" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D837" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E837" s="9" t="inlineStr">
+        <is>
+          <t>University of New England</t>
+        </is>
+      </c>
+      <c r="F837" s="9" t="inlineStr"/>
+      <c r="G837" s="9" t="inlineStr"/>
+      <c r="H837" s="9" t="inlineStr">
+        <is>
+          <t>marketing@une.edu.au</t>
+        </is>
+      </c>
+      <c r="I837" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J837" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K837" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of New England</t>
+        </is>
+      </c>
+      <c r="L837" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M837" s="9" t="inlineStr">
+        <is>
+          <t>http://www.myregion.au (confirmed via une.edu.au domain)</t>
+        </is>
+      </c>
+      <c r="N837" s="9" t="inlineStr">
+        <is>
+          <t>General/marketing contact</t>
+        </is>
+      </c>
+      <c r="O837" s="9" t="inlineStr"/>
+      <c r="P837" s="9" t="inlineStr"/>
+      <c r="Q837" s="9" t="inlineStr"/>
+    </row>
+    <row r="838">
+      <c r="A838" s="9" t="n">
+        <v>837</v>
+      </c>
+      <c r="B838" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C838" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D838" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E838" s="9" t="inlineStr">
+        <is>
+          <t>University of Melbourne</t>
+        </is>
+      </c>
+      <c r="F838" s="9" t="inlineStr"/>
+      <c r="G838" s="9" t="inlineStr"/>
+      <c r="H838" s="9" t="inlineStr">
+        <is>
+          <t>engagement@unimelb.edu.au</t>
+        </is>
+      </c>
+      <c r="I838" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J838" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K838" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Melbourne</t>
+        </is>
+      </c>
+      <c r="L838" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M838" s="9" t="inlineStr">
+        <is>
+          <t>https://eng.unimelb.edu.au/About</t>
+        </is>
+      </c>
+      <c r="N838" s="9" t="inlineStr">
+        <is>
+          <t>Faculty of Engineering and IT engagement</t>
+        </is>
+      </c>
+      <c r="O838" s="9" t="inlineStr"/>
+      <c r="P838" s="9" t="inlineStr"/>
+      <c r="Q838" s="9" t="inlineStr"/>
+    </row>
+    <row r="839">
+      <c r="A839" s="9" t="n">
+        <v>838</v>
+      </c>
+      <c r="B839" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C839" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D839" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E839" s="9" t="inlineStr">
+        <is>
+          <t>Monash University</t>
+        </is>
+      </c>
+      <c r="F839" s="9" t="inlineStr"/>
+      <c r="G839" s="9" t="inlineStr"/>
+      <c r="H839" s="9" t="inlineStr">
+        <is>
+          <t>eng-gradresearch@monash.edu</t>
+        </is>
+      </c>
+      <c r="I839" s="9" t="inlineStr">
+        <is>
+          <t>On hold (prior contact)</t>
+        </is>
+      </c>
+      <c r="J839" s="9" t="inlineStr"/>
+      <c r="K839" s="9" t="inlineStr"/>
+      <c r="L839" s="9" t="inlineStr"/>
+      <c r="M839" s="9" t="inlineStr">
+        <is>
+          <t>https://www.monash.edu/industry-doctoral-program</t>
+        </is>
+      </c>
+      <c r="N839" s="9" t="inlineStr">
+        <is>
+          <t>Engineering Graduate Research Office | Prior contact found (Monash Malaysia eiHub, sent 2026-09-26)</t>
+        </is>
+      </c>
+      <c r="O839" s="9" t="inlineStr"/>
+      <c r="P839" s="9" t="inlineStr"/>
+      <c r="Q839" s="9" t="inlineStr"/>
+    </row>
+    <row r="840">
+      <c r="A840" s="9" t="n">
+        <v>839</v>
+      </c>
+      <c r="B840" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C840" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D840" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E840" s="9" t="inlineStr">
+        <is>
+          <t>RMIT University</t>
+        </is>
+      </c>
+      <c r="F840" s="9" t="inlineStr"/>
+      <c r="G840" s="9" t="inlineStr"/>
+      <c r="H840" s="9" t="inlineStr">
+        <is>
+          <t>STEM-Industry@rmit.edu.au</t>
+        </is>
+      </c>
+      <c r="I840" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J840" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K840" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for RMIT University</t>
+        </is>
+      </c>
+      <c r="L840" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M840" s="9" t="inlineStr">
+        <is>
+          <t>https://www.rmit.edu.au/work-integrated-learning/engineering</t>
+        </is>
+      </c>
+      <c r="N840" s="9" t="inlineStr">
+        <is>
+          <t>Engineering industry engagement</t>
+        </is>
+      </c>
+      <c r="O840" s="9" t="inlineStr"/>
+      <c r="P840" s="9" t="inlineStr"/>
+      <c r="Q840" s="9" t="inlineStr"/>
+    </row>
+    <row r="841">
+      <c r="A841" s="9" t="n">
+        <v>840</v>
+      </c>
+      <c r="B841" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C841" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D841" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E841" s="9" t="inlineStr">
+        <is>
+          <t>Swinburne University of Technology</t>
+        </is>
+      </c>
+      <c r="F841" s="9" t="inlineStr"/>
+      <c r="G841" s="9" t="inlineStr"/>
+      <c r="H841" s="9" t="inlineStr">
+        <is>
+          <t>edge@swinburne.edu.au</t>
+        </is>
+      </c>
+      <c r="I841" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J841" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K841" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Swinburne University of Technology</t>
+        </is>
+      </c>
+      <c r="L841" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M841" s="9" t="inlineStr">
+        <is>
+          <t>https://www.swinburne.edu.au/collaboration-partnerships</t>
+        </is>
+      </c>
+      <c r="N841" s="9" t="inlineStr">
+        <is>
+          <t>Collaborations and partnerships</t>
+        </is>
+      </c>
+      <c r="O841" s="9" t="inlineStr"/>
+      <c r="P841" s="9" t="inlineStr"/>
+      <c r="Q841" s="9" t="inlineStr"/>
+    </row>
+    <row r="842">
+      <c r="A842" s="9" t="n">
+        <v>841</v>
+      </c>
+      <c r="B842" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C842" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D842" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E842" s="9" t="inlineStr">
+        <is>
+          <t>Deakin University</t>
+        </is>
+      </c>
+      <c r="F842" s="9" t="inlineStr"/>
+      <c r="G842" s="9" t="inlineStr"/>
+      <c r="H842" s="9" t="inlineStr">
+        <is>
+          <t>des@deakin.edu.au</t>
+        </is>
+      </c>
+      <c r="I842" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J842" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K842" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Deakin University</t>
+        </is>
+      </c>
+      <c r="L842" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M842" s="9" t="inlineStr">
+        <is>
+          <t>https://www.deakin.edu.au/students/faculties/sebe</t>
+        </is>
+      </c>
+      <c r="N842" s="9" t="inlineStr">
+        <is>
+          <t>Engineering student support (Deakin Engineering Society)</t>
+        </is>
+      </c>
+      <c r="O842" s="9" t="inlineStr"/>
+      <c r="P842" s="9" t="inlineStr"/>
+      <c r="Q842" s="9" t="inlineStr"/>
+    </row>
+    <row r="843">
+      <c r="A843" s="9" t="n">
+        <v>842</v>
+      </c>
+      <c r="B843" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C843" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D843" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E843" s="9" t="inlineStr">
+        <is>
+          <t>La Trobe University</t>
+        </is>
+      </c>
+      <c r="F843" s="9" t="inlineStr"/>
+      <c r="G843" s="9" t="inlineStr"/>
+      <c r="H843" s="9" t="inlineStr">
+        <is>
+          <t>industry.engagement@latrobe.edu.au</t>
+        </is>
+      </c>
+      <c r="I843" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J843" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K843" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for La Trobe University</t>
+        </is>
+      </c>
+      <c r="L843" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M843" s="9" t="inlineStr">
+        <is>
+          <t>https://www.latrobe.edu.au/la-trobe-industry/contact-us</t>
+        </is>
+      </c>
+      <c r="N843" s="9" t="inlineStr">
+        <is>
+          <t>Industry engagement</t>
+        </is>
+      </c>
+      <c r="O843" s="9" t="inlineStr"/>
+      <c r="P843" s="9" t="inlineStr"/>
+      <c r="Q843" s="9" t="inlineStr"/>
+    </row>
+    <row r="844">
+      <c r="A844" s="9" t="n">
+        <v>843</v>
+      </c>
+      <c r="B844" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C844" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D844" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E844" s="9" t="inlineStr">
+        <is>
+          <t>Victoria University</t>
+        </is>
+      </c>
+      <c r="F844" s="9" t="inlineStr"/>
+      <c r="G844" s="9" t="inlineStr"/>
+      <c r="H844" s="9" t="inlineStr">
+        <is>
+          <t>international@vu.edu.au</t>
+        </is>
+      </c>
+      <c r="I844" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J844" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K844" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Victoria University</t>
+        </is>
+      </c>
+      <c r="L844" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M844" s="9" t="inlineStr">
+        <is>
+          <t>https://www.vu.edu.au/contact-us/international-students</t>
+        </is>
+      </c>
+      <c r="N844" s="9" t="inlineStr">
+        <is>
+          <t>General/international enquiries</t>
+        </is>
+      </c>
+      <c r="O844" s="9" t="inlineStr"/>
+      <c r="P844" s="9" t="inlineStr"/>
+      <c r="Q844" s="9" t="inlineStr"/>
+    </row>
+    <row r="845">
+      <c r="A845" s="9" t="n">
+        <v>844</v>
+      </c>
+      <c r="B845" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C845" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D845" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E845" s="9" t="inlineStr">
+        <is>
+          <t>Federation University Australia</t>
+        </is>
+      </c>
+      <c r="F845" s="9" t="inlineStr"/>
+      <c r="G845" s="9" t="inlineStr"/>
+      <c r="H845" s="9" t="inlineStr">
+        <is>
+          <t>engineeringautomotive@federation.edu.au</t>
+        </is>
+      </c>
+      <c r="I845" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J845" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K845" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Federation University Australia</t>
+        </is>
+      </c>
+      <c r="L845" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M845" s="9" t="inlineStr">
+        <is>
+          <t>https://www.federation.edu.au/courses/dlcl-diploma</t>
+        </is>
+      </c>
+      <c r="N845" s="9" t="inlineStr">
+        <is>
+          <t>Engineering dept contact</t>
+        </is>
+      </c>
+      <c r="O845" s="9" t="inlineStr"/>
+      <c r="P845" s="9" t="inlineStr"/>
+      <c r="Q845" s="9" t="inlineStr"/>
+    </row>
+    <row r="846">
+      <c r="A846" s="9" t="n">
+        <v>845</v>
+      </c>
+      <c r="B846" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C846" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D846" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E846" s="9" t="inlineStr">
+        <is>
+          <t>University of Queensland</t>
+        </is>
+      </c>
+      <c r="F846" s="9" t="inlineStr"/>
+      <c r="G846" s="9" t="inlineStr"/>
+      <c r="H846" s="9" t="inlineStr">
+        <is>
+          <t>enquiries@eait.uq.edu.au</t>
+        </is>
+      </c>
+      <c r="I846" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J846" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K846" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Queensland</t>
+        </is>
+      </c>
+      <c r="L846" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M846" s="9" t="inlineStr">
+        <is>
+          <t>https://www.eait.uq.edu.au/contact</t>
+        </is>
+      </c>
+      <c r="N846" s="9" t="inlineStr">
+        <is>
+          <t>Engineering, Architecture and IT faculty</t>
+        </is>
+      </c>
+      <c r="O846" s="9" t="inlineStr"/>
+      <c r="P846" s="9" t="inlineStr"/>
+      <c r="Q846" s="9" t="inlineStr"/>
+    </row>
+    <row r="847">
+      <c r="A847" s="9" t="n">
+        <v>846</v>
+      </c>
+      <c r="B847" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C847" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D847" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E847" s="9" t="inlineStr">
+        <is>
+          <t>Queensland University of Technology</t>
+        </is>
+      </c>
+      <c r="F847" s="9" t="inlineStr"/>
+      <c r="G847" s="9" t="inlineStr"/>
+      <c r="H847" s="9" t="inlineStr">
+        <is>
+          <t>askqut@qut.edu.au</t>
+        </is>
+      </c>
+      <c r="I847" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J847" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K847" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Queensland University of Technology</t>
+        </is>
+      </c>
+      <c r="L847" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M847" s="9" t="inlineStr">
+        <is>
+          <t>https://www.qut.edu.au/about/faculty-of-engineering</t>
+        </is>
+      </c>
+      <c r="N847" s="9" t="inlineStr">
+        <is>
+          <t>Faculty of Engineering</t>
+        </is>
+      </c>
+      <c r="O847" s="9" t="inlineStr"/>
+      <c r="P847" s="9" t="inlineStr"/>
+      <c r="Q847" s="9" t="inlineStr"/>
+    </row>
+    <row r="848">
+      <c r="A848" s="9" t="n">
+        <v>847</v>
+      </c>
+      <c r="B848" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C848" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D848" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E848" s="9" t="inlineStr">
+        <is>
+          <t>James Cook University</t>
+        </is>
+      </c>
+      <c r="F848" s="9" t="inlineStr"/>
+      <c r="G848" s="9" t="inlineStr"/>
+      <c r="H848" s="9" t="inlineStr">
+        <is>
+          <t>enquiries@jcu.edu.au</t>
+        </is>
+      </c>
+      <c r="I848" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J848" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K848" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for James Cook University</t>
+        </is>
+      </c>
+      <c r="L848" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M848" s="9" t="inlineStr">
+        <is>
+          <t>https://www.jcu.edu.au/college-of-science-and-engineering</t>
+        </is>
+      </c>
+      <c r="N848" s="9" t="inlineStr">
+        <is>
+          <t>General enquiries; also deancse@jcu.edu.au</t>
+        </is>
+      </c>
+      <c r="O848" s="9" t="inlineStr"/>
+      <c r="P848" s="9" t="inlineStr"/>
+      <c r="Q848" s="9" t="inlineStr"/>
+    </row>
+    <row r="849">
+      <c r="A849" s="9" t="n">
+        <v>848</v>
+      </c>
+      <c r="B849" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C849" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D849" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E849" s="9" t="inlineStr">
+        <is>
+          <t>Central Queensland University</t>
+        </is>
+      </c>
+      <c r="F849" s="9" t="inlineStr"/>
+      <c r="G849" s="9" t="inlineStr"/>
+      <c r="H849" s="9" t="inlineStr">
+        <is>
+          <t>SETadmin@cqu.edu.au</t>
+        </is>
+      </c>
+      <c r="I849" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J849" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K849" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Central Queensland University</t>
+        </is>
+      </c>
+      <c r="L849" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M849" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cqu.edu.au/engineering-technology/college</t>
+        </is>
+      </c>
+      <c r="N849" s="9" t="inlineStr">
+        <is>
+          <t>College of Engineering and Aviation</t>
+        </is>
+      </c>
+      <c r="O849" s="9" t="inlineStr"/>
+      <c r="P849" s="9" t="inlineStr"/>
+      <c r="Q849" s="9" t="inlineStr"/>
+    </row>
+    <row r="850">
+      <c r="A850" s="9" t="n">
+        <v>849</v>
+      </c>
+      <c r="B850" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C850" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D850" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E850" s="9" t="inlineStr">
+        <is>
+          <t>University of Southern Queensland</t>
+        </is>
+      </c>
+      <c r="F850" s="9" t="inlineStr"/>
+      <c r="G850" s="9" t="inlineStr"/>
+      <c r="H850" s="9" t="inlineStr">
+        <is>
+          <t>study@unisq.edu.au</t>
+        </is>
+      </c>
+      <c r="I850" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J850" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K850" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Southern Queensland</t>
+        </is>
+      </c>
+      <c r="L850" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M850" s="9" t="inlineStr">
+        <is>
+          <t>https://sbq.com.au (confirmed via unisq.edu.au domain)</t>
+        </is>
+      </c>
+      <c r="N850" s="9" t="inlineStr">
+        <is>
+          <t>General study enquiries</t>
+        </is>
+      </c>
+      <c r="O850" s="9" t="inlineStr"/>
+      <c r="P850" s="9" t="inlineStr"/>
+      <c r="Q850" s="9" t="inlineStr"/>
+    </row>
+    <row r="851">
+      <c r="A851" s="9" t="n">
+        <v>850</v>
+      </c>
+      <c r="B851" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C851" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D851" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E851" s="9" t="inlineStr">
+        <is>
+          <t>University of the Sunshine Coast</t>
+        </is>
+      </c>
+      <c r="F851" s="9" t="inlineStr"/>
+      <c r="G851" s="9" t="inlineStr"/>
+      <c r="H851" s="9" t="inlineStr">
+        <is>
+          <t>information@unisc.edu.au</t>
+        </is>
+      </c>
+      <c r="I851" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J851" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K851" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of the Sunshine Coast</t>
+        </is>
+      </c>
+      <c r="L851" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M851" s="9" t="inlineStr">
+        <is>
+          <t>https://www.unisc.edu.au/contact-unisc</t>
+        </is>
+      </c>
+      <c r="N851" s="9" t="inlineStr">
+        <is>
+          <t>Prospective student enquiries</t>
+        </is>
+      </c>
+      <c r="O851" s="9" t="inlineStr"/>
+      <c r="P851" s="9" t="inlineStr"/>
+      <c r="Q851" s="9" t="inlineStr"/>
+    </row>
+    <row r="852">
+      <c r="A852" s="9" t="n">
+        <v>851</v>
+      </c>
+      <c r="B852" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C852" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D852" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E852" s="9" t="inlineStr">
+        <is>
+          <t>University of Western Australia</t>
+        </is>
+      </c>
+      <c r="F852" s="9" t="inlineStr"/>
+      <c r="G852" s="9" t="inlineStr"/>
+      <c r="H852" s="9" t="inlineStr">
+        <is>
+          <t>industry@uwa.edu.au</t>
+        </is>
+      </c>
+      <c r="I852" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J852" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K852" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Western Australia</t>
+        </is>
+      </c>
+      <c r="L852" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M852" s="9" t="inlineStr">
+        <is>
+          <t>https://www.uwa.edu.au/contact-us</t>
+        </is>
+      </c>
+      <c r="N852" s="9" t="inlineStr">
+        <is>
+          <t>Industry contact</t>
+        </is>
+      </c>
+      <c r="O852" s="9" t="inlineStr"/>
+      <c r="P852" s="9" t="inlineStr"/>
+      <c r="Q852" s="9" t="inlineStr"/>
+    </row>
+    <row r="853">
+      <c r="A853" s="9" t="n">
+        <v>852</v>
+      </c>
+      <c r="B853" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C853" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D853" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E853" s="9" t="inlineStr">
+        <is>
+          <t>Curtin University</t>
+        </is>
+      </c>
+      <c r="F853" s="9" t="inlineStr"/>
+      <c r="G853" s="9" t="inlineStr"/>
+      <c r="H853" s="9" t="inlineStr">
+        <is>
+          <t>saeWIL@curtin.edu.au</t>
+        </is>
+      </c>
+      <c r="I853" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J853" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K853" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Curtin University</t>
+        </is>
+      </c>
+      <c r="L853" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M853" s="9" t="inlineStr">
+        <is>
+          <t>https://www.curtin.edu.au (Industry experience)</t>
+        </is>
+      </c>
+      <c r="N853" s="9" t="inlineStr">
+        <is>
+          <t>Science and Engineering WIL/industry team</t>
+        </is>
+      </c>
+      <c r="O853" s="9" t="inlineStr"/>
+      <c r="P853" s="9" t="inlineStr"/>
+      <c r="Q853" s="9" t="inlineStr"/>
+    </row>
+    <row r="854">
+      <c r="A854" s="9" t="n">
+        <v>853</v>
+      </c>
+      <c r="B854" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C854" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D854" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E854" s="9" t="inlineStr">
+        <is>
+          <t>Edith Cowan University</t>
+        </is>
+      </c>
+      <c r="F854" s="9" t="inlineStr"/>
+      <c r="G854" s="9" t="inlineStr"/>
+      <c r="H854" s="9" t="inlineStr">
+        <is>
+          <t>seadmin@ecu.edu.au</t>
+        </is>
+      </c>
+      <c r="I854" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J854" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K854" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Edith Cowan University</t>
+        </is>
+      </c>
+      <c r="L854" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M854" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ecu.edu.au/schools/engineering/contact</t>
+        </is>
+      </c>
+      <c r="N854" s="9" t="inlineStr">
+        <is>
+          <t>School of Engineering general enquiries</t>
+        </is>
+      </c>
+      <c r="O854" s="9" t="inlineStr"/>
+      <c r="P854" s="9" t="inlineStr"/>
+      <c r="Q854" s="9" t="inlineStr"/>
+    </row>
+    <row r="855">
+      <c r="A855" s="9" t="n">
+        <v>854</v>
+      </c>
+      <c r="B855" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C855" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D855" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E855" s="9" t="inlineStr">
+        <is>
+          <t>Murdoch University</t>
+        </is>
+      </c>
+      <c r="F855" s="9" t="inlineStr"/>
+      <c r="G855" s="9" t="inlineStr"/>
+      <c r="H855" s="9" t="inlineStr">
+        <is>
+          <t>international.enquiries@murdoch.edu.au</t>
+        </is>
+      </c>
+      <c r="I855" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J855" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K855" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Murdoch University</t>
+        </is>
+      </c>
+      <c r="L855" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M855" s="9" t="inlineStr">
+        <is>
+          <t>https://studyingabroad.co.in (confirmed via murdoch.edu.au domain)</t>
+        </is>
+      </c>
+      <c r="N855" s="9" t="inlineStr">
+        <is>
+          <t>International enquiries</t>
+        </is>
+      </c>
+      <c r="O855" s="9" t="inlineStr"/>
+      <c r="P855" s="9" t="inlineStr"/>
+      <c r="Q855" s="9" t="inlineStr"/>
+    </row>
+    <row r="856">
+      <c r="A856" s="9" t="n">
+        <v>855</v>
+      </c>
+      <c r="B856" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C856" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D856" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E856" s="9" t="inlineStr">
+        <is>
+          <t>Adelaide University</t>
+        </is>
+      </c>
+      <c r="F856" s="9" t="inlineStr"/>
+      <c r="G856" s="9" t="inlineStr"/>
+      <c r="H856" s="9" t="inlineStr">
+        <is>
+          <t>cdf@adelaide.edu.au</t>
+        </is>
+      </c>
+      <c r="I856" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J856" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K856" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Adelaide University</t>
+        </is>
+      </c>
+      <c r="L856" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M856" s="9" t="inlineStr">
+        <is>
+          <t>https://adelaide.edu.au (College of Engineering and IT)</t>
+        </is>
+      </c>
+      <c r="N856" s="9" t="inlineStr">
+        <is>
+          <t>College of Engineering and IT contact</t>
+        </is>
+      </c>
+      <c r="O856" s="9" t="inlineStr"/>
+      <c r="P856" s="9" t="inlineStr"/>
+      <c r="Q856" s="9" t="inlineStr"/>
+    </row>
+    <row r="857">
+      <c r="A857" s="9" t="n">
+        <v>856</v>
+      </c>
+      <c r="B857" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C857" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D857" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E857" s="9" t="inlineStr">
+        <is>
+          <t>Flinders University</t>
+        </is>
+      </c>
+      <c r="F857" s="9" t="inlineStr"/>
+      <c r="G857" s="9" t="inlineStr"/>
+      <c r="H857" s="9" t="inlineStr">
+        <is>
+          <t>cse.enquiries@flinders.edu.au</t>
+        </is>
+      </c>
+      <c r="I857" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J857" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K857" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Flinders University</t>
+        </is>
+      </c>
+      <c r="L857" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M857" s="9" t="inlineStr">
+        <is>
+          <t>https://www.flinders.edu.au/contact-us</t>
+        </is>
+      </c>
+      <c r="N857" s="9" t="inlineStr">
+        <is>
+          <t>College of Science and Engineering</t>
+        </is>
+      </c>
+      <c r="O857" s="9" t="inlineStr"/>
+      <c r="P857" s="9" t="inlineStr"/>
+      <c r="Q857" s="9" t="inlineStr"/>
+    </row>
+    <row r="858">
+      <c r="A858" s="9" t="n">
+        <v>857</v>
+      </c>
+      <c r="B858" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C858" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D858" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E858" s="9" t="inlineStr">
+        <is>
+          <t>University of Tasmania</t>
+        </is>
+      </c>
+      <c r="F858" s="9" t="inlineStr"/>
+      <c r="G858" s="9" t="inlineStr"/>
+      <c r="H858" s="9" t="inlineStr">
+        <is>
+          <t>course.info@utas.edu.au</t>
+        </is>
+      </c>
+      <c r="I858" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J858" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K858" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Tasmania</t>
+        </is>
+      </c>
+      <c r="L858" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M858" s="9" t="inlineStr">
+        <is>
+          <t>https://www.utas.edu.au/enquire</t>
+        </is>
+      </c>
+      <c r="N858" s="9" t="inlineStr">
+        <is>
+          <t>Domestic student enquiries</t>
+        </is>
+      </c>
+      <c r="O858" s="9" t="inlineStr"/>
+      <c r="P858" s="9" t="inlineStr"/>
+      <c r="Q858" s="9" t="inlineStr"/>
+    </row>
+    <row r="859">
+      <c r="A859" s="9" t="n">
+        <v>858</v>
+      </c>
+      <c r="B859" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C859" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D859" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E859" s="9" t="inlineStr">
+        <is>
+          <t>Charles Darwin University</t>
+        </is>
+      </c>
+      <c r="F859" s="9" t="inlineStr"/>
+      <c r="G859" s="9" t="inlineStr"/>
+      <c r="H859" s="9" t="inlineStr">
+        <is>
+          <t>study@cdu.edu.au</t>
+        </is>
+      </c>
+      <c r="I859" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J859" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K859" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Charles Darwin University</t>
+        </is>
+      </c>
+      <c r="L859" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M859" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cdu.edu.au/engineering-it-environment</t>
+        </is>
+      </c>
+      <c r="N859" s="9" t="inlineStr">
+        <is>
+          <t>Engineering general enquiries</t>
+        </is>
+      </c>
+      <c r="O859" s="9" t="inlineStr"/>
+      <c r="P859" s="9" t="inlineStr"/>
+      <c r="Q859" s="9" t="inlineStr"/>
+    </row>
+    <row r="860">
+      <c r="A860" s="9" t="n">
+        <v>859</v>
+      </c>
+      <c r="B860" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C860" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D860" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E860" s="9" t="inlineStr">
+        <is>
+          <t>Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="F860" s="9" t="inlineStr"/>
+      <c r="G860" s="9" t="inlineStr"/>
+      <c r="H860" s="9" t="inlineStr">
+        <is>
+          <t>info@tudelft.nl</t>
+        </is>
+      </c>
+      <c r="I860" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J860" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K860" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Delft University of Technology</t>
+        </is>
+      </c>
+      <c r="L860" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M860" s="9" t="inlineStr">
+        <is>
+          <t>https://www.tudelft.nl (About TU Delft contact)</t>
+        </is>
+      </c>
+      <c r="N860" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O860" s="9" t="inlineStr"/>
+      <c r="P860" s="9" t="inlineStr"/>
+      <c r="Q860" s="9" t="inlineStr"/>
+    </row>
+    <row r="861">
+      <c r="A861" s="9" t="n">
+        <v>860</v>
+      </c>
+      <c r="B861" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C861" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D861" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E861" s="9" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="F861" s="9" t="inlineStr"/>
+      <c r="G861" s="9" t="inlineStr"/>
+      <c r="H861" s="9" t="inlineStr">
+        <is>
+          <t>io@tue.nl</t>
+        </is>
+      </c>
+      <c r="I861" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J861" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K861" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Eindhoven University of Technology</t>
+        </is>
+      </c>
+      <c r="L861" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M861" s="9" t="inlineStr">
+        <is>
+          <t>https://educationguide.tue.nl</t>
+        </is>
+      </c>
+      <c r="N861" s="9" t="inlineStr">
+        <is>
+          <t>International Office</t>
+        </is>
+      </c>
+      <c r="O861" s="9" t="inlineStr"/>
+      <c r="P861" s="9" t="inlineStr"/>
+      <c r="Q861" s="9" t="inlineStr"/>
+    </row>
+    <row r="862">
+      <c r="A862" s="9" t="n">
+        <v>861</v>
+      </c>
+      <c r="B862" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C862" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D862" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E862" s="9" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="F862" s="9" t="inlineStr"/>
+      <c r="G862" s="9" t="inlineStr"/>
+      <c r="H862" s="9" t="inlineStr">
+        <is>
+          <t>study@utwente.nl</t>
+        </is>
+      </c>
+      <c r="I862" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J862" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K862" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Twente</t>
+        </is>
+      </c>
+      <c r="L862" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M862" s="9" t="inlineStr">
+        <is>
+          <t>https://www.utwente.nl (Contact &amp; route)</t>
+        </is>
+      </c>
+      <c r="N862" s="9" t="inlineStr">
+        <is>
+          <t>General/study enquiries</t>
+        </is>
+      </c>
+      <c r="O862" s="9" t="inlineStr"/>
+      <c r="P862" s="9" t="inlineStr"/>
+      <c r="Q862" s="9" t="inlineStr"/>
+    </row>
+    <row r="863">
+      <c r="A863" s="9" t="n">
+        <v>862</v>
+      </c>
+      <c r="B863" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C863" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D863" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E863" s="9" t="inlineStr">
+        <is>
+          <t>Wageningen University &amp; Research</t>
+        </is>
+      </c>
+      <c r="F863" s="9" t="inlineStr"/>
+      <c r="G863" s="9" t="inlineStr"/>
+      <c r="H863" s="9" t="inlineStr">
+        <is>
+          <t>students@wur.nl</t>
+        </is>
+      </c>
+      <c r="I863" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J863" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K863" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Wageningen University &amp; Research</t>
+        </is>
+      </c>
+      <c r="L863" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M863" s="9" t="inlineStr">
+        <is>
+          <t>https://weblog.wur.eu</t>
+        </is>
+      </c>
+      <c r="N863" s="9" t="inlineStr">
+        <is>
+          <t>General student enquiries</t>
+        </is>
+      </c>
+      <c r="O863" s="9" t="inlineStr"/>
+      <c r="P863" s="9" t="inlineStr"/>
+      <c r="Q863" s="9" t="inlineStr"/>
+    </row>
+    <row r="864">
+      <c r="A864" s="9" t="n">
+        <v>863</v>
+      </c>
+      <c r="B864" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C864" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D864" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E864" s="9" t="inlineStr">
+        <is>
+          <t>University of Groningen</t>
+        </is>
+      </c>
+      <c r="F864" s="9" t="inlineStr"/>
+      <c r="G864" s="9" t="inlineStr"/>
+      <c r="H864" s="9" t="inlineStr">
+        <is>
+          <t>communicatie@rug.nl</t>
+        </is>
+      </c>
+      <c r="I864" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J864" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K864" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Groningen</t>
+        </is>
+      </c>
+      <c r="L864" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M864" s="9" t="inlineStr">
+        <is>
+          <t>https://www.rug.nl (Contact information)</t>
+        </is>
+      </c>
+      <c r="N864" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O864" s="9" t="inlineStr"/>
+      <c r="P864" s="9" t="inlineStr"/>
+      <c r="Q864" s="9" t="inlineStr"/>
+    </row>
+    <row r="865">
+      <c r="A865" s="9" t="n">
+        <v>864</v>
+      </c>
+      <c r="B865" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C865" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D865" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E865" s="9" t="inlineStr">
+        <is>
+          <t>Utrecht University</t>
+        </is>
+      </c>
+      <c r="F865" s="9" t="inlineStr"/>
+      <c r="G865" s="9" t="inlineStr"/>
+      <c r="H865" s="9" t="inlineStr">
+        <is>
+          <t>study@uu.nl</t>
+        </is>
+      </c>
+      <c r="I865" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J865" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K865" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Utrecht University</t>
+        </is>
+      </c>
+      <c r="L865" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M865" s="9" t="inlineStr">
+        <is>
+          <t>https://www.uu.nl/bachelors/general-information/contact</t>
+        </is>
+      </c>
+      <c r="N865" s="9" t="inlineStr">
+        <is>
+          <t>General/study enquiries</t>
+        </is>
+      </c>
+      <c r="O865" s="9" t="inlineStr"/>
+      <c r="P865" s="9" t="inlineStr"/>
+      <c r="Q865" s="9" t="inlineStr"/>
+    </row>
+    <row r="866">
+      <c r="A866" s="9" t="n">
+        <v>865</v>
+      </c>
+      <c r="B866" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C866" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D866" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E866" s="9" t="inlineStr">
+        <is>
+          <t>University of Amsterdam</t>
+        </is>
+      </c>
+      <c r="F866" s="9" t="inlineStr"/>
+      <c r="G866" s="9" t="inlineStr"/>
+      <c r="H866" s="9" t="inlineStr">
+        <is>
+          <t>info-science@uva.nl</t>
+        </is>
+      </c>
+      <c r="I866" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J866" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K866" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Amsterdam</t>
+        </is>
+      </c>
+      <c r="L866" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M866" s="9" t="inlineStr">
+        <is>
+          <t>https://www.uva.nl (Contact and location)</t>
+        </is>
+      </c>
+      <c r="N866" s="9" t="inlineStr">
+        <is>
+          <t>General inquiries (Science faculty)</t>
+        </is>
+      </c>
+      <c r="O866" s="9" t="inlineStr"/>
+      <c r="P866" s="9" t="inlineStr"/>
+      <c r="Q866" s="9" t="inlineStr"/>
+    </row>
+    <row r="867">
+      <c r="A867" s="9" t="n">
+        <v>866</v>
+      </c>
+      <c r="B867" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C867" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D867" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E867" s="9" t="inlineStr">
+        <is>
+          <t>Vrije Universiteit Amsterdam</t>
+        </is>
+      </c>
+      <c r="F867" s="9" t="inlineStr"/>
+      <c r="G867" s="9" t="inlineStr"/>
+      <c r="H867" s="9" t="inlineStr">
+        <is>
+          <t>incoming@vu.nl</t>
+        </is>
+      </c>
+      <c r="I867" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J867" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K867" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Vrije Universiteit Amsterdam</t>
+        </is>
+      </c>
+      <c r="L867" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M867" s="9" t="inlineStr">
+        <is>
+          <t>https://www.mh.tum.de (confirmed via vu.nl domain)</t>
+        </is>
+      </c>
+      <c r="N867" s="9" t="inlineStr">
+        <is>
+          <t>Exchange/incoming enquiries</t>
+        </is>
+      </c>
+      <c r="O867" s="9" t="inlineStr"/>
+      <c r="P867" s="9" t="inlineStr"/>
+      <c r="Q867" s="9" t="inlineStr"/>
+    </row>
+    <row r="868">
+      <c r="A868" s="9" t="n">
+        <v>867</v>
+      </c>
+      <c r="B868" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C868" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D868" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E868" s="9" t="inlineStr">
+        <is>
+          <t>Radboud University</t>
+        </is>
+      </c>
+      <c r="F868" s="9" t="inlineStr"/>
+      <c r="G868" s="9" t="inlineStr"/>
+      <c r="H868" s="9" t="inlineStr">
+        <is>
+          <t>study-information@ru.nl</t>
+        </is>
+      </c>
+      <c r="I868" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J868" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K868" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Radboud University</t>
+        </is>
+      </c>
+      <c r="L868" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M868" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ru.nl/about-us/contact</t>
+        </is>
+      </c>
+      <c r="N868" s="9" t="inlineStr">
+        <is>
+          <t>General study information</t>
+        </is>
+      </c>
+      <c r="O868" s="9" t="inlineStr"/>
+      <c r="P868" s="9" t="inlineStr"/>
+      <c r="Q868" s="9" t="inlineStr"/>
+    </row>
+    <row r="869">
+      <c r="A869" s="9" t="n">
+        <v>868</v>
+      </c>
+      <c r="B869" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C869" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D869" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E869" s="9" t="inlineStr">
+        <is>
+          <t>Leiden University</t>
+        </is>
+      </c>
+      <c r="F869" s="9" t="inlineStr"/>
+      <c r="G869" s="9" t="inlineStr"/>
+      <c r="H869" s="9" t="inlineStr">
+        <is>
+          <t>study@bb.leidenuniv.nl</t>
+        </is>
+      </c>
+      <c r="I869" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J869" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K869" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Leiden University</t>
+        </is>
+      </c>
+      <c r="L869" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M869" s="9" t="inlineStr">
+        <is>
+          <t>https://www.universiteitleiden.nl/about-us/contact</t>
+        </is>
+      </c>
+      <c r="N869" s="9" t="inlineStr">
+        <is>
+          <t>Study Line general contact</t>
+        </is>
+      </c>
+      <c r="O869" s="9" t="inlineStr"/>
+      <c r="P869" s="9" t="inlineStr"/>
+      <c r="Q869" s="9" t="inlineStr"/>
+    </row>
+    <row r="870">
+      <c r="A870" s="9" t="n">
+        <v>869</v>
+      </c>
+      <c r="B870" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C870" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D870" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E870" s="9" t="inlineStr">
+        <is>
+          <t>Maastricht University</t>
+        </is>
+      </c>
+      <c r="F870" s="9" t="inlineStr"/>
+      <c r="G870" s="9" t="inlineStr"/>
+      <c r="H870" s="9" t="inlineStr">
+        <is>
+          <t>study@maastrichtuniversity.nl</t>
+        </is>
+      </c>
+      <c r="I870" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J870" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K870" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Maastricht University</t>
+        </is>
+      </c>
+      <c r="L870" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M870" s="9" t="inlineStr">
+        <is>
+          <t>https://www.maastrichtuniversity.nl/student-administration</t>
+        </is>
+      </c>
+      <c r="N870" s="9" t="inlineStr">
+        <is>
+          <t>General student administration</t>
+        </is>
+      </c>
+      <c r="O870" s="9" t="inlineStr"/>
+      <c r="P870" s="9" t="inlineStr"/>
+      <c r="Q870" s="9" t="inlineStr"/>
+    </row>
+    <row r="871">
+      <c r="A871" s="9" t="n">
+        <v>870</v>
+      </c>
+      <c r="B871" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C871" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D871" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E871" s="9" t="inlineStr">
+        <is>
+          <t>Open Universiteit</t>
+        </is>
+      </c>
+      <c r="F871" s="9" t="inlineStr"/>
+      <c r="G871" s="9" t="inlineStr"/>
+      <c r="H871" s="9" t="inlineStr">
+        <is>
+          <t>info@ou.nl</t>
+        </is>
+      </c>
+      <c r="I871" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J871" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K871" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Open Universiteit</t>
+        </is>
+      </c>
+      <c r="L871" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M871" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ou.nl/contact-and-adresses</t>
+        </is>
+      </c>
+      <c r="N871" s="9" t="inlineStr">
+        <is>
+          <t>General study information</t>
+        </is>
+      </c>
+      <c r="O871" s="9" t="inlineStr"/>
+      <c r="P871" s="9" t="inlineStr"/>
+      <c r="Q871" s="9" t="inlineStr"/>
+    </row>
+    <row r="872">
+      <c r="A872" s="9" t="n">
+        <v>871</v>
+      </c>
+      <c r="B872" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C872" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D872" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E872" s="9" t="inlineStr">
+        <is>
+          <t>Amsterdam University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="F872" s="9" t="inlineStr"/>
+      <c r="G872" s="9" t="inlineStr"/>
+      <c r="H872" s="9" t="inlineStr">
+        <is>
+          <t>studentinformation@amsterdamuas.com</t>
+        </is>
+      </c>
+      <c r="I872" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J872" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K872" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Amsterdam University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="L872" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M872" s="9" t="inlineStr">
+        <is>
+          <t>https://www.amsterdamuas.com/about-auas/contact</t>
+        </is>
+      </c>
+      <c r="N872" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O872" s="9" t="inlineStr"/>
+      <c r="P872" s="9" t="inlineStr"/>
+      <c r="Q872" s="9" t="inlineStr"/>
+    </row>
+    <row r="873">
+      <c r="A873" s="9" t="n">
+        <v>872</v>
+      </c>
+      <c r="B873" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C873" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D873" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E873" s="9" t="inlineStr">
+        <is>
+          <t>Rotterdam University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="F873" s="9" t="inlineStr"/>
+      <c r="G873" s="9" t="inlineStr"/>
+      <c r="H873" s="9" t="inlineStr">
+        <is>
+          <t>info@hr.nl</t>
+        </is>
+      </c>
+      <c r="I873" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J873" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K873" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Rotterdam University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="L873" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M873" s="9" t="inlineStr">
+        <is>
+          <t>https://dutchstudenthousing.nl (confirmed via hr.nl domain)</t>
+        </is>
+      </c>
+      <c r="N873" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O873" s="9" t="inlineStr"/>
+      <c r="P873" s="9" t="inlineStr"/>
+      <c r="Q873" s="9" t="inlineStr"/>
+    </row>
+    <row r="874">
+      <c r="A874" s="9" t="n">
+        <v>873</v>
+      </c>
+      <c r="B874" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C874" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D874" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E874" s="9" t="inlineStr">
+        <is>
+          <t>The Hague University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="F874" s="9" t="inlineStr"/>
+      <c r="G874" s="9" t="inlineStr"/>
+      <c r="H874" s="9" t="inlineStr">
+        <is>
+          <t>internationaloffice@hhs.nl</t>
+        </is>
+      </c>
+      <c r="I874" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J874" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K874" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for The Hague University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="L874" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M874" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kastu.pl (confirmed via hhs.nl domain)</t>
+        </is>
+      </c>
+      <c r="N874" s="9" t="inlineStr">
+        <is>
+          <t>International Office</t>
+        </is>
+      </c>
+      <c r="O874" s="9" t="inlineStr"/>
+      <c r="P874" s="9" t="inlineStr"/>
+      <c r="Q874" s="9" t="inlineStr"/>
+    </row>
+    <row r="875">
+      <c r="A875" s="9" t="n">
+        <v>874</v>
+      </c>
+      <c r="B875" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C875" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D875" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E875" s="9" t="inlineStr">
+        <is>
+          <t>HU University of Applied Sciences Utrecht</t>
+        </is>
+      </c>
+      <c r="F875" s="9" t="inlineStr"/>
+      <c r="G875" s="9" t="inlineStr"/>
+      <c r="H875" s="9" t="inlineStr">
+        <is>
+          <t>info@hu.nl</t>
+        </is>
+      </c>
+      <c r="I875" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J875" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K875" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for HU University of Applied Sciences Utrecht</t>
+        </is>
+      </c>
+      <c r="L875" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M875" s="9" t="inlineStr">
+        <is>
+          <t>https://www.internationalhu.com/practical-information</t>
+        </is>
+      </c>
+      <c r="N875" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O875" s="9" t="inlineStr"/>
+      <c r="P875" s="9" t="inlineStr"/>
+      <c r="Q875" s="9" t="inlineStr"/>
+    </row>
+    <row r="876">
+      <c r="A876" s="9" t="n">
+        <v>875</v>
+      </c>
+      <c r="B876" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C876" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D876" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E876" s="9" t="inlineStr">
+        <is>
+          <t>Fontys University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="F876" s="9" t="inlineStr"/>
+      <c r="G876" s="9" t="inlineStr"/>
+      <c r="H876" s="9" t="inlineStr">
+        <is>
+          <t>info@fontys.nl</t>
+        </is>
+      </c>
+      <c r="I876" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J876" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K876" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Fontys University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="L876" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M876" s="9" t="inlineStr">
+        <is>
+          <t>https://www.fontys.nl (Contact)</t>
+        </is>
+      </c>
+      <c r="N876" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O876" s="9" t="inlineStr"/>
+      <c r="P876" s="9" t="inlineStr"/>
+      <c r="Q876" s="9" t="inlineStr"/>
+    </row>
+    <row r="877">
+      <c r="A877" s="9" t="n">
+        <v>876</v>
+      </c>
+      <c r="B877" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C877" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D877" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E877" s="9" t="inlineStr">
+        <is>
+          <t>Avans University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="F877" s="9" t="inlineStr"/>
+      <c r="G877" s="9" t="inlineStr"/>
+      <c r="H877" s="9" t="inlineStr">
+        <is>
+          <t>internationaloffice@avans.nl</t>
+        </is>
+      </c>
+      <c r="I877" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J877" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K877" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Avans University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="L877" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M877" s="9" t="inlineStr">
+        <is>
+          <t>https://www.avans.nl/studying/practical-information</t>
+        </is>
+      </c>
+      <c r="N877" s="9" t="inlineStr">
+        <is>
+          <t>International office</t>
+        </is>
+      </c>
+      <c r="O877" s="9" t="inlineStr"/>
+      <c r="P877" s="9" t="inlineStr"/>
+      <c r="Q877" s="9" t="inlineStr"/>
+    </row>
+    <row r="878">
+      <c r="A878" s="9" t="n">
+        <v>877</v>
+      </c>
+      <c r="B878" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C878" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D878" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E878" s="9" t="inlineStr">
+        <is>
+          <t>Saxion University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="F878" s="9" t="inlineStr"/>
+      <c r="G878" s="9" t="inlineStr"/>
+      <c r="H878" s="9" t="inlineStr">
+        <is>
+          <t>internationaloffice@saxion.nl</t>
+        </is>
+      </c>
+      <c r="I878" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J878" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K878" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Saxion University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="L878" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M878" s="9" t="inlineStr">
+        <is>
+          <t>https://www.saxion.edu/about-saxion (Get in touch)</t>
+        </is>
+      </c>
+      <c r="N878" s="9" t="inlineStr">
+        <is>
+          <t>International Office; also info@saxion.nl</t>
+        </is>
+      </c>
+      <c r="O878" s="9" t="inlineStr"/>
+      <c r="P878" s="9" t="inlineStr"/>
+      <c r="Q878" s="9" t="inlineStr"/>
+    </row>
+    <row r="879">
+      <c r="A879" s="9" t="n">
+        <v>878</v>
+      </c>
+      <c r="B879" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C879" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D879" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E879" s="9" t="inlineStr">
+        <is>
+          <t>Hanze University of Applied Sciences Groningen</t>
+        </is>
+      </c>
+      <c r="F879" s="9" t="inlineStr"/>
+      <c r="G879" s="9" t="inlineStr"/>
+      <c r="H879" s="9" t="inlineStr">
+        <is>
+          <t>info@org.hanze.nl</t>
+        </is>
+      </c>
+      <c r="I879" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J879" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K879" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Hanze University of Applied Sciences Groningen</t>
+        </is>
+      </c>
+      <c r="L879" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M879" s="9" t="inlineStr">
+        <is>
+          <t>https://www.hanze.nl/contact-and-locations</t>
+        </is>
+      </c>
+      <c r="N879" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O879" s="9" t="inlineStr"/>
+      <c r="P879" s="9" t="inlineStr"/>
+      <c r="Q879" s="9" t="inlineStr"/>
+    </row>
+    <row r="880">
+      <c r="A880" s="9" t="n">
+        <v>879</v>
+      </c>
+      <c r="B880" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C880" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D880" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E880" s="9" t="inlineStr">
+        <is>
+          <t>HAN University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="F880" s="9" t="inlineStr"/>
+      <c r="G880" s="9" t="inlineStr"/>
+      <c r="H880" s="9" t="inlineStr">
+        <is>
+          <t>ask@han.nl</t>
+        </is>
+      </c>
+      <c r="I880" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J880" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K880" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for HAN University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="L880" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M880" s="9" t="inlineStr">
+        <is>
+          <t>https://www.hanuniversity.com/business-units/international</t>
+        </is>
+      </c>
+      <c r="N880" s="9" t="inlineStr">
+        <is>
+          <t>International Office Arnhem</t>
+        </is>
+      </c>
+      <c r="O880" s="9" t="inlineStr"/>
+      <c r="P880" s="9" t="inlineStr"/>
+      <c r="Q880" s="9" t="inlineStr"/>
+    </row>
+    <row r="881">
+      <c r="A881" s="9" t="n">
+        <v>880</v>
+      </c>
+      <c r="B881" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C881" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D881" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E881" s="9" t="inlineStr">
+        <is>
+          <t>Windesheim University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="F881" s="9" t="inlineStr"/>
+      <c r="G881" s="9" t="inlineStr"/>
+      <c r="H881" s="9" t="inlineStr">
+        <is>
+          <t>info@windesheim.nl</t>
+        </is>
+      </c>
+      <c r="I881" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J881" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K881" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Windesheim University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="L881" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M881" s="9" t="inlineStr">
+        <is>
+          <t>https://www.windesheim.com/About-Windesheim</t>
+        </is>
+      </c>
+      <c r="N881" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O881" s="9" t="inlineStr"/>
+      <c r="P881" s="9" t="inlineStr"/>
+      <c r="Q881" s="9" t="inlineStr"/>
+    </row>
+    <row r="882">
+      <c r="A882" s="9" t="n">
+        <v>881</v>
+      </c>
+      <c r="B882" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C882" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D882" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E882" s="9" t="inlineStr">
+        <is>
+          <t>NHL Stenden University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="F882" s="9" t="inlineStr"/>
+      <c r="G882" s="9" t="inlineStr"/>
+      <c r="H882" s="9" t="inlineStr">
+        <is>
+          <t>studentinfo@nhlstenden.com</t>
+        </is>
+      </c>
+      <c r="I882" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J882" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K882" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for NHL Stenden University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="L882" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M882" s="9" t="inlineStr">
+        <is>
+          <t>https://www.nhlstenden.com/contact</t>
+        </is>
+      </c>
+      <c r="N882" s="9" t="inlineStr">
+        <is>
+          <t>General questions</t>
+        </is>
+      </c>
+      <c r="O882" s="9" t="inlineStr"/>
+      <c r="P882" s="9" t="inlineStr"/>
+      <c r="Q882" s="9" t="inlineStr"/>
+    </row>
+    <row r="883">
+      <c r="A883" s="9" t="n">
+        <v>882</v>
+      </c>
+      <c r="B883" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C883" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D883" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E883" s="9" t="inlineStr">
+        <is>
+          <t>Zuyd University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="F883" s="9" t="inlineStr"/>
+      <c r="G883" s="9" t="inlineStr"/>
+      <c r="H883" s="9" t="inlineStr">
+        <is>
+          <t>info@zuyd.nl</t>
+        </is>
+      </c>
+      <c r="I883" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J883" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K883" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Zuyd University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="L883" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M883" s="9" t="inlineStr">
+        <is>
+          <t>https://www.zuyd.nl/locations-and-contact</t>
+        </is>
+      </c>
+      <c r="N883" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O883" s="9" t="inlineStr"/>
+      <c r="P883" s="9" t="inlineStr"/>
+      <c r="Q883" s="9" t="inlineStr"/>
+    </row>
+    <row r="884">
+      <c r="A884" s="9" t="n">
+        <v>883</v>
+      </c>
+      <c r="B884" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C884" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D884" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E884" s="9" t="inlineStr">
+        <is>
+          <t>Inholland University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="F884" s="9" t="inlineStr"/>
+      <c r="G884" s="9" t="inlineStr"/>
+      <c r="H884" s="9" t="inlineStr">
+        <is>
+          <t>admissions@inholland.nl</t>
+        </is>
+      </c>
+      <c r="I884" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J884" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K884" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Inholland University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="L884" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M884" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inholland.nl/about-inholland/contact-us</t>
+        </is>
+      </c>
+      <c r="N884" s="9" t="inlineStr">
+        <is>
+          <t>Admissions/general</t>
+        </is>
+      </c>
+      <c r="O884" s="9" t="inlineStr"/>
+      <c r="P884" s="9" t="inlineStr"/>
+      <c r="Q884" s="9" t="inlineStr"/>
+    </row>
+    <row r="885">
+      <c r="A885" s="9" t="n">
+        <v>884</v>
+      </c>
+      <c r="B885" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C885" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D885" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E885" s="9" t="inlineStr">
+        <is>
+          <t>University of Applied Sciences Leiden</t>
+        </is>
+      </c>
+      <c r="F885" s="9" t="inlineStr"/>
+      <c r="G885" s="9" t="inlineStr"/>
+      <c r="H885" s="9" t="inlineStr">
+        <is>
+          <t>info@hsleiden.nl</t>
+        </is>
+      </c>
+      <c r="I885" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J885" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K885" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Applied Sciences Leiden</t>
+        </is>
+      </c>
+      <c r="L885" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M885" s="9" t="inlineStr">
+        <is>
+          <t>https://www.hsleiden.nl/get-in-touch</t>
+        </is>
+      </c>
+      <c r="N885" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O885" s="9" t="inlineStr"/>
+      <c r="P885" s="9" t="inlineStr"/>
+      <c r="Q885" s="9" t="inlineStr"/>
+    </row>
+    <row r="886">
+      <c r="A886" s="9" t="n">
+        <v>885</v>
+      </c>
+      <c r="B886" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C886" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D886" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E886" s="9" t="inlineStr">
+        <is>
+          <t>Van Hall Larenstein University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="F886" s="9" t="inlineStr"/>
+      <c r="G886" s="9" t="inlineStr"/>
+      <c r="H886" s="9" t="inlineStr">
+        <is>
+          <t>info@vhluas.com</t>
+        </is>
+      </c>
+      <c r="I886" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J886" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K886" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Van Hall Larenstein University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="L886" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M886" s="9" t="inlineStr">
+        <is>
+          <t>https://www.vhluas.com/contact</t>
+        </is>
+      </c>
+      <c r="N886" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O886" s="9" t="inlineStr"/>
+      <c r="P886" s="9" t="inlineStr"/>
+      <c r="Q886" s="9" t="inlineStr"/>
+    </row>
+    <row r="887">
+      <c r="A887" s="9" t="n">
+        <v>886</v>
+      </c>
+      <c r="B887" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C887" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D887" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E887" s="9" t="inlineStr">
+        <is>
+          <t>Aeres University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="F887" s="9" t="inlineStr"/>
+      <c r="G887" s="9" t="inlineStr"/>
+      <c r="H887" s="9" t="inlineStr">
+        <is>
+          <t>info.hogeschool.wageningen@aeres.nl</t>
+        </is>
+      </c>
+      <c r="I887" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J887" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K887" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Aeres University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="L887" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M887" s="9" t="inlineStr">
+        <is>
+          <t>https://www.aeresuas.com/about-aeres-uas/contact</t>
+        </is>
+      </c>
+      <c r="N887" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O887" s="9" t="inlineStr"/>
+      <c r="P887" s="9" t="inlineStr"/>
+      <c r="Q887" s="9" t="inlineStr"/>
+    </row>
+    <row r="888">
+      <c r="A888" s="9" t="n">
+        <v>887</v>
+      </c>
+      <c r="B888" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C888" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D888" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E888" s="9" t="inlineStr">
+        <is>
+          <t>Breda University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="F888" s="9" t="inlineStr"/>
+      <c r="G888" s="9" t="inlineStr"/>
+      <c r="H888" s="9" t="inlineStr">
+        <is>
+          <t>servicedesk@buas.nl</t>
+        </is>
+      </c>
+      <c r="I888" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J888" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K888" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Breda University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="L888" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M888" s="9" t="inlineStr">
+        <is>
+          <t>https://www.buas.nl/contact-and-locations</t>
+        </is>
+      </c>
+      <c r="N888" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O888" s="9" t="inlineStr"/>
+      <c r="P888" s="9" t="inlineStr"/>
+      <c r="Q888" s="9" t="inlineStr"/>
+    </row>
+    <row r="889">
+      <c r="A889" s="9" t="n">
+        <v>888</v>
+      </c>
+      <c r="B889" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C889" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D889" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E889" s="9" t="inlineStr">
+        <is>
+          <t>IHE Delft Institute for Water Education</t>
+        </is>
+      </c>
+      <c r="F889" s="9" t="inlineStr"/>
+      <c r="G889" s="9" t="inlineStr"/>
+      <c r="H889" s="9" t="inlineStr">
+        <is>
+          <t>info@un-ihe.org</t>
+        </is>
+      </c>
+      <c r="I889" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J889" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K889" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for IHE Delft Institute for Water Education</t>
+        </is>
+      </c>
+      <c r="L889" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M889" s="9" t="inlineStr">
+        <is>
+          <t>https://www.un-ihe.org/contact</t>
+        </is>
+      </c>
+      <c r="N889" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O889" s="9" t="inlineStr"/>
+      <c r="P889" s="9" t="inlineStr"/>
+      <c r="Q889" s="9" t="inlineStr"/>
+    </row>
+    <row r="890">
+      <c r="A890" s="9" t="n">
+        <v>889</v>
+      </c>
+      <c r="B890" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C890" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D890" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E890" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands Defence Academy</t>
+        </is>
+      </c>
+      <c r="F890" s="9" t="inlineStr"/>
+      <c r="G890" s="9" t="inlineStr"/>
+      <c r="H890" s="9" t="inlineStr">
+        <is>
+          <t>nlda@mindef.nl</t>
+        </is>
+      </c>
+      <c r="I890" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J890" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K890" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for Netherlands Defence Academy</t>
+        </is>
+      </c>
+      <c r="L890" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M890" s="9" t="inlineStr">
+        <is>
+          <t>https://english.defensie.nl/topics</t>
+        </is>
+      </c>
+      <c r="N890" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O890" s="9" t="inlineStr"/>
+      <c r="P890" s="9" t="inlineStr"/>
+      <c r="Q890" s="9" t="inlineStr"/>
+    </row>
+    <row r="891">
+      <c r="A891" s="9" t="n">
+        <v>890</v>
+      </c>
+      <c r="B891" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C891" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D891" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E891" s="9" t="inlineStr">
+        <is>
+          <t>STC Group</t>
+        </is>
+      </c>
+      <c r="F891" s="9" t="inlineStr"/>
+      <c r="G891" s="9" t="inlineStr"/>
+      <c r="H891" s="9" t="inlineStr">
+        <is>
+          <t>info@stc-group.nl</t>
+        </is>
+      </c>
+      <c r="I891" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J891" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K891" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for STC Group</t>
+        </is>
+      </c>
+      <c r="L891" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M891" s="9" t="inlineStr">
+        <is>
+          <t>https://railmarket.com (confirmed via stc-group.nl domain)</t>
+        </is>
+      </c>
+      <c r="N891" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O891" s="9" t="inlineStr"/>
+      <c r="P891" s="9" t="inlineStr"/>
+      <c r="Q891" s="9" t="inlineStr"/>
+    </row>
+    <row r="892">
+      <c r="A892" s="9" t="n">
+        <v>891</v>
+      </c>
+      <c r="B892" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C892" s="9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D892" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E892" s="9" t="inlineStr">
+        <is>
+          <t>NCOI University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="F892" s="9" t="inlineStr"/>
+      <c r="G892" s="9" t="inlineStr"/>
+      <c r="H892" s="9" t="inlineStr">
+        <is>
+          <t>info@ncoi.nl</t>
+        </is>
+      </c>
+      <c r="I892" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J892" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K892" s="9" t="inlineStr">
+        <is>
+          <t>External Mentor for NCOI University of Applied Sciences</t>
+        </is>
+      </c>
+      <c r="L892" s="9" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M892" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ncoi.nl (Contact)</t>
+        </is>
+      </c>
+      <c r="N892" s="9" t="inlineStr">
+        <is>
+          <t>General contact</t>
+        </is>
+      </c>
+      <c r="O892" s="9" t="inlineStr"/>
+      <c r="P892" s="9" t="inlineStr"/>
+      <c r="Q892" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O207"/>
@@ -47441,21 +57114,21 @@
     <row r="3" ht="15" customHeight="1" s="10">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>On hold: existing contact</t>
+          <t>On hold</t>
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="10">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Blocked / other</t>
+          <t>Blocked/other</t>
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="10">
@@ -47465,20 +57138,20 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0</v>
-      </c>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="n"/>
+      <c r="B6" s="9" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="10">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
+          <t>Response Count</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="10">
       <c r="A8" s="9" t="inlineStr">

--- a/data/Incubation_Outreach_Tracker.xlsx
+++ b/data/Incubation_Outreach_Tracker.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q892"/>
+  <dimension ref="A1:Q923"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="9" min="1" max="1"/>
@@ -10676,17 +10676,37 @@
         </is>
       </c>
       <c r="G164" s="14" t="n"/>
-      <c r="H164" s="14" t="n"/>
+      <c r="H164" s="14" t="inlineStr">
+        <is>
+          <t>info@mdx.ac.ae</t>
+        </is>
+      </c>
       <c r="I164" s="14" t="inlineStr">
         <is>
-          <t>Blocked: no hub email</t>
-        </is>
-      </c>
-      <c r="J164" s="14" t="n"/>
-      <c r="K164" s="14" t="n"/>
-      <c r="L164" s="14" t="n"/>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J164" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K164" s="14" t="inlineStr">
+        <is>
+          <t>External Mentor for Middlesex University Dubai</t>
+        </is>
+      </c>
+      <c r="L164" s="14" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
       <c r="M164" s="14" t="n"/>
-      <c r="N164" s="14" t="n"/>
+      <c r="N164" s="14" t="inlineStr">
+        <is>
+          <t>Previously blocked (no hub email); general email found via Gulf master list research</t>
+        </is>
+      </c>
       <c r="O164" s="14" t="n"/>
       <c r="P164" s="13" t="n"/>
       <c r="Q164" s="13" t="n"/>
@@ -11834,19 +11854,35 @@
         </is>
       </c>
       <c r="G182" s="14" t="n"/>
-      <c r="H182" s="14" t="n"/>
+      <c r="H182" s="14" t="inlineStr">
+        <is>
+          <t>info@ajman.ac.ae</t>
+        </is>
+      </c>
       <c r="I182" s="14" t="inlineStr">
         <is>
-          <t>Blocked: site rejects requests</t>
-        </is>
-      </c>
-      <c r="J182" s="14" t="n"/>
-      <c r="K182" s="14" t="n"/>
-      <c r="L182" s="14" t="n"/>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J182" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K182" s="14" t="inlineStr">
+        <is>
+          <t>External Mentor for Ajman University</t>
+        </is>
+      </c>
+      <c r="L182" s="14" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
       <c r="M182" s="14" t="n"/>
       <c r="N182" s="14" t="inlineStr">
         <is>
-          <t>115 startups; Hi2 certified</t>
+          <t>115 startups; Hi2 certified | Previously blocked (site rejected requests); email found via Gulf master list research</t>
         </is>
       </c>
       <c r="O182" s="14" t="n"/>
@@ -57068,6 +57104,1921 @@
       <c r="O892" s="9" t="inlineStr"/>
       <c r="P892" s="9" t="inlineStr"/>
       <c r="Q892" s="9" t="inlineStr"/>
+    </row>
+    <row r="893">
+      <c r="A893" s="9" t="n">
+        <v>892</v>
+      </c>
+      <c r="B893" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C893" s="9" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D893" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E893" s="9" t="inlineStr">
+        <is>
+          <t>Curtin University Dubai</t>
+        </is>
+      </c>
+      <c r="H893" s="9" t="inlineStr">
+        <is>
+          <t>info@curtindubai.ac.ae</t>
+        </is>
+      </c>
+      <c r="I893" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J893" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>External Mentor for Curtin University Dubai</t>
+        </is>
+      </c>
+      <c r="L893" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M893" s="9" t="inlineStr">
+        <is>
+          <t>https://curtindubai.ac.ae/</t>
+        </is>
+      </c>
+      <c r="N893" s="9" t="inlineStr">
+        <is>
+          <t>From user's gulf_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="9" t="n">
+        <v>893</v>
+      </c>
+      <c r="B894" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C894" s="9" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D894" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E894" s="9" t="inlineStr">
+        <is>
+          <t>University of Fujairah</t>
+        </is>
+      </c>
+      <c r="H894" s="9" t="inlineStr">
+        <is>
+          <t>info@uof.ac.ae</t>
+        </is>
+      </c>
+      <c r="I894" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J894" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Fujairah</t>
+        </is>
+      </c>
+      <c r="L894" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M894" s="9" t="inlineStr">
+        <is>
+          <t>https://www.uof.ac.ae/</t>
+        </is>
+      </c>
+      <c r="N894" s="9" t="inlineStr">
+        <is>
+          <t>From user's gulf_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="9" t="n">
+        <v>894</v>
+      </c>
+      <c r="B895" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C895" s="9" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D895" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E895" s="9" t="inlineStr">
+        <is>
+          <t>Higher Colleges of Technology</t>
+        </is>
+      </c>
+      <c r="H895" s="9" t="inlineStr">
+        <is>
+          <t>info@hct.ac.ae</t>
+        </is>
+      </c>
+      <c r="I895" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J895" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K895" t="inlineStr">
+        <is>
+          <t>External Mentor for Higher Colleges of Technology</t>
+        </is>
+      </c>
+      <c r="L895" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M895" s="9" t="inlineStr">
+        <is>
+          <t>https://hct.ac.ae/</t>
+        </is>
+      </c>
+      <c r="N895" s="9" t="inlineStr">
+        <is>
+          <t>From user's gulf_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="9" t="n">
+        <v>895</v>
+      </c>
+      <c r="B896" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C896" s="9" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D896" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E896" s="9" t="inlineStr">
+        <is>
+          <t>Liwa University</t>
+        </is>
+      </c>
+      <c r="H896" s="9" t="inlineStr">
+        <is>
+          <t>info@lu.ac.ae</t>
+        </is>
+      </c>
+      <c r="I896" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J896" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>External Mentor for Liwa University</t>
+        </is>
+      </c>
+      <c r="L896" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M896" s="9" t="inlineStr">
+        <is>
+          <t>https://lu.ac.ae/</t>
+        </is>
+      </c>
+      <c r="N896" s="9" t="inlineStr">
+        <is>
+          <t>From user's gulf_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="9" t="n">
+        <v>896</v>
+      </c>
+      <c r="B897" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C897" s="9" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D897" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E897" s="9" t="inlineStr">
+        <is>
+          <t>University of Birmingham Dubai</t>
+        </is>
+      </c>
+      <c r="H897" s="9" t="inlineStr">
+        <is>
+          <t>dubai@contacts.bham.ac.uk</t>
+        </is>
+      </c>
+      <c r="I897" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J897" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Birmingham Dubai</t>
+        </is>
+      </c>
+      <c r="L897" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M897" s="9" t="inlineStr">
+        <is>
+          <t>https://www.birmingham.ac.uk/dubai</t>
+        </is>
+      </c>
+      <c r="N897" s="9" t="inlineStr">
+        <is>
+          <t>From user's gulf_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="9" t="n">
+        <v>897</v>
+      </c>
+      <c r="B898" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C898" s="9" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D898" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E898" s="9" t="inlineStr">
+        <is>
+          <t>University of Wollongong in Dubai</t>
+        </is>
+      </c>
+      <c r="H898" s="9" t="inlineStr">
+        <is>
+          <t>info@uowdubai.ac.ae</t>
+        </is>
+      </c>
+      <c r="I898" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J898" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Wollongong in Dubai</t>
+        </is>
+      </c>
+      <c r="L898" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M898" s="9" t="inlineStr">
+        <is>
+          <t>https://www.uowdubai.ac.ae/</t>
+        </is>
+      </c>
+      <c r="N898" s="9" t="inlineStr">
+        <is>
+          <t>From user's gulf_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="9" t="n">
+        <v>898</v>
+      </c>
+      <c r="B899" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C899" s="9" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D899" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E899" s="9" t="inlineStr">
+        <is>
+          <t>Umm Al-Qura University</t>
+        </is>
+      </c>
+      <c r="H899" s="9" t="inlineStr">
+        <is>
+          <t>info@uqu.edu.sa</t>
+        </is>
+      </c>
+      <c r="I899" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J899" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>External Mentor for Umm Al-Qura University</t>
+        </is>
+      </c>
+      <c r="L899" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M899" s="9" t="inlineStr">
+        <is>
+          <t>https://uqu.edu.sa/</t>
+        </is>
+      </c>
+      <c r="N899" s="9" t="inlineStr">
+        <is>
+          <t>From user's gulf_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="9" t="n">
+        <v>899</v>
+      </c>
+      <c r="B900" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C900" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D900" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E900" s="9" t="inlineStr">
+        <is>
+          <t>International College of Engineering and Management</t>
+        </is>
+      </c>
+      <c r="H900" s="9" t="inlineStr">
+        <is>
+          <t>info@icem.edu.om</t>
+        </is>
+      </c>
+      <c r="I900" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J900" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>External Mentor for International College of Engineering and Management</t>
+        </is>
+      </c>
+      <c r="L900" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M900" s="9" t="inlineStr">
+        <is>
+          <t>https://www.icem.edu.om/</t>
+        </is>
+      </c>
+      <c r="N900" s="9" t="inlineStr">
+        <is>
+          <t>From user's gulf_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="9" t="n">
+        <v>900</v>
+      </c>
+      <c r="B901" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C901" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D901" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E901" s="9" t="inlineStr">
+        <is>
+          <t>University of Buraimi</t>
+        </is>
+      </c>
+      <c r="H901" s="9" t="inlineStr">
+        <is>
+          <t>info@uob.edu.om</t>
+        </is>
+      </c>
+      <c r="I901" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J901" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>External Mentor for University of Buraimi</t>
+        </is>
+      </c>
+      <c r="L901" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M901" s="9" t="inlineStr">
+        <is>
+          <t>https://www.uob.edu.om/</t>
+        </is>
+      </c>
+      <c r="N901" s="9" t="inlineStr">
+        <is>
+          <t>From user's gulf_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="9" t="n">
+        <v>901</v>
+      </c>
+      <c r="B902" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C902" s="9" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="D902" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E902" s="9" t="inlineStr">
+        <is>
+          <t>Australian University</t>
+        </is>
+      </c>
+      <c r="H902" s="9" t="inlineStr">
+        <is>
+          <t>contactus@au.edu.kw</t>
+        </is>
+      </c>
+      <c r="I902" s="9" t="inlineStr">
+        <is>
+          <t>On hold (prior contact)</t>
+        </is>
+      </c>
+      <c r="M902" s="9" t="inlineStr">
+        <is>
+          <t>https://www.au.edu.kw/academics/our-colleges-schools-departments/</t>
+        </is>
+      </c>
+      <c r="N902" s="9" t="inlineStr">
+        <is>
+          <t>From user's gulf_master spreadsheet | Prior contact found (sent 2026-09-26 to innovate@au.edu.kw)</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="9" t="n">
+        <v>902</v>
+      </c>
+      <c r="B903" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C903" s="9" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="D903" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E903" s="9" t="inlineStr">
+        <is>
+          <t>Kuwait College of Science and Technology (KCST)</t>
+        </is>
+      </c>
+      <c r="H903" s="9" t="inlineStr">
+        <is>
+          <t>info@kcst.edu.kw</t>
+        </is>
+      </c>
+      <c r="I903" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J903" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>External Mentor for Kuwait College of Science and Technology (KCST)</t>
+        </is>
+      </c>
+      <c r="L903" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M903" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kcst.edu.kw/</t>
+        </is>
+      </c>
+      <c r="N903" s="9" t="inlineStr">
+        <is>
+          <t>From user's gulf_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="9" t="n">
+        <v>903</v>
+      </c>
+      <c r="B904" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C904" s="9" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="D904" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E904" s="9" t="inlineStr">
+        <is>
+          <t>Kuwait Technical College</t>
+        </is>
+      </c>
+      <c r="H904" s="9" t="inlineStr">
+        <is>
+          <t>info@ktech.edu.kw</t>
+        </is>
+      </c>
+      <c r="I904" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J904" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>External Mentor for Kuwait Technical College</t>
+        </is>
+      </c>
+      <c r="L904" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M904" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ktech.edu.kw/</t>
+        </is>
+      </c>
+      <c r="N904" s="9" t="inlineStr">
+        <is>
+          <t>From user's gulf_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="9" t="n">
+        <v>904</v>
+      </c>
+      <c r="B905" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C905" s="9" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="D905" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E905" s="9" t="inlineStr">
+        <is>
+          <t>Applied Science University</t>
+        </is>
+      </c>
+      <c r="H905" s="9" t="inlineStr">
+        <is>
+          <t>info@asu.edu.bh</t>
+        </is>
+      </c>
+      <c r="I905" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J905" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K905" t="inlineStr">
+        <is>
+          <t>External Mentor for Applied Science University</t>
+        </is>
+      </c>
+      <c r="L905" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M905" s="9" t="inlineStr">
+        <is>
+          <t>https://www.asu.edu.bh/</t>
+        </is>
+      </c>
+      <c r="N905" s="9" t="inlineStr">
+        <is>
+          <t>From user's gulf_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="9" t="n">
+        <v>905</v>
+      </c>
+      <c r="B906" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C906" s="9" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="D906" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E906" s="9" t="inlineStr">
+        <is>
+          <t>Ahlia University</t>
+        </is>
+      </c>
+      <c r="H906" s="9" t="inlineStr">
+        <is>
+          <t>info@ahlia.edu.bh</t>
+        </is>
+      </c>
+      <c r="I906" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J906" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>External Mentor for Ahlia University</t>
+        </is>
+      </c>
+      <c r="L906" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M906" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ahlia.edu.bh/</t>
+        </is>
+      </c>
+      <c r="N906" s="9" t="inlineStr">
+        <is>
+          <t>From user's gulf_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="9" t="n">
+        <v>906</v>
+      </c>
+      <c r="B907" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C907" s="9" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="D907" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E907" s="9" t="inlineStr">
+        <is>
+          <t>Nasser Centre for Science and Technology</t>
+        </is>
+      </c>
+      <c r="H907" s="9" t="inlineStr">
+        <is>
+          <t>info@ncst.edu.bh</t>
+        </is>
+      </c>
+      <c r="I907" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J907" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>External Mentor for Nasser Centre for Science and Technology</t>
+        </is>
+      </c>
+      <c r="L907" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M907" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ncst.edu.bh/</t>
+        </is>
+      </c>
+      <c r="N907" s="9" t="inlineStr">
+        <is>
+          <t>From user's gulf_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="9" t="n">
+        <v>907</v>
+      </c>
+      <c r="B908" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C908" s="9" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="D908" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E908" s="9" t="inlineStr">
+        <is>
+          <t>Albright Institute</t>
+        </is>
+      </c>
+      <c r="G908" s="9" t="inlineStr">
+        <is>
+          <t>Md Abu Huraira</t>
+        </is>
+      </c>
+      <c r="H908" s="9" t="inlineStr">
+        <is>
+          <t>info@albrightinstitute.edu.au</t>
+        </is>
+      </c>
+      <c r="I908" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J908" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K908" t="inlineStr">
+        <is>
+          <t>External Mentor for Albright Institute</t>
+        </is>
+      </c>
+      <c r="L908" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M908" s="9" t="inlineStr">
+        <is>
+          <t>https://albrightinstitute.edu.au/</t>
+        </is>
+      </c>
+      <c r="N908" s="9" t="inlineStr">
+        <is>
+          <t>From user's aus_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="9" t="n">
+        <v>908</v>
+      </c>
+      <c r="B909" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C909" s="9" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="D909" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E909" s="9" t="inlineStr">
+        <is>
+          <t>Australian College of Management and Innovation (ACMi)</t>
+        </is>
+      </c>
+      <c r="G909" s="9" t="inlineStr">
+        <is>
+          <t>Muhammad Junaid Khan</t>
+        </is>
+      </c>
+      <c r="H909" s="9" t="inlineStr">
+        <is>
+          <t>ceo@acmi.wa.edu.au</t>
+        </is>
+      </c>
+      <c r="I909" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J909" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>External Mentor for Australian College of Management and Innovation (ACMi)</t>
+        </is>
+      </c>
+      <c r="L909" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M909" s="9" t="inlineStr">
+        <is>
+          <t>https://acmi.wa.edu.au/</t>
+        </is>
+      </c>
+      <c r="N909" s="9" t="inlineStr">
+        <is>
+          <t>From user's aus_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="9" t="n">
+        <v>909</v>
+      </c>
+      <c r="B910" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C910" s="9" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="D910" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E910" s="9" t="inlineStr">
+        <is>
+          <t>Australian Institute of Advanced Studies</t>
+        </is>
+      </c>
+      <c r="G910" s="9" t="inlineStr">
+        <is>
+          <t>Noel Higginbotham</t>
+        </is>
+      </c>
+      <c r="H910" s="9" t="inlineStr">
+        <is>
+          <t>information@aias.edu.au</t>
+        </is>
+      </c>
+      <c r="I910" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J910" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>External Mentor for Australian Institute of Advanced Studies</t>
+        </is>
+      </c>
+      <c r="L910" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M910" s="9" t="inlineStr">
+        <is>
+          <t>https://aias.edu.au/</t>
+        </is>
+      </c>
+      <c r="N910" s="9" t="inlineStr">
+        <is>
+          <t>From user's aus_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="9" t="n">
+        <v>910</v>
+      </c>
+      <c r="B911" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C911" s="9" t="inlineStr">
+        <is>
+          <t>TAS</t>
+        </is>
+      </c>
+      <c r="D911" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E911" s="9" t="inlineStr">
+        <is>
+          <t>Australian Maritime College</t>
+        </is>
+      </c>
+      <c r="G911" s="9" t="inlineStr">
+        <is>
+          <t>AMC Team</t>
+        </is>
+      </c>
+      <c r="H911" s="9" t="inlineStr">
+        <is>
+          <t>amc.future.students@utas.edu.au</t>
+        </is>
+      </c>
+      <c r="I911" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J911" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>External Mentor for Australian Maritime College</t>
+        </is>
+      </c>
+      <c r="L911" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M911" s="9" t="inlineStr">
+        <is>
+          <t>https://www.amc.edu.au/</t>
+        </is>
+      </c>
+      <c r="N911" s="9" t="inlineStr">
+        <is>
+          <t>From user's aus_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="9" t="n">
+        <v>911</v>
+      </c>
+      <c r="B912" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C912" s="9" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="D912" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E912" s="9" t="inlineStr">
+        <is>
+          <t>Danford College</t>
+        </is>
+      </c>
+      <c r="H912" s="9" t="inlineStr">
+        <is>
+          <t>support@danford.edu.au</t>
+        </is>
+      </c>
+      <c r="I912" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J912" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K912" t="inlineStr">
+        <is>
+          <t>External Mentor for Danford College</t>
+        </is>
+      </c>
+      <c r="L912" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M912" s="9" t="inlineStr">
+        <is>
+          <t>https://danford.edu.au/</t>
+        </is>
+      </c>
+      <c r="N912" s="9" t="inlineStr">
+        <is>
+          <t>From user's aus_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="9" t="n">
+        <v>912</v>
+      </c>
+      <c r="B913" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C913" s="9" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="D913" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E913" s="9" t="inlineStr">
+        <is>
+          <t>Engineering Institute of Technology</t>
+        </is>
+      </c>
+      <c r="G913" s="9" t="inlineStr">
+        <is>
+          <t>Caroline Patterson</t>
+        </is>
+      </c>
+      <c r="H913" s="9" t="inlineStr">
+        <is>
+          <t>eit@eit.edu.au</t>
+        </is>
+      </c>
+      <c r="I913" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J913" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K913" t="inlineStr">
+        <is>
+          <t>External Mentor for Engineering Institute of Technology</t>
+        </is>
+      </c>
+      <c r="L913" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M913" s="9" t="inlineStr">
+        <is>
+          <t>https://www.eit.edu.au/</t>
+        </is>
+      </c>
+      <c r="N913" s="9" t="inlineStr">
+        <is>
+          <t>From user's aus_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="9" t="n">
+        <v>913</v>
+      </c>
+      <c r="B914" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C914" s="9" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="D914" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E914" s="9" t="inlineStr">
+        <is>
+          <t>Griffith University</t>
+        </is>
+      </c>
+      <c r="G914" s="9" t="inlineStr">
+        <is>
+          <t>School of Engineering and Built Environment</t>
+        </is>
+      </c>
+      <c r="H914" s="9" t="inlineStr">
+        <is>
+          <t>ebe-admin@griffith.edu.au</t>
+        </is>
+      </c>
+      <c r="I914" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J914" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>External Mentor for Griffith University</t>
+        </is>
+      </c>
+      <c r="L914" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M914" s="9" t="inlineStr">
+        <is>
+          <t>https://www.griffith.edu.au/</t>
+        </is>
+      </c>
+      <c r="N914" s="9" t="inlineStr">
+        <is>
+          <t>From user's aus_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="9" t="n">
+        <v>914</v>
+      </c>
+      <c r="B915" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C915" s="9" t="inlineStr">
+        <is>
+          <t>NSW</t>
+        </is>
+      </c>
+      <c r="D915" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E915" s="9" t="inlineStr">
+        <is>
+          <t>Lead College</t>
+        </is>
+      </c>
+      <c r="G915" s="9" t="inlineStr">
+        <is>
+          <t>David Garner</t>
+        </is>
+      </c>
+      <c r="H915" s="9" t="inlineStr">
+        <is>
+          <t>info@leadcollege.edu.au</t>
+        </is>
+      </c>
+      <c r="I915" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J915" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>External Mentor for Lead College</t>
+        </is>
+      </c>
+      <c r="L915" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M915" s="9" t="inlineStr">
+        <is>
+          <t>https://leadcollege.edu.au/</t>
+        </is>
+      </c>
+      <c r="N915" s="9" t="inlineStr">
+        <is>
+          <t>From user's aus_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="9" t="n">
+        <v>915</v>
+      </c>
+      <c r="B916" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C916" s="9" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="D916" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E916" s="9" t="inlineStr">
+        <is>
+          <t>Melbourne Polytechnic</t>
+        </is>
+      </c>
+      <c r="G916" s="9" t="inlineStr">
+        <is>
+          <t>Melbourne Polytechnic Team</t>
+        </is>
+      </c>
+      <c r="H916" s="9" t="inlineStr">
+        <is>
+          <t>info@melbournepolytechnic.edu.au</t>
+        </is>
+      </c>
+      <c r="I916" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J916" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K916" t="inlineStr">
+        <is>
+          <t>External Mentor for Melbourne Polytechnic</t>
+        </is>
+      </c>
+      <c r="L916" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M916" s="9" t="inlineStr">
+        <is>
+          <t>https://www.melbournepolytechnic.edu.au/</t>
+        </is>
+      </c>
+      <c r="N916" s="9" t="inlineStr">
+        <is>
+          <t>From user's aus_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="9" t="n">
+        <v>916</v>
+      </c>
+      <c r="B917" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C917" s="9" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="D917" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E917" s="9" t="inlineStr">
+        <is>
+          <t>Nova Anglia College</t>
+        </is>
+      </c>
+      <c r="G917" s="9" t="inlineStr">
+        <is>
+          <t>Nova Anglia Team</t>
+        </is>
+      </c>
+      <c r="H917" s="9" t="inlineStr">
+        <is>
+          <t>admissions@nac.edu.au</t>
+        </is>
+      </c>
+      <c r="I917" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J917" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K917" t="inlineStr">
+        <is>
+          <t>External Mentor for Nova Anglia College</t>
+        </is>
+      </c>
+      <c r="L917" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M917" s="9" t="inlineStr">
+        <is>
+          <t>https://nac.edu.au/</t>
+        </is>
+      </c>
+      <c r="N917" s="9" t="inlineStr">
+        <is>
+          <t>From user's aus_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="9" t="n">
+        <v>917</v>
+      </c>
+      <c r="B918" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C918" s="9" t="inlineStr">
+        <is>
+          <t>NSW</t>
+        </is>
+      </c>
+      <c r="D918" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E918" s="9" t="inlineStr">
+        <is>
+          <t>Oban College</t>
+        </is>
+      </c>
+      <c r="G918" s="9" t="inlineStr">
+        <is>
+          <t>Jugandeep</t>
+        </is>
+      </c>
+      <c r="H918" s="9" t="inlineStr">
+        <is>
+          <t>info@oban.edu.au</t>
+        </is>
+      </c>
+      <c r="I918" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J918" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K918" t="inlineStr">
+        <is>
+          <t>External Mentor for Oban College</t>
+        </is>
+      </c>
+      <c r="L918" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M918" s="9" t="inlineStr">
+        <is>
+          <t>https://oban.edu.au/</t>
+        </is>
+      </c>
+      <c r="N918" s="9" t="inlineStr">
+        <is>
+          <t>From user's aus_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="9" t="n">
+        <v>918</v>
+      </c>
+      <c r="B919" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C919" s="9" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="D919" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E919" s="9" t="inlineStr">
+        <is>
+          <t>SITS College</t>
+        </is>
+      </c>
+      <c r="G919" s="9" t="inlineStr">
+        <is>
+          <t>SITS Team</t>
+        </is>
+      </c>
+      <c r="H919" s="9" t="inlineStr">
+        <is>
+          <t>info@sits.edu.au</t>
+        </is>
+      </c>
+      <c r="I919" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J919" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K919" t="inlineStr">
+        <is>
+          <t>External Mentor for SITS College</t>
+        </is>
+      </c>
+      <c r="L919" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M919" s="9" t="inlineStr">
+        <is>
+          <t>https://sits.edu.au/</t>
+        </is>
+      </c>
+      <c r="N919" s="9" t="inlineStr">
+        <is>
+          <t>From user's aus_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="9" t="n">
+        <v>919</v>
+      </c>
+      <c r="B920" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C920" s="9" t="inlineStr">
+        <is>
+          <t>NSW</t>
+        </is>
+      </c>
+      <c r="D920" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E920" s="9" t="inlineStr">
+        <is>
+          <t>TAFE NSW</t>
+        </is>
+      </c>
+      <c r="G920" s="9" t="inlineStr">
+        <is>
+          <t>TAFE NSW Team</t>
+        </is>
+      </c>
+      <c r="H920" s="9" t="inlineStr">
+        <is>
+          <t>customer_contact_centre@tafensw.edu.au</t>
+        </is>
+      </c>
+      <c r="I920" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J920" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K920" t="inlineStr">
+        <is>
+          <t>External Mentor for TAFE NSW</t>
+        </is>
+      </c>
+      <c r="L920" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M920" s="9" t="inlineStr">
+        <is>
+          <t>https://www.tafensw.edu.au/</t>
+        </is>
+      </c>
+      <c r="N920" s="9" t="inlineStr">
+        <is>
+          <t>From user's aus_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="9" t="n">
+        <v>920</v>
+      </c>
+      <c r="B921" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C921" s="9" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="D921" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E921" s="9" t="inlineStr">
+        <is>
+          <t>TAFE Queensland</t>
+        </is>
+      </c>
+      <c r="G921" s="9" t="inlineStr">
+        <is>
+          <t>SkillsTech Team</t>
+        </is>
+      </c>
+      <c r="H921" s="9" t="inlineStr">
+        <is>
+          <t>skillstech.marketing@tafeqld.edu.au</t>
+        </is>
+      </c>
+      <c r="I921" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J921" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>External Mentor for TAFE Queensland</t>
+        </is>
+      </c>
+      <c r="L921" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M921" s="9" t="inlineStr">
+        <is>
+          <t>https://tafeqld.edu.au/</t>
+        </is>
+      </c>
+      <c r="N921" s="9" t="inlineStr">
+        <is>
+          <t>From user's aus_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="9" t="n">
+        <v>921</v>
+      </c>
+      <c r="B922" s="9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C922" s="9" t="inlineStr">
+        <is>
+          <t>ACT</t>
+        </is>
+      </c>
+      <c r="D922" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E922" s="9" t="inlineStr">
+        <is>
+          <t>UNSW Canberra</t>
+        </is>
+      </c>
+      <c r="G922" s="9" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="H922" s="9" t="inlineStr">
+        <is>
+          <t>set.cbr@unsw.edu.au</t>
+        </is>
+      </c>
+      <c r="I922" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J922" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>External Mentor for UNSW Canberra</t>
+        </is>
+      </c>
+      <c r="L922" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M922" s="9" t="inlineStr">
+        <is>
+          <t>https://www.unsw.edu.au/canberra</t>
+        </is>
+      </c>
+      <c r="N922" s="9" t="inlineStr">
+        <is>
+          <t>From user's aus_master spreadsheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="9" t="n">
+        <v>922</v>
+      </c>
+      <c r="B923" s="9" t="inlineStr">
+        <is>
+          <t>Gulf</t>
+        </is>
+      </c>
+      <c r="C923" s="9" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D923" s="9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E923" s="9" t="inlineStr">
+        <is>
+          <t>Global College of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="H923" s="9" t="inlineStr">
+        <is>
+          <t>info@gcet.edu.om</t>
+        </is>
+      </c>
+      <c r="I923" s="9" t="inlineStr">
+        <is>
+          <t>Drafted (not sent)</t>
+        </is>
+      </c>
+      <c r="J923" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K923" t="inlineStr">
+        <is>
+          <t>External Mentor for Global College of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="L923" t="inlineStr">
+        <is>
+          <t>Institution name in greeting/body; template style</t>
+        </is>
+      </c>
+      <c r="M923" s="9" t="inlineStr">
+        <is>
+          <t>https://gcet.edu.om/</t>
+        </is>
+      </c>
+      <c r="N923" s="9" t="inlineStr">
+        <is>
+          <t>From user's gulf_master spreadsheet</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:O207"/>
@@ -57118,7 +59069,7 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="10">
@@ -57128,7 +59079,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="10">
@@ -57138,7 +59089,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>146</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6">
